--- a/GORRITI/Julio/GORRITI-Julio.xlsx
+++ b/GORRITI/Julio/GORRITI-Julio.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\GORRITI\Junio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\GORRITI\Julio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27CF83AB-B0C8-435D-94A4-E5DC1DF81C6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09C0ABA2-A758-4666-A0FC-8EEAEB3D5458}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -19,14 +19,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$R$90</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$138</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$140</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="246">
   <si>
     <t>MAIL: consorciogorriti368@gmail.com</t>
   </si>
@@ -58,9 +58,6 @@
     <t>10 A 16HS - EMERGENCIAS 24HS</t>
   </si>
   <si>
-    <t>VTO 14/07</t>
-  </si>
-  <si>
     <t>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. CASO CONTRARIO SE INFORMARA VIA CARTA DOCUMENTO A LA UNIDAD FUNCIONAL QUE CREEMOS QUE CORRESPONDE, CUYO COSTO SERA IMPUTADO A LA UNIDAD FUNCIONAL SOSPECHADA.</t>
   </si>
   <si>
@@ -646,48 +643,18 @@
     <t>DE BIAGGIO PABLO</t>
   </si>
   <si>
-    <t>PERÍODO: JUNIO</t>
-  </si>
-  <si>
-    <t>Sindicatos mes de JUNIO</t>
-  </si>
-  <si>
-    <t>HONORARIOS ADMINISTRACION RC - SE ABONA EL MES MAYO - SE DEBE JUNIO</t>
-  </si>
-  <si>
     <t>Transf 19/06</t>
   </si>
   <si>
-    <t>Transf 17/06</t>
-  </si>
-  <si>
-    <t>Transf 12/06</t>
-  </si>
-  <si>
     <t>Ascensores Lema - Provision y colocacion de una nueva base original para antenas de freno, para cabezal de freno y una nueva antena con el buje correspondiente de apertura y cierre del ascensor unico que esta andando</t>
   </si>
   <si>
     <t>PMC 09/06</t>
   </si>
   <si>
-    <t>Transf 11/06</t>
-  </si>
-  <si>
     <t>HONORARIOS CONTADOR GUSTAVO PADRON</t>
   </si>
   <si>
-    <t>Transf 09/06</t>
-  </si>
-  <si>
-    <t>Doartero soldadura de puerta de acero inoxidable principal</t>
-  </si>
-  <si>
-    <t>Debito 12/06</t>
-  </si>
-  <si>
-    <t>Articuos de limpieza</t>
-  </si>
-  <si>
     <t>Debito 10/06</t>
   </si>
   <si>
@@ -709,24 +676,12 @@
     <t>Debito 17/06</t>
   </si>
   <si>
-    <t>Transf 16/06</t>
-  </si>
-  <si>
     <t>Matias Silva - Destapacion 10A</t>
   </si>
   <si>
     <t>Doartero 50% adelanto mano de obra trabajo caños ascendentes</t>
   </si>
   <si>
-    <t>Efectivo 13/06</t>
-  </si>
-  <si>
-    <t>Doble imputacion de gasto (Destapaciones Italoamericana -  Mes anterior)</t>
-  </si>
-  <si>
-    <t>Castellano Alejandro - Abono de servicio de mantenimiento de grupo electrogeno y porton junio</t>
-  </si>
-  <si>
     <t>MANTENIMIENTO DE CUENTA - NO SE DEBITO NUEVAMENTE</t>
   </si>
   <si>
@@ -752,6 +707,63 @@
   </si>
   <si>
     <t>PABLO DI COIRO TIENE A FAVOR 280 MIL PESOS - PINTURA OSCAR</t>
+  </si>
+  <si>
+    <t>VTO 14/08</t>
+  </si>
+  <si>
+    <t>PERÍODO: JULIO</t>
+  </si>
+  <si>
+    <t>Sindicatos mes de JULIO</t>
+  </si>
+  <si>
+    <t>Castellano Alejandro - Abono de servicio de mantenimiento de grupo electrogeno y porton JULIO</t>
+  </si>
+  <si>
+    <t>HONORARIOS ADMINISTRACION RC - SE ABONA EL MES JUNIO - SE DEBE JULIO</t>
+  </si>
+  <si>
+    <t>Transf 14/07</t>
+  </si>
+  <si>
+    <t>Transf 15/07</t>
+  </si>
+  <si>
+    <t>Debito 17/4/07</t>
+  </si>
+  <si>
+    <t>Transf 14/7</t>
+  </si>
+  <si>
+    <t>Transf 07/07</t>
+  </si>
+  <si>
+    <t>Doartero mano de obra reparacion de portero</t>
+  </si>
+  <si>
+    <t>Transf 10/07</t>
+  </si>
+  <si>
+    <t>Articulos de limpieza</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balcazza Leonardo </t>
+  </si>
+  <si>
+    <t>Debito 14/07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doartero - </t>
+  </si>
+  <si>
+    <t>Transf 21/07</t>
+  </si>
+  <si>
+    <t>Transf 17/07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cerrajeria Ayram </t>
   </si>
 </sst>
 </file>
@@ -759,15 +771,15 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="9">
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="165" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="166" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="169" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;?_-;_-@_-"/>
-    <numFmt numFmtId="170" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="171" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
+    <numFmt numFmtId="164" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;?_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="169" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
   </numFmts>
   <fonts count="28" x14ac:knownFonts="1">
     <font>
@@ -1497,11 +1509,11 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="240">
+  <cellXfs count="242">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1509,7 +1521,7 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="8" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="2" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1522,9 +1534,9 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1539,7 +1551,7 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1549,40 +1561,40 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="10" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="10" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="15" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="16" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="16" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="16" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1597,24 +1609,24 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="6" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="21" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="21" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="21" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="16" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="16" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="21" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="21" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="21" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="22" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="22" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="21" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="22" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="22" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1627,65 +1639,64 @@
     <xf numFmtId="2" fontId="16" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="21" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="21" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="21" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="16" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="21" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="21" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="21" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="21" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="16" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="6" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="16" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="14" fillId="8" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="6" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="14" fillId="8" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="11" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="11" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="23" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="23" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="8" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="11" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="11" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="11" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="21" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="21" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="10" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1700,27 +1711,27 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="16" fillId="10" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="166" fontId="6" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="21" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="9" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="6" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="9" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="12" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="12" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1733,59 +1744,56 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="168" fontId="21" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="24" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="21" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="24" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="24" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="12" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="25" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="8" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="8" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="11" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="23" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="8" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="24" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="8" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="11" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="12" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="25" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="8" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="11" fillId="4" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="8" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="11" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="23" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="23" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="23" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="16" fontId="17" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="11" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="23" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="11" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="23" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="11" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="11" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="23" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="23" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="23" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="23" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="26" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="26" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="166" fontId="9" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="9" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="23" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="27" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="27" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="3" borderId="12" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1798,32 +1806,26 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="27" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="27" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="171" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1833,32 +1835,22 @@
     <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1870,10 +1862,36 @@
     <xf numFmtId="0" fontId="17" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="11" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="3" builtinId="3"/>
@@ -2239,57 +2257,57 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M142"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M144"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="37.5703125" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" customWidth="1"/>
-    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" customWidth="1"/>
+    <col min="1" max="1" width="37.5546875" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
+    <col min="5" max="5" width="14.6640625" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.28515625" customWidth="1"/>
+    <col min="12" max="12" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="201"/>
-      <c r="B1" s="202"/>
-      <c r="C1" s="203"/>
-      <c r="D1" s="203"/>
-      <c r="E1" s="204"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="197"/>
+      <c r="B1" s="198"/>
+      <c r="C1" s="199"/>
+      <c r="D1" s="199"/>
+      <c r="E1" s="200"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="15"/>
-      <c r="B2" s="200" t="s">
+      <c r="B2" s="196" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="70"/>
-      <c r="D2" s="200"/>
+      <c r="D2" s="196"/>
       <c r="E2" s="71"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="15"/>
-      <c r="B3" s="200" t="s">
+      <c r="B3" s="196" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="200"/>
-      <c r="D3" s="200"/>
+      <c r="C3" s="196"/>
+      <c r="D3" s="196"/>
       <c r="E3" s="71"/>
     </row>
-    <row r="4" spans="1:5" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="15"/>
-      <c r="B4" s="205" t="s">
+      <c r="B4" s="201" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="200"/>
-      <c r="D4" s="206" t="s">
+      <c r="C4" s="196"/>
+      <c r="D4" s="202" t="s">
         <v>3</v>
       </c>
       <c r="E4" s="71"/>
     </row>
-    <row r="5" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="17" t="s">
         <v>4</v>
       </c>
@@ -2300,20 +2318,20 @@
       <c r="D5" s="18"/>
       <c r="E5" s="19"/>
     </row>
-    <row r="6" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="15" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>206</v>
-      </c>
-      <c r="C6" s="207"/>
-      <c r="D6" s="200" t="s">
+        <v>228</v>
+      </c>
+      <c r="C6" s="203"/>
+      <c r="D6" s="196" t="s">
         <v>7</v>
       </c>
       <c r="E6" s="16"/>
     </row>
-    <row r="7" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="17" t="s">
         <v>8</v>
       </c>
@@ -2324,150 +2342,150 @@
       </c>
       <c r="E7" s="19"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="218" t="s">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B9" s="210" t="s">
+        <v>227</v>
+      </c>
+      <c r="C9" s="211"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="211"/>
+      <c r="C10" s="211"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B11" s="211"/>
+      <c r="C11" s="211"/>
+    </row>
+    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="216" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="212"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="212"/>
-      <c r="C10" s="212"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B11" s="212"/>
-      <c r="C11" s="212"/>
-    </row>
-    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="222" t="s">
+      <c r="B14" s="211"/>
+      <c r="C14" s="211"/>
+      <c r="D14" s="211"/>
+      <c r="E14" s="211"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="211"/>
+      <c r="B15" s="211"/>
+      <c r="C15" s="211"/>
+      <c r="D15" s="211"/>
+      <c r="E15" s="211"/>
+    </row>
+    <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="211"/>
+      <c r="B16" s="211"/>
+      <c r="C16" s="211"/>
+      <c r="D16" s="211"/>
+      <c r="E16" s="211"/>
+    </row>
+    <row r="17" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="211"/>
+      <c r="B17" s="211"/>
+      <c r="C17" s="211"/>
+      <c r="D17" s="211"/>
+      <c r="E17" s="211"/>
+    </row>
+    <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="2"/>
+    </row>
+    <row r="20" spans="1:7" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="11" t="s">
         <v>11</v>
-      </c>
-      <c r="B14" s="212"/>
-      <c r="C14" s="212"/>
-      <c r="D14" s="212"/>
-      <c r="E14" s="212"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="212"/>
-      <c r="B15" s="212"/>
-      <c r="C15" s="212"/>
-      <c r="D15" s="212"/>
-      <c r="E15" s="212"/>
-    </row>
-    <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="212"/>
-      <c r="B16" s="212"/>
-      <c r="C16" s="212"/>
-      <c r="D16" s="212"/>
-      <c r="E16" s="212"/>
-    </row>
-    <row r="17" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="212"/>
-      <c r="B17" s="212"/>
-      <c r="C17" s="212"/>
-      <c r="D17" s="212"/>
-      <c r="E17" s="212"/>
-    </row>
-    <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="2"/>
-    </row>
-    <row r="20" spans="1:7" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="11" t="s">
-        <v>12</v>
       </c>
       <c r="B21" s="12"/>
       <c r="C21" s="13"/>
       <c r="D21" s="9"/>
       <c r="E21" s="14"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="34" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B22" s="34"/>
       <c r="C22" s="34"/>
       <c r="D22" s="33"/>
       <c r="E22" s="33"/>
     </row>
-    <row r="23" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>237</v>
+        <v>222</v>
       </c>
       <c r="C23" s="5"/>
-      <c r="D23" s="160">
+      <c r="D23" s="159">
         <v>1879916</v>
       </c>
-      <c r="E23" s="155" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E23" s="154" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5"/>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
-      <c r="D24" s="160"/>
+      <c r="D24" s="159"/>
       <c r="E24" s="113"/>
     </row>
-    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5"/>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
-      <c r="D25" s="160"/>
+      <c r="D25" s="159"/>
       <c r="E25" s="113"/>
     </row>
-    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
-      <c r="D26" s="160">
+      <c r="D26" s="159">
         <v>0</v>
       </c>
       <c r="E26" s="113"/>
     </row>
-    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
-      <c r="D27" s="160"/>
+      <c r="D27" s="159"/>
       <c r="E27" s="113"/>
       <c r="G27" s="20"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="57" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B28" s="57"/>
       <c r="C28" s="57"/>
-      <c r="D28" s="161">
+      <c r="D28" s="160">
         <f>SUM(D23:D27)</f>
         <v>1879916</v>
       </c>
-      <c r="E28" s="162"/>
+      <c r="E28" s="161"/>
       <c r="G28" s="20">
         <f>D28+D37</f>
         <v>3523284</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>237</v>
+        <v>222</v>
       </c>
       <c r="C29" s="5"/>
-      <c r="D29" s="160">
+      <c r="D29" s="159">
         <v>1643368</v>
       </c>
-      <c r="E29" s="155" t="str">
+      <c r="E29" s="154" t="str">
         <f>E23</f>
         <v>Transf parcial 27/6</v>
       </c>
@@ -2475,1066 +2493,1098 @@
         <v>2000000</v>
       </c>
     </row>
-    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="27"/>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
-      <c r="D30" s="160"/>
+      <c r="D30" s="159"/>
       <c r="E30" s="113"/>
     </row>
-    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="5"/>
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
-      <c r="D31" s="160"/>
+      <c r="D31" s="159"/>
       <c r="E31" s="113"/>
     </row>
-    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5"/>
       <c r="B32" s="5"/>
       <c r="C32" s="5"/>
-      <c r="D32" s="163"/>
+      <c r="D32" s="162"/>
       <c r="E32" s="113"/>
     </row>
-    <row r="33" spans="1:8" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5"/>
-      <c r="D33" s="163"/>
+      <c r="D33" s="162"/>
       <c r="E33" s="113"/>
     </row>
-    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5"/>
-      <c r="D34" s="163"/>
+      <c r="D34" s="162"/>
       <c r="E34" s="113"/>
     </row>
-    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5"/>
-      <c r="D35" s="163">
+      <c r="D35" s="162">
         <v>0</v>
       </c>
       <c r="E35" s="113"/>
     </row>
-    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="5"/>
       <c r="B36" s="5"/>
       <c r="C36" s="5"/>
-      <c r="D36" s="163"/>
+      <c r="D36" s="162"/>
       <c r="E36" s="113"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="57" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B37" s="57"/>
       <c r="C37" s="57"/>
-      <c r="D37" s="164">
+      <c r="D37" s="163">
         <f>SUM(D29:D36)</f>
         <v>1643368</v>
       </c>
-      <c r="E37" s="162"/>
-      <c r="G37" s="209">
+      <c r="E37" s="161"/>
+      <c r="G37" s="205">
         <f>G28-G29</f>
         <v>1523284</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="28" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B38" s="28"/>
       <c r="C38" s="28"/>
-      <c r="D38" s="165"/>
-      <c r="E38" s="166">
+      <c r="D38" s="164"/>
+      <c r="E38" s="165">
         <f>D28+D37</f>
         <v>3523284</v>
       </c>
       <c r="F38" s="20"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="34" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B39" s="34"/>
       <c r="C39" s="34"/>
-      <c r="D39" s="167"/>
-      <c r="E39" s="168"/>
-    </row>
-    <row r="40" spans="1:8" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="221" t="s">
-        <v>215</v>
-      </c>
-      <c r="B40" s="214"/>
-      <c r="C40" s="190"/>
-      <c r="D40" s="160">
-        <v>56000</v>
-      </c>
-      <c r="E40" s="189" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="213" t="s">
+      <c r="D39" s="166"/>
+      <c r="E39" s="167"/>
+    </row>
+    <row r="40" spans="1:8" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="215" t="s">
         <v>208</v>
       </c>
-      <c r="B41" s="214"/>
+      <c r="B40" s="209"/>
+      <c r="C40" s="187"/>
+      <c r="D40" s="236">
+        <v>60000</v>
+      </c>
+      <c r="E40" s="186" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="237" t="s">
+        <v>231</v>
+      </c>
+      <c r="B41" s="238"/>
       <c r="C41" s="52"/>
-      <c r="D41" s="160">
+      <c r="D41" s="236">
         <v>249000</v>
       </c>
-      <c r="E41" s="189" t="s">
-        <v>210</v>
-      </c>
-      <c r="H41" s="139"/>
-    </row>
-    <row r="42" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E41" s="186" t="s">
+        <v>232</v>
+      </c>
+      <c r="H41" s="138"/>
+    </row>
+    <row r="42" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B42" s="28"/>
       <c r="C42" s="28"/>
-      <c r="D42" s="169"/>
-      <c r="E42" s="170">
+      <c r="D42" s="168"/>
+      <c r="E42" s="169">
         <f>SUM(D40:D41)</f>
-        <v>305000</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+        <v>309000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="34" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B43" s="28"/>
       <c r="C43" s="28"/>
-      <c r="D43" s="171"/>
-      <c r="E43" s="172"/>
-    </row>
-    <row r="44" spans="1:8" s="37" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="215" t="s">
+      <c r="D43" s="170"/>
+      <c r="E43" s="171"/>
+    </row>
+    <row r="44" spans="1:8" s="37" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="208" t="s">
+        <v>24</v>
+      </c>
+      <c r="B44" s="209"/>
+      <c r="C44" s="54"/>
+      <c r="D44" s="195">
+        <v>120977</v>
+      </c>
+      <c r="E44" s="172" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="208"/>
+      <c r="B45" s="209"/>
+      <c r="C45" s="54"/>
+      <c r="D45" s="173"/>
+      <c r="E45" s="172"/>
+    </row>
+    <row r="46" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="28" t="s">
         <v>25</v>
-      </c>
-      <c r="B44" s="214"/>
-      <c r="C44" s="54"/>
-      <c r="D44" s="198">
-        <v>120977</v>
-      </c>
-      <c r="E44" s="173" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="215"/>
-      <c r="B45" s="214"/>
-      <c r="C45" s="54"/>
-      <c r="D45" s="174"/>
-      <c r="E45" s="173"/>
-    </row>
-    <row r="46" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="28" t="s">
-        <v>26</v>
       </c>
       <c r="B46" s="28"/>
       <c r="C46" s="28"/>
-      <c r="D46" s="169"/>
+      <c r="D46" s="168"/>
       <c r="E46" s="114">
         <f>SUM(D44:D45)</f>
         <v>120977</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="B47" s="155"/>
+      <c r="C47" s="155"/>
+      <c r="D47" s="174"/>
+      <c r="E47" s="175"/>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A48" s="5" t="s">
         <v>27</v>
-      </c>
-      <c r="B47" s="156"/>
-      <c r="C47" s="156"/>
-      <c r="D47" s="175"/>
-      <c r="E47" s="176"/>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="5" t="s">
-        <v>28</v>
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="52"/>
-      <c r="D48" s="199">
-        <v>1688376.15</v>
-      </c>
-      <c r="E48" s="177" t="s">
-        <v>213</v>
-      </c>
-      <c r="G48" s="139"/>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D48" s="241">
+        <v>2581613.04</v>
+      </c>
+      <c r="E48" s="176" t="s">
+        <v>207</v>
+      </c>
+      <c r="G48" s="138"/>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
-        <v>207</v>
+        <v>229</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C49" s="5"/>
-      <c r="D49" s="174">
-        <v>132484</v>
-      </c>
-      <c r="E49" s="178" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D49" s="190">
+        <v>202628.43</v>
+      </c>
+      <c r="E49" s="177" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="str">
         <f>A49</f>
-        <v>Sindicatos mes de JUNIO</v>
+        <v>Sindicatos mes de JULIO</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C50" s="5"/>
-      <c r="D50" s="174">
-        <v>239365.78</v>
-      </c>
-      <c r="E50" s="178" t="str">
+      <c r="D50" s="190">
+        <v>365477.51</v>
+      </c>
+      <c r="E50" s="177" t="str">
         <f>E49</f>
-        <v>Debito 12/06</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+        <v>Debito 14/07</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="str">
         <f>A50</f>
-        <v>Sindicatos mes de JUNIO</v>
+        <v>Sindicatos mes de JULIO</v>
       </c>
       <c r="B51" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C51" s="5"/>
+      <c r="D51" s="190">
+        <v>22514.27</v>
+      </c>
+      <c r="E51" s="178" t="str">
+        <f>E50</f>
+        <v>Debito 14/07</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="C51" s="5"/>
-      <c r="D51" s="174">
-        <v>14720.45</v>
-      </c>
-      <c r="E51" s="179" t="str">
-        <f>E50</f>
-        <v>Debito 12/06</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="B52" s="156"/>
-      <c r="C52" s="156"/>
-      <c r="D52" s="180"/>
+      <c r="B52" s="155"/>
+      <c r="C52" s="155"/>
+      <c r="D52" s="179"/>
       <c r="E52" s="114">
         <f>SUM(D48:D51)</f>
-        <v>2074946.38</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+        <v>3172233.2500000005</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="B53" s="155"/>
+      <c r="C53" s="155"/>
+      <c r="D53" s="174"/>
+      <c r="E53" s="175"/>
+    </row>
+    <row r="54" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="5" t="s">
         <v>33</v>
-      </c>
-      <c r="B53" s="156"/>
-      <c r="C53" s="156"/>
-      <c r="D53" s="175"/>
-      <c r="E53" s="176"/>
-    </row>
-    <row r="54" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="5" t="s">
-        <v>34</v>
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
-      <c r="D54" s="174">
-        <v>907716.3</v>
-      </c>
-      <c r="E54" s="187" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D54" s="190">
+        <v>918866.69</v>
+      </c>
+      <c r="E54" s="184" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B55" s="190"/>
+      <c r="C55" s="5"/>
+      <c r="D55" s="190">
+        <v>23882.62</v>
+      </c>
+      <c r="E55" s="184" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A56" s="5" t="s">
         <v>35</v>
-      </c>
-      <c r="B55" s="193"/>
-      <c r="C55" s="5"/>
-      <c r="D55" s="174">
-        <v>11144.38</v>
-      </c>
-      <c r="E55" s="187" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="5" t="s">
-        <v>36</v>
       </c>
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
-      <c r="D56" s="174">
-        <v>13452.23</v>
-      </c>
-      <c r="E56" s="181" t="str">
+      <c r="D56" s="190">
+        <v>14748.22</v>
+      </c>
+      <c r="E56" s="180" t="str">
         <f>E55</f>
-        <v>Efectivo 13/06</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+        <v>Transf 07/07</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B57" s="193"/>
+        <v>36</v>
+      </c>
+      <c r="B57" s="190"/>
       <c r="C57" s="5"/>
-      <c r="D57" s="174">
-        <v>22454.93</v>
-      </c>
-      <c r="E57" s="187" t="str">
+      <c r="D57" s="190">
+        <v>12392.89</v>
+      </c>
+      <c r="E57" s="184" t="str">
         <f>E56</f>
-        <v>Efectivo 13/06</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+        <v>Transf 07/07</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" s="5" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="B58" s="5"/>
       <c r="C58" s="5"/>
-      <c r="D58" s="174">
+      <c r="D58" s="173">
         <f>4753.74</f>
         <v>4753.74</v>
       </c>
-      <c r="E58" s="194" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E58" s="191" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" s="5" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
-      <c r="D59" s="174">
-        <v>5015.88</v>
-      </c>
-      <c r="E59" s="194" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D59" s="190">
+        <v>9890.09</v>
+      </c>
+      <c r="E59" s="191" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="5" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
-      <c r="D60" s="174">
-        <v>5348.66</v>
-      </c>
-      <c r="E60" s="194" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D60" s="190">
+        <v>1474687.08</v>
+      </c>
+      <c r="E60" s="191" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
-      <c r="D61" s="174">
+      <c r="D61" s="173">
         <v>571919</v>
       </c>
-      <c r="E61" s="181" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E61" s="180" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B62" s="5"/>
       <c r="C62" s="5"/>
-      <c r="D62" s="174">
+      <c r="D62" s="173">
         <v>22603.51</v>
       </c>
-      <c r="E62" s="194" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" s="215" t="s">
+      <c r="E62" s="191" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A63" s="208" t="s">
+        <v>38</v>
+      </c>
+      <c r="B63" s="209"/>
+      <c r="C63" s="5"/>
+      <c r="D63" s="190">
+        <v>2168902.4500000002</v>
+      </c>
+      <c r="E63" s="191" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="208"/>
+      <c r="B64" s="209"/>
+      <c r="C64" s="156"/>
+      <c r="D64" s="213"/>
+      <c r="E64" s="214"/>
+    </row>
+    <row r="65" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="28" t="s">
         <v>39</v>
-      </c>
-      <c r="B63" s="214"/>
-      <c r="C63" s="5"/>
-      <c r="D63" s="174">
-        <v>2302294.3199999998</v>
-      </c>
-      <c r="E63" s="194" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="215"/>
-      <c r="B64" s="214"/>
-      <c r="C64" s="157"/>
-      <c r="D64" s="219"/>
-      <c r="E64" s="220"/>
-    </row>
-    <row r="65" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="28" t="s">
-        <v>40</v>
       </c>
       <c r="B65" s="28"/>
       <c r="C65" s="28"/>
-      <c r="D65" s="169"/>
+      <c r="D65" s="168"/>
       <c r="E65" s="114">
         <f>SUM(D54:D64)</f>
-        <v>3866702.95</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>5222646.29</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="34" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B66" s="28"/>
       <c r="C66" s="28"/>
-      <c r="D66" s="169"/>
-      <c r="E66" s="183"/>
-    </row>
-    <row r="67" spans="1:10" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="213" t="s">
-        <v>232</v>
-      </c>
-      <c r="B67" s="214"/>
+      <c r="D66" s="168"/>
+      <c r="E66" s="181"/>
+    </row>
+    <row r="67" spans="1:10" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="212" t="s">
+        <v>230</v>
+      </c>
+      <c r="B67" s="209"/>
       <c r="C67" s="55"/>
-      <c r="D67" s="174">
+      <c r="D67" s="173">
         <v>96800</v>
       </c>
-      <c r="E67" s="187" t="s">
+      <c r="E67" s="184" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A68" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B68" s="157"/>
+      <c r="C68" s="5"/>
+      <c r="D68" s="190">
+        <v>55700</v>
+      </c>
+      <c r="E68" s="184" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A68" s="5" t="s">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A69" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B68" s="158"/>
-      <c r="C68" s="5"/>
-      <c r="D68" s="174">
-        <v>54600</v>
-      </c>
-      <c r="E68" s="187" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A69" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B69" s="158"/>
+      <c r="B69" s="157"/>
       <c r="C69" s="5"/>
-      <c r="D69" s="174">
-        <v>120000</v>
-      </c>
-      <c r="E69" s="188" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10" ht="69" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="215" t="s">
-        <v>212</v>
-      </c>
-      <c r="B70" s="214"/>
+      <c r="D69" s="190">
+        <v>135000</v>
+      </c>
+      <c r="E69" s="185" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" ht="69" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="237" t="s">
+        <v>206</v>
+      </c>
+      <c r="B70" s="238"/>
       <c r="C70" s="5"/>
-      <c r="D70" s="174">
-        <v>190500</v>
-      </c>
-      <c r="E70" s="188" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="213" t="s">
-        <v>231</v>
-      </c>
-      <c r="B71" s="216"/>
+      <c r="D70" s="190">
+        <v>770000</v>
+      </c>
+      <c r="E70" s="185" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="237" t="s">
+        <v>242</v>
+      </c>
+      <c r="B71" s="238"/>
       <c r="C71" s="5"/>
-      <c r="D71" s="174">
-        <v>-240000</v>
-      </c>
-      <c r="E71" s="188"/>
-    </row>
-    <row r="72" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="213" t="s">
-        <v>229</v>
-      </c>
-      <c r="B72" s="216"/>
+      <c r="D71" s="190">
+        <v>40020</v>
+      </c>
+      <c r="E71" s="185" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="212" t="s">
+        <v>217</v>
+      </c>
+      <c r="B72" s="217"/>
       <c r="C72" s="5"/>
       <c r="D72" s="117">
         <v>450000</v>
       </c>
-      <c r="E72" s="182" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="213" t="s">
-        <v>217</v>
-      </c>
-      <c r="B73" s="214"/>
+      <c r="E72" s="185" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="212" t="s">
+        <v>237</v>
+      </c>
+      <c r="B73" s="209"/>
       <c r="C73" s="5"/>
-      <c r="D73" s="117">
-        <v>85000</v>
-      </c>
-      <c r="E73" s="182" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="213" t="s">
-        <v>219</v>
-      </c>
-      <c r="B74" s="216"/>
+      <c r="D73" s="143">
+        <v>150000</v>
+      </c>
+      <c r="E73" s="185" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="240" t="s">
+        <v>240</v>
+      </c>
+      <c r="B74" s="157"/>
       <c r="C74" s="5"/>
-      <c r="D74" s="117">
-        <f>178500</f>
-        <v>178500</v>
-      </c>
-      <c r="E74" s="182" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10" ht="22.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="215"/>
-      <c r="B75" s="214"/>
+      <c r="D74" s="143">
+        <v>643568</v>
+      </c>
+      <c r="E74" s="185" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="240"/>
+      <c r="B75" s="157"/>
       <c r="C75" s="5"/>
-      <c r="D75" s="117"/>
-      <c r="E75" s="184"/>
-      <c r="I75" s="215"/>
-      <c r="J75" s="214"/>
-    </row>
-    <row r="76" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="28" t="s">
+      <c r="D75" s="143">
+        <v>770000</v>
+      </c>
+      <c r="E75" s="185" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="212" t="s">
+        <v>239</v>
+      </c>
+      <c r="B76" s="217"/>
+      <c r="C76" s="5"/>
+      <c r="D76" s="143">
+        <f>65050+57650</f>
+        <v>122700</v>
+      </c>
+      <c r="E76" s="185" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="208" t="s">
+        <v>245</v>
+      </c>
+      <c r="B77" s="209"/>
+      <c r="C77" s="5"/>
+      <c r="D77" s="143">
+        <v>8000</v>
+      </c>
+      <c r="E77" s="185" t="s">
+        <v>243</v>
+      </c>
+      <c r="I77" s="208"/>
+      <c r="J77" s="209"/>
+    </row>
+    <row r="78" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A78" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="B78" s="34"/>
+      <c r="C78" s="34"/>
+      <c r="D78" s="33"/>
+      <c r="E78" s="182">
+        <f>SUM(D67:D77)</f>
+        <v>3241788</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A79" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="B76" s="34"/>
-      <c r="C76" s="34"/>
-      <c r="D76" s="33"/>
-      <c r="E76" s="185">
-        <f>SUM(D67:D75)</f>
-        <v>935400</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="34" t="s">
-        <v>45</v>
-      </c>
-      <c r="B77" s="68"/>
-      <c r="C77" s="28"/>
-      <c r="D77" s="165"/>
-      <c r="E77" s="183"/>
-    </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A78" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B78" s="5"/>
-      <c r="C78" s="5"/>
-      <c r="D78" s="174">
+      <c r="B79" s="68"/>
+      <c r="C79" s="28"/>
+      <c r="D79" s="164"/>
+      <c r="E79" s="181"/>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A80" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B80" s="5"/>
+      <c r="C80" s="5"/>
+      <c r="D80" s="173">
         <f>117877.65+2102.91+12028.52</f>
         <v>132009.07999999999</v>
       </c>
-      <c r="E78" s="186"/>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A79" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="B79" s="5"/>
-      <c r="C79" s="5"/>
-      <c r="D79" s="174"/>
-      <c r="E79" s="119"/>
-      <c r="G79" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="51" t="s">
-        <v>23</v>
-      </c>
-      <c r="B80" s="51"/>
-      <c r="C80" s="51"/>
-      <c r="D80" s="120"/>
-      <c r="E80" s="114">
-        <f>SUM(D78:D79)</f>
-        <v>132009.07999999999</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="5"/>
+      <c r="E80" s="183"/>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A81" s="5" t="s">
+        <v>218</v>
+      </c>
       <c r="B81" s="5"/>
       <c r="C81" s="5"/>
-      <c r="D81" s="113"/>
-      <c r="E81" s="121"/>
-    </row>
-    <row r="82" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="29" t="s">
-        <v>240</v>
-      </c>
-      <c r="B82" s="29"/>
-      <c r="C82" s="29"/>
-      <c r="D82" s="122"/>
-      <c r="E82" s="123">
+      <c r="D81" s="173"/>
+      <c r="E81" s="119"/>
+      <c r="G81" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A82" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="B82" s="51"/>
+      <c r="C82" s="51"/>
+      <c r="D82" s="120"/>
+      <c r="E82" s="114">
+        <f>SUM(D80:D81)</f>
+        <v>132009.07999999999</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A83" s="5"/>
+      <c r="B83" s="5"/>
+      <c r="C83" s="5"/>
+      <c r="D83" s="113"/>
+      <c r="E83" s="121"/>
+    </row>
+    <row r="84" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A84" s="29" t="s">
+        <v>225</v>
+      </c>
+      <c r="B84" s="29"/>
+      <c r="C84" s="29"/>
+      <c r="D84" s="122"/>
+      <c r="E84" s="123">
         <v>1418512.03</v>
       </c>
     </row>
-    <row r="83" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="1"/>
-      <c r="D83" s="124"/>
-      <c r="E83" s="125"/>
-      <c r="F83" s="43"/>
-    </row>
-    <row r="84" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="3" t="s">
+    <row r="85" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A85" s="1"/>
+      <c r="D85" s="124"/>
+      <c r="E85" s="125"/>
+      <c r="F85" s="43"/>
+    </row>
+    <row r="86" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A86" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B86" s="10"/>
+      <c r="C86" s="4"/>
+      <c r="D86" s="126"/>
+      <c r="E86" s="239">
+        <f>(SUM(E31:E84))</f>
+        <v>17140449.649999999</v>
+      </c>
+      <c r="F86" s="153"/>
+      <c r="G86" s="43"/>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D87" s="124"/>
+      <c r="E87" s="124"/>
+      <c r="G87" s="153">
+        <f>G86-E86</f>
+        <v>-17140449.649999999</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D88" s="124"/>
+      <c r="E88" s="124"/>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A89" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="B84" s="10"/>
-      <c r="C84" s="4"/>
-      <c r="D84" s="126"/>
-      <c r="E84" s="127">
-        <f>(SUM(E31:E82))</f>
-        <v>12376831.439999999</v>
-      </c>
-      <c r="F84" s="154"/>
-      <c r="G84" s="43"/>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D85" s="124"/>
-      <c r="E85" s="124"/>
-      <c r="G85" s="154">
-        <f>G84-E84</f>
-        <v>-12376831.439999999</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D86" s="124"/>
-      <c r="E86" s="124"/>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A87" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="B87" s="12"/>
-      <c r="C87" s="13"/>
-      <c r="D87" s="128"/>
-      <c r="E87" s="129"/>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88" s="215"/>
-      <c r="B88" s="214"/>
-      <c r="C88" s="5"/>
-      <c r="D88" s="144"/>
-      <c r="E88" s="115"/>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89" s="215"/>
-      <c r="B89" s="214"/>
-      <c r="C89" s="5"/>
-      <c r="D89" s="117"/>
-      <c r="E89" s="115"/>
-    </row>
-    <row r="90" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="213"/>
-      <c r="B90" s="214"/>
+      <c r="B89" s="12"/>
+      <c r="C89" s="13"/>
+      <c r="D89" s="127"/>
+      <c r="E89" s="128"/>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A90" s="208"/>
+      <c r="B90" s="209"/>
       <c r="C90" s="5"/>
-      <c r="D90" s="117"/>
+      <c r="D90" s="143"/>
       <c r="E90" s="115"/>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" s="116"/>
-      <c r="B91" s="118"/>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A91" s="208"/>
+      <c r="B91" s="209"/>
       <c r="C91" s="5"/>
       <c r="D91" s="117"/>
       <c r="E91" s="115"/>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92" s="49"/>
-      <c r="B92" s="48"/>
-      <c r="C92" s="48"/>
-      <c r="D92" s="58"/>
-      <c r="E92" s="58">
-        <f>SUM(D88:D91)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="29" t="s">
+    <row r="92" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="212"/>
+      <c r="B92" s="209"/>
+      <c r="C92" s="5"/>
+      <c r="D92" s="117"/>
+      <c r="E92" s="115"/>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A93" s="116"/>
+      <c r="B93" s="118"/>
+      <c r="C93" s="5"/>
+      <c r="D93" s="117"/>
+      <c r="E93" s="115"/>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A94" s="49"/>
+      <c r="B94" s="48"/>
+      <c r="C94" s="48"/>
+      <c r="D94" s="58"/>
+      <c r="E94" s="58">
+        <f>SUM(D90:D93)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="96" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="97" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A97" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="B97" s="29"/>
+      <c r="C97" s="29"/>
+      <c r="D97" s="30"/>
+      <c r="E97" s="112"/>
+    </row>
+    <row r="98" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="99" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A99" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B95" s="29"/>
-      <c r="C95" s="29"/>
-      <c r="D95" s="30"/>
-      <c r="E95" s="112"/>
-    </row>
-    <row r="96" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="97" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="3" t="s">
+      <c r="B99" s="10"/>
+      <c r="C99" s="4"/>
+      <c r="D99" s="4"/>
+      <c r="E99" s="69">
+        <f>E94+E97</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="101" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A101" s="109" t="s">
         <v>49</v>
       </c>
-      <c r="B97" s="10"/>
-      <c r="C97" s="4"/>
-      <c r="D97" s="4"/>
-      <c r="E97" s="69">
-        <f>E92+E95</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="99" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="109" t="s">
+      <c r="B101" s="110">
+        <f>E86</f>
+        <v>17140449.649999999</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A102" s="109" t="s">
         <v>50</v>
       </c>
-      <c r="B99" s="110">
-        <f>E84</f>
-        <v>12376831.439999999</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="109" t="s">
+      <c r="B102" s="110">
+        <f>E86-E84</f>
+        <v>15721937.619999999</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A103" s="109" t="s">
         <v>51</v>
       </c>
-      <c r="B100" s="110">
-        <f>E84-E82</f>
-        <v>10958319.41</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="109" t="s">
+      <c r="B103" s="110">
+        <f>E99-E97</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A104" s="109" t="s">
         <v>52</v>
       </c>
-      <c r="B101" s="110">
-        <f>E97-E95</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="109" t="s">
+      <c r="B104" s="110">
+        <f>E99</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" ht="34.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="106" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="218"/>
+      <c r="B106" s="211"/>
+      <c r="C106" s="211"/>
+      <c r="D106" s="211"/>
+      <c r="E106" s="211"/>
+    </row>
+    <row r="107" spans="1:5" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="211"/>
+      <c r="B107" s="211"/>
+      <c r="C107" s="211"/>
+      <c r="D107" s="211"/>
+      <c r="E107" s="211"/>
+    </row>
+    <row r="108" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="211"/>
+      <c r="B108" s="211"/>
+      <c r="C108" s="211"/>
+      <c r="D108" s="211"/>
+      <c r="E108" s="211"/>
+    </row>
+    <row r="110" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A110" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="B102" s="110">
-        <f>E97</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5" ht="34.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="104" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="211"/>
-      <c r="B104" s="212"/>
-      <c r="C104" s="212"/>
-      <c r="D104" s="212"/>
-      <c r="E104" s="212"/>
-    </row>
-    <row r="105" spans="1:5" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="212"/>
-      <c r="B105" s="212"/>
-      <c r="C105" s="212"/>
-      <c r="D105" s="212"/>
-      <c r="E105" s="212"/>
-    </row>
-    <row r="106" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="212"/>
-      <c r="B106" s="212"/>
-      <c r="C106" s="212"/>
-      <c r="D106" s="212"/>
-      <c r="E106" s="212"/>
-    </row>
-    <row r="108" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="21" t="s">
+      <c r="B110" s="139"/>
+      <c r="C110" s="22"/>
+    </row>
+    <row r="111" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A111" s="32"/>
+      <c r="B111" s="59">
+        <v>0</v>
+      </c>
+      <c r="C111" s="24"/>
+    </row>
+    <row r="112" spans="1:5" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A112" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="B108" s="140"/>
-      <c r="C108" s="22"/>
-    </row>
-    <row r="109" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="32"/>
-      <c r="B109" s="59">
-        <v>0</v>
-      </c>
-      <c r="C109" s="24"/>
-    </row>
-    <row r="110" spans="1:5" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="23" t="s">
-        <v>55</v>
-      </c>
-      <c r="B110" s="39">
+      <c r="B112" s="39">
         <f>PRORRATEO!I81</f>
         <v>12230220.440623038</v>
       </c>
-      <c r="C110" s="22"/>
-    </row>
-    <row r="111" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="23"/>
-      <c r="B111" s="39">
-        <v>0</v>
-      </c>
-      <c r="C111" s="22"/>
-    </row>
-    <row r="112" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="23" t="s">
+      <c r="C112" s="22"/>
+    </row>
+    <row r="113" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A113" s="23"/>
+      <c r="B113" s="39">
+        <v>0</v>
+      </c>
+      <c r="C113" s="22"/>
+    </row>
+    <row r="114" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A114" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="B114" s="119">
+        <f>B139</f>
+        <v>0</v>
+      </c>
+      <c r="C114" s="22"/>
+    </row>
+    <row r="115" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A115" s="26"/>
+      <c r="B115" s="47"/>
+      <c r="C115" s="22"/>
+    </row>
+    <row r="116" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A116" s="133" t="s">
         <v>56</v>
       </c>
-      <c r="B112" s="119">
-        <f>B137</f>
-        <v>0</v>
-      </c>
-      <c r="C112" s="22"/>
-    </row>
-    <row r="113" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="26"/>
-      <c r="B113" s="47"/>
-      <c r="C113" s="22"/>
-    </row>
-    <row r="114" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="134" t="s">
+      <c r="B116" s="47"/>
+      <c r="C116" s="22"/>
+    </row>
+    <row r="117" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="38" t="s">
         <v>57</v>
       </c>
-      <c r="B114" s="47"/>
-      <c r="C114" s="22"/>
-    </row>
-    <row r="115" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="38" t="s">
+      <c r="B117" s="47">
+        <f>-B102</f>
+        <v>-15721937.619999999</v>
+      </c>
+      <c r="C117" s="22"/>
+    </row>
+    <row r="118" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A118" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="B115" s="47">
-        <f>-B100</f>
-        <v>-10958319.41</v>
-      </c>
-      <c r="C115" s="22"/>
-    </row>
-    <row r="116" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="26" t="s">
+      <c r="B118" s="47">
+        <f>-(B103)</f>
+        <v>0</v>
+      </c>
+      <c r="C118" s="22"/>
+    </row>
+    <row r="119" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A119" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="B119" s="59">
+        <f>SUM(B111:B118)</f>
+        <v>-3491717.1793769617</v>
+      </c>
+      <c r="C119" s="25"/>
+      <c r="D119" s="43"/>
+    </row>
+    <row r="120" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B120" s="40"/>
+      <c r="C120" s="25"/>
+      <c r="D120" s="43"/>
+      <c r="E120" s="140"/>
+      <c r="F120" s="141"/>
+    </row>
+    <row r="121" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B121" s="41"/>
+      <c r="C121" s="25"/>
+    </row>
+    <row r="122" spans="1:6" s="37" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B122" s="40"/>
+      <c r="C122" s="36"/>
+    </row>
+    <row r="123" spans="1:6" s="37" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A123" s="145" t="s">
         <v>59</v>
       </c>
-      <c r="B116" s="47">
-        <f>-(B101)</f>
-        <v>0</v>
-      </c>
-      <c r="C116" s="22"/>
-    </row>
-    <row r="117" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="31" t="s">
-        <v>44</v>
-      </c>
-      <c r="B117" s="59">
-        <f>SUM(B109:B116)</f>
-        <v>1271901.0306230374</v>
-      </c>
-      <c r="C117" s="25"/>
-      <c r="D117" s="43"/>
-    </row>
-    <row r="118" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B118" s="40"/>
-      <c r="C118" s="25"/>
-      <c r="D118" s="43"/>
-      <c r="E118" s="141"/>
-      <c r="F118" s="142"/>
-    </row>
-    <row r="119" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B119" s="41"/>
-      <c r="C119" s="25"/>
-    </row>
-    <row r="120" spans="1:6" s="37" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B120" s="40"/>
-      <c r="C120" s="36"/>
-    </row>
-    <row r="121" spans="1:6" s="37" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="146" t="s">
+      <c r="B123" s="146">
+        <v>-334887.05000000633</v>
+      </c>
+      <c r="C123" s="36"/>
+      <c r="D123" s="46"/>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A124" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="B121" s="147">
-        <v>-334887.05000000633</v>
-      </c>
-      <c r="C121" s="36"/>
-      <c r="D121" s="46"/>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A122" s="54" t="s">
+      <c r="B124" s="150">
+        <f>-B102</f>
+        <v>-15721937.619999999</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A125" s="54" t="s">
         <v>61</v>
       </c>
-      <c r="B122" s="151">
-        <f>-B100</f>
-        <v>-10958319.41</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A123" s="54" t="s">
+      <c r="B125" s="150">
+        <f>-B103</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A126" s="54" t="s">
         <v>62</v>
       </c>
-      <c r="B123" s="151">
-        <f>-B101</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A124" s="54" t="s">
+      <c r="B126" s="150">
+        <f>B139</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A127" s="54" t="s">
+        <v>224</v>
+      </c>
+      <c r="B127" s="206">
+        <v>-300521.3</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A128" s="54" t="s">
+        <v>223</v>
+      </c>
+      <c r="B128" s="204">
+        <v>-184089</v>
+      </c>
+    </row>
+    <row r="129" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A129" s="54" t="s">
         <v>63</v>
       </c>
-      <c r="B124" s="151">
-        <f>B137</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A125" s="54" t="s">
-        <v>239</v>
-      </c>
-      <c r="B125" s="210">
-        <v>-300521.3</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A126" s="54" t="s">
-        <v>238</v>
-      </c>
-      <c r="B126" s="208">
-        <v>-184089</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A127" s="54" t="s">
-        <v>64</v>
-      </c>
-      <c r="B127" s="152">
+      <c r="B129" s="151">
         <f>PRORRATEO!I81</f>
         <v>12230220.440623038</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A128" s="54" t="s">
-        <v>228</v>
-      </c>
-      <c r="B128" s="196">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A130" s="54" t="s">
+        <v>216</v>
+      </c>
+      <c r="B130" s="193">
         <v>-18500</v>
       </c>
     </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A129" s="153" t="s">
-        <v>65</v>
-      </c>
-      <c r="B129" s="195">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A131" s="152" t="s">
+        <v>64</v>
+      </c>
+      <c r="B131" s="192">
         <f>-16168-5521</f>
         <v>-21689</v>
       </c>
     </row>
-    <row r="130" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="149" t="s">
+    <row r="132" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A132" s="148" t="s">
+        <v>65</v>
+      </c>
+      <c r="B132" s="149">
+        <f>SUM(B123:C131)</f>
+        <v>-4351403.5293769687</v>
+      </c>
+    </row>
+    <row r="133" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A133" s="147"/>
+      <c r="B133" s="147"/>
+    </row>
+    <row r="134" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="135" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A135" s="219" t="s">
         <v>66</v>
       </c>
-      <c r="B130" s="150">
-        <f>SUM(B121:C129)</f>
-        <v>412214.68062303029</v>
-      </c>
-    </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A131" s="148"/>
-      <c r="B131" s="148"/>
-    </row>
-    <row r="132" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A133" s="217" t="s">
-        <v>67</v>
-      </c>
-      <c r="B133" s="212"/>
-      <c r="C133" s="212"/>
-    </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A134" s="212"/>
-      <c r="B134" s="212"/>
-      <c r="C134" s="212"/>
-    </row>
-    <row r="135" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="131"/>
-      <c r="B135" s="35"/>
-      <c r="C135" s="35">
+      <c r="B135" s="211"/>
+      <c r="C135" s="211"/>
+    </row>
+    <row r="136" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A136" s="211"/>
+      <c r="B136" s="211"/>
+      <c r="C136" s="211"/>
+    </row>
+    <row r="137" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A137" s="130"/>
+      <c r="B137" s="35"/>
+      <c r="C137" s="35">
         <v>40000</v>
       </c>
     </row>
-    <row r="136" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="131"/>
-      <c r="B136" s="133"/>
-      <c r="C136" s="40"/>
-    </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A137" s="44" t="s">
-        <v>44</v>
-      </c>
-      <c r="B137" s="132">
-        <f>SUM(B135:B136)</f>
-        <v>0</v>
-      </c>
-      <c r="C137" s="45"/>
-    </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="M138" s="8"/>
-    </row>
-    <row r="139" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="211"/>
-      <c r="B139" s="212"/>
-      <c r="C139" s="212"/>
-      <c r="D139" s="212"/>
-      <c r="E139" s="212"/>
-    </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A140" s="212"/>
-      <c r="B140" s="212"/>
-      <c r="C140" s="212"/>
-      <c r="D140" s="212"/>
-      <c r="E140" s="212"/>
-    </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A141" s="212"/>
-      <c r="B141" s="212"/>
-      <c r="C141" s="212"/>
-      <c r="D141" s="212"/>
-      <c r="E141" s="212"/>
-    </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A142" s="212"/>
-      <c r="B142" s="212"/>
-      <c r="C142" s="212"/>
-      <c r="D142" s="212"/>
-      <c r="E142" s="212"/>
+    <row r="138" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A138" s="130"/>
+      <c r="B138" s="132"/>
+      <c r="C138" s="40"/>
+    </row>
+    <row r="139" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A139" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="B139" s="131">
+        <f>SUM(B137:B138)</f>
+        <v>0</v>
+      </c>
+      <c r="C139" s="45"/>
+    </row>
+    <row r="140" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M140" s="8"/>
+    </row>
+    <row r="141" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A141" s="218"/>
+      <c r="B141" s="211"/>
+      <c r="C141" s="211"/>
+      <c r="D141" s="211"/>
+      <c r="E141" s="211"/>
+    </row>
+    <row r="142" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A142" s="211"/>
+      <c r="B142" s="211"/>
+      <c r="C142" s="211"/>
+      <c r="D142" s="211"/>
+      <c r="E142" s="211"/>
+    </row>
+    <row r="143" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A143" s="211"/>
+      <c r="B143" s="211"/>
+      <c r="C143" s="211"/>
+      <c r="D143" s="211"/>
+      <c r="E143" s="211"/>
+    </row>
+    <row r="144" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A144" s="211"/>
+      <c r="B144" s="211"/>
+      <c r="C144" s="211"/>
+      <c r="D144" s="211"/>
+      <c r="E144" s="211"/>
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="I75:J75"/>
+    <mergeCell ref="A141:E144"/>
+    <mergeCell ref="A106:E108"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="A67:B67"/>
+    <mergeCell ref="A91:B91"/>
+    <mergeCell ref="A90:B90"/>
+    <mergeCell ref="A135:C136"/>
+    <mergeCell ref="I77:J77"/>
     <mergeCell ref="B9:C11"/>
     <mergeCell ref="A73:B73"/>
-    <mergeCell ref="A75:B75"/>
+    <mergeCell ref="A77:B77"/>
     <mergeCell ref="D64:E64"/>
     <mergeCell ref="A44:B44"/>
     <mergeCell ref="A40:B40"/>
     <mergeCell ref="A14:E17"/>
     <mergeCell ref="A41:B41"/>
     <mergeCell ref="A72:B72"/>
-    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="A76:B76"/>
     <mergeCell ref="A70:B70"/>
     <mergeCell ref="A45:B45"/>
     <mergeCell ref="A63:B63"/>
-    <mergeCell ref="A139:E142"/>
-    <mergeCell ref="A104:E106"/>
-    <mergeCell ref="A90:B90"/>
-    <mergeCell ref="A64:B64"/>
-    <mergeCell ref="A71:B71"/>
-    <mergeCell ref="A67:B67"/>
-    <mergeCell ref="A89:B89"/>
-    <mergeCell ref="A88:B88"/>
-    <mergeCell ref="A133:C134"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3545,52 +3595,52 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:U89"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.28515625" customWidth="1"/>
-    <col min="3" max="3" width="3.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.28515625" customWidth="1"/>
-    <col min="5" max="5" width="17.7109375" customWidth="1"/>
-    <col min="6" max="6" width="13.85546875" customWidth="1"/>
-    <col min="7" max="7" width="5.42578125" customWidth="1"/>
-    <col min="8" max="8" width="14.140625" customWidth="1"/>
-    <col min="9" max="9" width="11.5703125" customWidth="1"/>
-    <col min="10" max="10" width="7.7109375" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="9.7109375" customWidth="1"/>
-    <col min="12" max="12" width="8.140625" customWidth="1"/>
-    <col min="13" max="13" width="0.140625" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="10.5703125" customWidth="1"/>
-    <col min="15" max="15" width="8.42578125" customWidth="1"/>
-    <col min="16" max="16" width="13.5703125" customWidth="1"/>
-    <col min="17" max="17" width="0.42578125" hidden="1" customWidth="1"/>
-    <col min="18" max="18" width="12.140625" customWidth="1"/>
-    <col min="19" max="19" width="0.140625" customWidth="1"/>
+    <col min="1" max="1" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.33203125" customWidth="1"/>
+    <col min="3" max="3" width="3.6640625" customWidth="1"/>
+    <col min="4" max="4" width="4.33203125" customWidth="1"/>
+    <col min="5" max="5" width="17.6640625" customWidth="1"/>
+    <col min="6" max="6" width="13.88671875" customWidth="1"/>
+    <col min="7" max="7" width="5.44140625" customWidth="1"/>
+    <col min="8" max="8" width="14.109375" customWidth="1"/>
+    <col min="9" max="9" width="11.5546875" customWidth="1"/>
+    <col min="10" max="10" width="7.6640625" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="9.6640625" customWidth="1"/>
+    <col min="12" max="12" width="8.109375" customWidth="1"/>
+    <col min="13" max="13" width="0.109375" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="10.5546875" customWidth="1"/>
+    <col min="15" max="15" width="8.44140625" customWidth="1"/>
+    <col min="16" max="16" width="13.5546875" customWidth="1"/>
+    <col min="17" max="17" width="0.44140625" hidden="1" customWidth="1"/>
+    <col min="18" max="18" width="12.109375" customWidth="1"/>
+    <col min="19" max="19" width="0.109375" customWidth="1"/>
     <col min="20" max="20" width="12" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
       <c r="F1" s="6"/>
-      <c r="G1" s="236"/>
-      <c r="H1" s="212"/>
-      <c r="I1" s="212"/>
-      <c r="J1" s="212"/>
-      <c r="K1" s="212"/>
-      <c r="L1" s="212"/>
-      <c r="M1" s="212"/>
-      <c r="N1" s="212"/>
-      <c r="O1" s="212"/>
-      <c r="P1" s="212"/>
+      <c r="G1" s="226"/>
+      <c r="H1" s="211"/>
+      <c r="I1" s="211"/>
+      <c r="J1" s="211"/>
+      <c r="K1" s="211"/>
+      <c r="L1" s="211"/>
+      <c r="M1" s="211"/>
+      <c r="N1" s="211"/>
+      <c r="O1" s="211"/>
+      <c r="P1" s="211"/>
       <c r="Q1" s="6"/>
       <c r="R1" s="6"/>
     </row>
-    <row r="2" spans="1:21" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -3606,19 +3656,19 @@
       <c r="J2" s="6"/>
       <c r="K2" s="6"/>
       <c r="L2" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M2" s="7"/>
       <c r="N2" s="6"/>
       <c r="O2" s="6"/>
-      <c r="P2" s="233">
+      <c r="P2" s="222">
         <v>12376831.439999999</v>
       </c>
-      <c r="Q2" s="212"/>
-      <c r="R2" s="212"/>
+      <c r="Q2" s="211"/>
+      <c r="R2" s="211"/>
       <c r="S2" s="20"/>
     </row>
-    <row r="3" spans="1:21" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -3638,97 +3688,97 @@
       <c r="Q3" s="56"/>
       <c r="R3" s="60"/>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A4" s="228" t="s">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A4" s="233" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4" s="235" t="s">
         <v>69</v>
       </c>
-      <c r="B4" s="230" t="s">
+      <c r="C4" s="134"/>
+      <c r="D4" s="223" t="s">
         <v>70</v>
       </c>
-      <c r="C4" s="135"/>
-      <c r="D4" s="223" t="s">
+      <c r="E4" s="223" t="s">
         <v>71</v>
       </c>
-      <c r="E4" s="223" t="s">
+      <c r="F4" s="232" t="s">
         <v>72</v>
       </c>
-      <c r="F4" s="225" t="s">
+      <c r="G4" s="223" t="s">
         <v>73</v>
       </c>
-      <c r="G4" s="223" t="s">
+      <c r="H4" s="230" t="s">
         <v>74</v>
       </c>
-      <c r="H4" s="227" t="s">
+      <c r="I4" s="223" t="s">
+        <v>54</v>
+      </c>
+      <c r="J4" s="232" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="223" t="s">
-        <v>55</v>
-      </c>
-      <c r="J4" s="225" t="s">
+      <c r="K4" s="234" t="s">
         <v>76</v>
       </c>
-      <c r="K4" s="229" t="s">
+      <c r="L4" s="230" t="s">
         <v>77</v>
       </c>
-      <c r="L4" s="227" t="s">
+      <c r="M4" s="229" t="s">
         <v>78</v>
       </c>
-      <c r="M4" s="238" t="s">
+      <c r="N4" s="230" t="s">
         <v>79</v>
       </c>
-      <c r="N4" s="227" t="s">
+      <c r="O4" s="224" t="s">
         <v>80</v>
       </c>
-      <c r="O4" s="234" t="s">
+      <c r="P4" s="63" t="s">
         <v>81</v>
       </c>
-      <c r="P4" s="63" t="s">
+      <c r="Q4" s="227" t="s">
         <v>82</v>
       </c>
-      <c r="Q4" s="237" t="s">
+      <c r="R4" s="220" t="s">
         <v>83</v>
       </c>
-      <c r="R4" s="232" t="s">
-        <v>84</v>
-      </c>
       <c r="U4" s="43"/>
     </row>
-    <row r="5" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="224"/>
-      <c r="B5" s="231"/>
-      <c r="C5" s="136"/>
-      <c r="D5" s="224"/>
-      <c r="E5" s="224"/>
-      <c r="F5" s="226"/>
-      <c r="G5" s="224"/>
-      <c r="H5" s="226"/>
-      <c r="I5" s="224"/>
-      <c r="J5" s="226"/>
-      <c r="K5" s="226"/>
-      <c r="L5" s="226"/>
-      <c r="M5" s="224"/>
-      <c r="N5" s="226"/>
-      <c r="O5" s="235"/>
+    <row r="5" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="221"/>
+      <c r="B5" s="228"/>
+      <c r="C5" s="135"/>
+      <c r="D5" s="221"/>
+      <c r="E5" s="221"/>
+      <c r="F5" s="231"/>
+      <c r="G5" s="221"/>
+      <c r="H5" s="231"/>
+      <c r="I5" s="221"/>
+      <c r="J5" s="231"/>
+      <c r="K5" s="231"/>
+      <c r="L5" s="231"/>
+      <c r="M5" s="221"/>
+      <c r="N5" s="231"/>
+      <c r="O5" s="225"/>
       <c r="P5" s="61" t="str">
         <f>RESUMEN!B9</f>
-        <v>VTO 14/07</v>
-      </c>
-      <c r="Q5" s="231"/>
-      <c r="R5" s="224"/>
-    </row>
-    <row r="6" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>VTO 14/08</v>
+      </c>
+      <c r="Q5" s="228"/>
+      <c r="R5" s="221"/>
+    </row>
+    <row r="6" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B6" s="65"/>
       <c r="C6" s="65" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D6" s="65">
         <v>1</v>
       </c>
       <c r="E6" s="65" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F6" s="65"/>
       <c r="G6" s="72">
@@ -3737,7 +3787,7 @@
       <c r="H6" s="73">
         <v>63505.01</v>
       </c>
-      <c r="I6" s="159">
+      <c r="I6" s="158">
         <f>786304-I13-I7-I47-I48-I59-I69-I73</f>
         <v>63505.19</v>
       </c>
@@ -3776,23 +3826,23 @@
         <v>0.01</v>
       </c>
       <c r="U6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
         <v>88</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>89</v>
       </c>
       <c r="B7" s="65"/>
       <c r="C7" s="65" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D7" s="65">
         <f t="shared" ref="D7:D38" si="6">D6+1</f>
         <v>2</v>
       </c>
       <c r="E7" s="65" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F7" s="66"/>
       <c r="G7" s="72">
@@ -3801,7 +3851,7 @@
       <c r="H7" s="73">
         <v>75734.02</v>
       </c>
-      <c r="I7" s="159">
+      <c r="I7" s="158">
         <f>H7</f>
         <v>75734.02</v>
       </c>
@@ -3842,9 +3892,9 @@
       </c>
       <c r="T7" s="43"/>
     </row>
-    <row r="8" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B8" s="65">
         <v>1</v>
@@ -3855,7 +3905,7 @@
         <v>3</v>
       </c>
       <c r="E8" s="65" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F8" s="66"/>
       <c r="G8" s="72">
@@ -3864,7 +3914,7 @@
       <c r="H8" s="73">
         <v>147340.03</v>
       </c>
-      <c r="I8" s="159">
+      <c r="I8" s="158">
         <f>200270+184089+5521-I9-I10</f>
         <v>147339.91000000003</v>
       </c>
@@ -3904,9 +3954,9 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="9" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B9" s="65">
         <v>2</v>
@@ -3917,7 +3967,7 @@
         <v>4</v>
       </c>
       <c r="E9" s="65" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F9" s="66"/>
       <c r="G9" s="72">
@@ -3926,7 +3976,7 @@
       <c r="H9" s="73">
         <v>121270.04</v>
       </c>
-      <c r="I9" s="159">
+      <c r="I9" s="158">
         <f>H9</f>
         <v>121270.04</v>
       </c>
@@ -3967,9 +4017,9 @@
       </c>
       <c r="U9" s="43"/>
     </row>
-    <row r="10" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B10" s="65">
         <v>3</v>
@@ -3980,7 +4030,7 @@
         <v>5</v>
       </c>
       <c r="E10" s="65" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F10" s="66"/>
       <c r="G10" s="72">
@@ -3989,7 +4039,7 @@
       <c r="H10" s="73">
         <v>121270.05</v>
       </c>
-      <c r="I10" s="159">
+      <c r="I10" s="158">
         <f>H10</f>
         <v>121270.05</v>
       </c>
@@ -4030,9 +4080,9 @@
       </c>
       <c r="U10" s="43"/>
     </row>
-    <row r="11" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B11" s="65">
         <v>4</v>
@@ -4043,10 +4093,10 @@
         <v>6</v>
       </c>
       <c r="E11" s="65" t="s">
+        <v>93</v>
+      </c>
+      <c r="F11" s="65" t="s">
         <v>94</v>
-      </c>
-      <c r="F11" s="65" t="s">
-        <v>95</v>
       </c>
       <c r="G11" s="72">
         <v>0.74990000000000001</v>
@@ -4054,7 +4104,7 @@
       <c r="H11" s="73">
         <v>92814.06</v>
       </c>
-      <c r="I11" s="159">
+      <c r="I11" s="158">
         <f>H11</f>
         <v>92814.06</v>
       </c>
@@ -4094,9 +4144,9 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B12" s="65">
         <v>5</v>
@@ -4107,10 +4157,10 @@
         <v>7</v>
       </c>
       <c r="E12" s="65" t="s">
+        <v>95</v>
+      </c>
+      <c r="F12" s="65" t="s">
         <v>96</v>
-      </c>
-      <c r="F12" s="65" t="s">
-        <v>97</v>
       </c>
       <c r="G12" s="72">
         <v>0.54249999999999998</v>
@@ -4118,7 +4168,7 @@
       <c r="H12" s="73">
         <v>67144.070000000007</v>
       </c>
-      <c r="I12" s="159">
+      <c r="I12" s="158">
         <f>H12</f>
         <v>67144.070000000007</v>
       </c>
@@ -4158,9 +4208,9 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B13" s="65">
         <v>6</v>
@@ -4171,7 +4221,7 @@
         <v>8</v>
       </c>
       <c r="E13" s="65" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F13" s="66"/>
       <c r="G13" s="72">
@@ -4180,7 +4230,7 @@
       <c r="H13" s="73">
         <v>56154.080000000002</v>
       </c>
-      <c r="I13" s="159">
+      <c r="I13" s="158">
         <f>H13</f>
         <v>56154.080000000002</v>
       </c>
@@ -4220,9 +4270,9 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="14" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B14" s="65">
         <v>7</v>
@@ -4233,10 +4283,10 @@
         <v>9</v>
       </c>
       <c r="E14" s="65" t="s">
+        <v>99</v>
+      </c>
+      <c r="F14" s="85" t="s">
         <v>100</v>
-      </c>
-      <c r="F14" s="85" t="s">
-        <v>101</v>
       </c>
       <c r="G14" s="72">
         <v>0.52439999999999998</v>
@@ -4244,7 +4294,7 @@
       <c r="H14" s="73">
         <v>126354.09</v>
       </c>
-      <c r="I14" s="159">
+      <c r="I14" s="158">
         <f>H14-64904.10407136</f>
         <v>61449.985928639995</v>
       </c>
@@ -4284,12 +4334,12 @@
         <v>0.09</v>
       </c>
       <c r="U14" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="5" t="s">
         <v>102</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
-        <v>103</v>
       </c>
       <c r="B15" s="65">
         <v>8</v>
@@ -4300,10 +4350,10 @@
         <v>10</v>
       </c>
       <c r="E15" s="65" t="s">
+        <v>99</v>
+      </c>
+      <c r="F15" s="85" t="s">
         <v>100</v>
-      </c>
-      <c r="F15" s="85" t="s">
-        <v>101</v>
       </c>
       <c r="G15" s="72">
         <v>0.42399999999999999</v>
@@ -4311,7 +4361,7 @@
       <c r="H15" s="73">
         <v>102163.1</v>
       </c>
-      <c r="I15" s="159">
+      <c r="I15" s="158">
         <f>H15-52477.7653056</f>
         <v>49685.334694400008</v>
       </c>
@@ -4351,25 +4401,25 @@
         <v>9.9999999999999992E-2</v>
       </c>
       <c r="U15" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="5" t="s">
         <v>102</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
-        <v>103</v>
       </c>
       <c r="B16" s="65">
         <v>1</v>
       </c>
       <c r="C16" s="65" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D16" s="65">
         <f t="shared" si="6"/>
         <v>11</v>
       </c>
       <c r="E16" s="65" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F16" s="66"/>
       <c r="G16" s="72">
@@ -4378,7 +4428,7 @@
       <c r="H16" s="73">
         <v>3256669.11</v>
       </c>
-      <c r="I16" s="159"/>
+      <c r="I16" s="158"/>
       <c r="J16" s="75"/>
       <c r="K16" s="76">
         <f t="shared" si="0"/>
@@ -4415,25 +4465,25 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B17" s="65">
         <v>1</v>
       </c>
       <c r="C17" s="65" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D17" s="65">
         <f t="shared" si="6"/>
         <v>12</v>
       </c>
       <c r="E17" s="65" t="s">
+        <v>107</v>
+      </c>
+      <c r="F17" s="66" t="s">
         <v>108</v>
-      </c>
-      <c r="F17" s="66" t="s">
-        <v>109</v>
       </c>
       <c r="G17" s="72">
         <v>2.7492999999999999</v>
@@ -4441,7 +4491,7 @@
       <c r="H17" s="73">
         <v>350484.12</v>
       </c>
-      <c r="I17" s="159">
+      <c r="I17" s="158">
         <f>H17</f>
         <v>350484.12</v>
       </c>
@@ -4481,25 +4531,25 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="18" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B18" s="65">
         <v>2</v>
       </c>
       <c r="C18" s="65" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D18" s="65">
         <f t="shared" si="6"/>
         <v>13</v>
       </c>
       <c r="E18" s="65" t="s">
+        <v>109</v>
+      </c>
+      <c r="F18" s="66" t="s">
         <v>110</v>
-      </c>
-      <c r="F18" s="66" t="s">
-        <v>111</v>
       </c>
       <c r="G18" s="72">
         <v>2.3033000000000001</v>
@@ -4507,7 +4557,7 @@
       <c r="H18" s="73">
         <v>285076.13</v>
       </c>
-      <c r="I18" s="159">
+      <c r="I18" s="158">
         <f>H18</f>
         <v>285076.13</v>
       </c>
@@ -4547,25 +4597,25 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="19" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B19" s="65">
         <v>2</v>
       </c>
       <c r="C19" s="65" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D19" s="65">
         <f t="shared" si="6"/>
         <v>14</v>
       </c>
       <c r="E19" s="65" t="s">
+        <v>112</v>
+      </c>
+      <c r="F19" s="66" t="s">
         <v>113</v>
-      </c>
-      <c r="F19" s="66" t="s">
-        <v>114</v>
       </c>
       <c r="G19" s="72">
         <v>2.6368</v>
@@ -4573,7 +4623,7 @@
       <c r="H19" s="73">
         <v>326120.14</v>
       </c>
-      <c r="I19" s="159">
+      <c r="I19" s="158">
         <f>40000</f>
         <v>40000</v>
       </c>
@@ -4613,25 +4663,25 @@
         <v>0.13999999999999999</v>
       </c>
       <c r="U19" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="20" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B20" s="65">
         <v>3</v>
       </c>
       <c r="C20" s="65" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D20" s="65">
         <f t="shared" si="6"/>
         <v>15</v>
       </c>
       <c r="E20" s="65" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F20" s="66"/>
       <c r="G20" s="72">
@@ -4640,7 +4690,7 @@
       <c r="H20" s="73">
         <v>291313.15000000002</v>
       </c>
-      <c r="I20" s="159">
+      <c r="I20" s="158">
         <f>H20</f>
         <v>291313.15000000002</v>
       </c>
@@ -4680,25 +4730,25 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="21" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B21" s="65">
         <v>3</v>
       </c>
       <c r="C21" s="65" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D21" s="65">
         <f t="shared" si="6"/>
         <v>16</v>
       </c>
       <c r="E21" s="65" t="s">
+        <v>117</v>
+      </c>
+      <c r="F21" s="65" t="s">
         <v>118</v>
-      </c>
-      <c r="F21" s="65" t="s">
-        <v>119</v>
       </c>
       <c r="G21" s="72">
         <v>2.6476999999999999</v>
@@ -4706,7 +4756,7 @@
       <c r="H21" s="73">
         <v>327701.15999999997</v>
       </c>
-      <c r="I21" s="159">
+      <c r="I21" s="158">
         <f>H21</f>
         <v>327701.15999999997</v>
       </c>
@@ -4747,25 +4797,25 @@
       </c>
       <c r="U21" s="42"/>
     </row>
-    <row r="22" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B22" s="65">
         <v>4</v>
       </c>
       <c r="C22" s="65" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D22" s="65">
         <f t="shared" si="6"/>
         <v>17</v>
       </c>
       <c r="E22" s="65" t="s">
+        <v>119</v>
+      </c>
+      <c r="F22" s="66" t="s">
         <v>120</v>
-      </c>
-      <c r="F22" s="66" t="s">
-        <v>121</v>
       </c>
       <c r="G22" s="72">
         <v>2.3235000000000001</v>
@@ -4773,7 +4823,7 @@
       <c r="H22" s="74">
         <v>287576.17</v>
       </c>
-      <c r="I22" s="159">
+      <c r="I22" s="158">
         <f>H22</f>
         <v>287576.17</v>
       </c>
@@ -4813,25 +4863,25 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="23" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B23" s="65">
         <v>4</v>
       </c>
       <c r="C23" s="65" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D23" s="65">
         <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="E23" s="65" t="s">
+        <v>122</v>
+      </c>
+      <c r="F23" s="144" t="s">
         <v>123</v>
-      </c>
-      <c r="F23" s="145" t="s">
-        <v>124</v>
       </c>
       <c r="G23" s="72">
         <v>2.6880000000000002</v>
@@ -4839,7 +4889,7 @@
       <c r="H23" s="73">
         <v>333718.18</v>
       </c>
-      <c r="I23" s="159">
+      <c r="I23" s="158">
         <f>183718+150000</f>
         <v>333718</v>
       </c>
@@ -4878,26 +4928,26 @@
         <f t="shared" si="7"/>
         <v>0.18000000000000002</v>
       </c>
-      <c r="U23" s="155" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="24" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U23" s="154" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B24" s="65">
         <v>5</v>
       </c>
       <c r="C24" s="65" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D24" s="65">
         <f t="shared" si="6"/>
         <v>19</v>
       </c>
       <c r="E24" s="65" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F24" s="66"/>
       <c r="G24" s="72">
@@ -4906,7 +4956,7 @@
       <c r="H24" s="73">
         <v>292093.19</v>
       </c>
-      <c r="I24" s="159">
+      <c r="I24" s="158">
         <f>H24</f>
         <v>292093.19</v>
       </c>
@@ -4946,22 +4996,22 @@
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="25" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B25" s="65">
         <v>5</v>
       </c>
       <c r="C25" s="65" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D25" s="65">
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
       <c r="E25" s="65" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F25" s="65"/>
       <c r="G25" s="72">
@@ -4970,7 +5020,7 @@
       <c r="H25" s="73">
         <v>327175.2</v>
       </c>
-      <c r="I25" s="159">
+      <c r="I25" s="158">
         <v>337000</v>
       </c>
       <c r="J25" s="75"/>
@@ -5009,22 +5059,22 @@
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="26" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B26" s="65">
         <v>6</v>
       </c>
       <c r="C26" s="65" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D26" s="65">
         <f t="shared" si="6"/>
         <v>21</v>
       </c>
       <c r="E26" s="65" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F26" s="66"/>
       <c r="G26" s="72">
@@ -5033,7 +5083,7 @@
       <c r="H26" s="73">
         <v>285076.21000000002</v>
       </c>
-      <c r="I26" s="159">
+      <c r="I26" s="158">
         <f>H26</f>
         <v>285076.21000000002</v>
       </c>
@@ -5073,25 +5123,25 @@
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="27" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B27" s="65">
         <v>6</v>
       </c>
       <c r="C27" s="65" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D27" s="65">
         <f t="shared" si="6"/>
         <v>22</v>
       </c>
       <c r="E27" s="65" t="s">
+        <v>130</v>
+      </c>
+      <c r="F27" s="85" t="s">
         <v>131</v>
-      </c>
-      <c r="F27" s="85" t="s">
-        <v>132</v>
       </c>
       <c r="G27" s="72">
         <v>2.6360000000000001</v>
@@ -5099,7 +5149,7 @@
       <c r="H27" s="73">
         <v>859793.22</v>
       </c>
-      <c r="I27" s="159">
+      <c r="I27" s="158">
         <f>H27-317346.22</f>
         <v>542447</v>
       </c>
@@ -5119,7 +5169,7 @@
         <f t="shared" si="2"/>
         <v>326253.27675840002</v>
       </c>
-      <c r="O27" s="191">
+      <c r="O27" s="188">
         <v>0</v>
       </c>
       <c r="P27" s="80">
@@ -5139,28 +5189,28 @@
         <v>0.22000000000000006</v>
       </c>
       <c r="T27" s="66" t="s">
+        <v>100</v>
+      </c>
+      <c r="U27" t="s">
         <v>101</v>
       </c>
-      <c r="U27" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="28" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B28" s="65">
         <v>7</v>
       </c>
       <c r="C28" s="65" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D28" s="65">
         <f t="shared" si="6"/>
         <v>23</v>
       </c>
       <c r="E28" s="65" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F28" s="66"/>
       <c r="G28" s="72">
@@ -5169,7 +5219,7 @@
       <c r="H28" s="73">
         <v>285076.23</v>
       </c>
-      <c r="I28" s="159">
+      <c r="I28" s="158">
         <f t="shared" ref="I28:I34" si="8">H28</f>
         <v>285076.23</v>
       </c>
@@ -5209,22 +5259,22 @@
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="29" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B29" s="65">
         <v>7</v>
       </c>
       <c r="C29" s="65" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D29" s="65">
         <f t="shared" si="6"/>
         <v>24</v>
       </c>
       <c r="E29" s="65" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F29" s="66"/>
       <c r="G29" s="72">
@@ -5233,7 +5283,7 @@
       <c r="H29" s="73">
         <v>323766.24</v>
       </c>
-      <c r="I29" s="159">
+      <c r="I29" s="158">
         <f t="shared" si="8"/>
         <v>323766.24</v>
       </c>
@@ -5273,22 +5323,22 @@
         <v>0.24000000000000007</v>
       </c>
     </row>
-    <row r="30" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B30" s="65">
         <v>8</v>
       </c>
       <c r="C30" s="65" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D30" s="65">
         <f t="shared" si="6"/>
         <v>25</v>
       </c>
       <c r="E30" s="65" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F30" s="65"/>
       <c r="G30" s="72">
@@ -5297,7 +5347,7 @@
       <c r="H30" s="73">
         <v>291313.25</v>
       </c>
-      <c r="I30" s="159">
+      <c r="I30" s="158">
         <f t="shared" si="8"/>
         <v>291313.25</v>
       </c>
@@ -5337,25 +5387,25 @@
         <v>0.25000000000000006</v>
       </c>
     </row>
-    <row r="31" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B31" s="65">
         <v>8</v>
       </c>
       <c r="C31" s="65" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D31" s="65">
         <f t="shared" si="6"/>
         <v>26</v>
       </c>
       <c r="E31" s="65" t="s">
+        <v>137</v>
+      </c>
+      <c r="F31" s="65" t="s">
         <v>138</v>
-      </c>
-      <c r="F31" s="65" t="s">
-        <v>139</v>
       </c>
       <c r="G31" s="72">
         <v>2.6469</v>
@@ -5363,7 +5413,7 @@
       <c r="H31" s="73">
         <v>327602.26</v>
       </c>
-      <c r="I31" s="159">
+      <c r="I31" s="158">
         <f t="shared" si="8"/>
         <v>327602.26</v>
       </c>
@@ -5403,22 +5453,22 @@
         <v>0.26000000000000006</v>
       </c>
     </row>
-    <row r="32" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B32" s="65">
         <v>9</v>
       </c>
       <c r="C32" s="65" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D32" s="65">
         <f t="shared" si="6"/>
         <v>27</v>
       </c>
       <c r="E32" s="65" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F32" s="66"/>
       <c r="G32" s="72">
@@ -5427,7 +5477,7 @@
       <c r="H32" s="73">
         <v>291313.27</v>
       </c>
-      <c r="I32" s="159">
+      <c r="I32" s="158">
         <f t="shared" si="8"/>
         <v>291313.27</v>
       </c>
@@ -5467,22 +5517,22 @@
         <v>0.27000000000000007</v>
       </c>
     </row>
-    <row r="33" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B33" s="65">
         <v>9</v>
       </c>
       <c r="C33" s="65" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D33" s="65">
         <f t="shared" si="6"/>
         <v>28</v>
       </c>
       <c r="E33" s="65" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F33" s="65"/>
       <c r="G33" s="72">
@@ -5491,7 +5541,7 @@
       <c r="H33" s="73">
         <v>330003.28000000003</v>
       </c>
-      <c r="I33" s="159">
+      <c r="I33" s="158">
         <f t="shared" si="8"/>
         <v>330003.28000000003</v>
       </c>
@@ -5511,7 +5561,7 @@
         <f t="shared" si="2"/>
         <v>330003.45668472</v>
       </c>
-      <c r="O33" s="130">
+      <c r="O33" s="129">
         <v>0</v>
       </c>
       <c r="P33" s="80">
@@ -5531,25 +5581,25 @@
         <v>0.28000000000000008</v>
       </c>
     </row>
-    <row r="34" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B34" s="65">
         <v>10</v>
       </c>
       <c r="C34" s="65" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D34" s="65">
         <f t="shared" si="6"/>
         <v>29</v>
       </c>
       <c r="E34" s="65" t="s">
+        <v>141</v>
+      </c>
+      <c r="F34" s="65" t="s">
         <v>142</v>
-      </c>
-      <c r="F34" s="65" t="s">
-        <v>143</v>
       </c>
       <c r="G34" s="72">
         <v>2.4476</v>
@@ -5557,7 +5607,7 @@
       <c r="H34" s="73">
         <v>312023.28999999998</v>
       </c>
-      <c r="I34" s="159">
+      <c r="I34" s="158">
         <f t="shared" si="8"/>
         <v>312023.28999999998</v>
       </c>
@@ -5577,7 +5627,7 @@
         <f t="shared" si="2"/>
         <v>302935.32632544002</v>
       </c>
-      <c r="O34" s="197">
+      <c r="O34" s="194">
         <v>18500</v>
       </c>
       <c r="P34" s="80">
@@ -5597,22 +5647,22 @@
         <v>0.29000000000000009</v>
       </c>
     </row>
-    <row r="35" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B35" s="65">
         <v>10</v>
       </c>
       <c r="C35" s="65" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D35" s="65">
         <f t="shared" si="6"/>
         <v>30</v>
       </c>
       <c r="E35" s="65" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F35" s="66"/>
       <c r="G35" s="72">
@@ -5621,7 +5671,7 @@
       <c r="H35" s="73">
         <v>645976.30000000005</v>
       </c>
-      <c r="I35" s="159">
+      <c r="I35" s="158">
         <f>H35</f>
         <v>645976.30000000005</v>
       </c>
@@ -5661,25 +5711,25 @@
         <v>0.3000000000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B36" s="65">
         <v>11</v>
       </c>
       <c r="C36" s="65" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D36" s="65">
         <f t="shared" si="6"/>
         <v>31</v>
       </c>
       <c r="E36" s="65" t="s">
+        <v>144</v>
+      </c>
+      <c r="F36" s="65" t="s">
         <v>145</v>
-      </c>
-      <c r="F36" s="65" t="s">
-        <v>146</v>
       </c>
       <c r="G36" s="72">
         <v>2.3026</v>
@@ -5687,7 +5737,7 @@
       <c r="H36" s="74">
         <v>284989.31</v>
       </c>
-      <c r="I36" s="159">
+      <c r="I36" s="158">
         <f>H36</f>
         <v>284989.31</v>
       </c>
@@ -5703,7 +5753,7 @@
       <c r="M36" s="77">
         <v>0</v>
       </c>
-      <c r="N36" s="143">
+      <c r="N36" s="142">
         <f t="shared" si="2"/>
         <v>284988.92073744</v>
       </c>
@@ -5727,22 +5777,22 @@
         <v>0.31000000000000011</v>
       </c>
     </row>
-    <row r="37" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B37" s="65">
         <v>11</v>
       </c>
       <c r="C37" s="65" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D37" s="65">
         <f t="shared" si="6"/>
         <v>32</v>
       </c>
       <c r="E37" s="65" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F37" s="66"/>
       <c r="G37" s="72">
@@ -5751,7 +5801,7 @@
       <c r="H37" s="73">
         <v>452304.32</v>
       </c>
-      <c r="I37" s="159">
+      <c r="I37" s="158">
         <v>328753.32</v>
       </c>
       <c r="J37" s="75"/>
@@ -5790,22 +5840,22 @@
         <v>0.32000000000000012</v>
       </c>
     </row>
-    <row r="38" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B38" s="65">
         <v>12</v>
       </c>
       <c r="C38" s="65" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D38" s="65">
         <f t="shared" si="6"/>
         <v>33</v>
       </c>
       <c r="E38" s="65" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F38" s="66"/>
       <c r="G38" s="72">
@@ -5814,7 +5864,7 @@
       <c r="H38" s="73">
         <v>288912.33</v>
       </c>
-      <c r="I38" s="159">
+      <c r="I38" s="158">
         <f t="shared" ref="I38:I41" si="9">H38</f>
         <v>288912.33</v>
       </c>
@@ -5854,22 +5904,22 @@
         <v>0.33000000000000013</v>
       </c>
     </row>
-    <row r="39" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B39" s="65">
         <v>12</v>
       </c>
       <c r="C39" s="65" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D39" s="65">
         <f t="shared" ref="D39:D75" si="16">D38+1</f>
         <v>34</v>
       </c>
       <c r="E39" s="65" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F39" s="65"/>
       <c r="G39" s="72">
@@ -5878,7 +5928,7 @@
       <c r="H39" s="73">
         <v>325003.34000000003</v>
       </c>
-      <c r="I39" s="159">
+      <c r="I39" s="158">
         <f t="shared" si="9"/>
         <v>325003.34000000003</v>
       </c>
@@ -5918,25 +5968,25 @@
         <v>0.34000000000000014</v>
       </c>
     </row>
-    <row r="40" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B40" s="65">
         <v>1</v>
       </c>
       <c r="C40" s="65" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D40" s="65">
         <f t="shared" si="16"/>
         <v>35</v>
       </c>
       <c r="E40" s="65" t="s">
+        <v>150</v>
+      </c>
+      <c r="F40" s="66" t="s">
         <v>151</v>
-      </c>
-      <c r="F40" s="66" t="s">
-        <v>152</v>
       </c>
       <c r="G40" s="72">
         <v>1.0069999999999999</v>
@@ -5944,7 +5994,7 @@
       <c r="H40" s="73">
         <v>124635.35</v>
       </c>
-      <c r="I40" s="159">
+      <c r="I40" s="158">
         <f t="shared" si="9"/>
         <v>124635.35</v>
       </c>
@@ -5984,25 +6034,25 @@
         <v>0.35000000000000014</v>
       </c>
     </row>
-    <row r="41" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B41" s="65">
         <v>1</v>
       </c>
       <c r="C41" s="65" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D41" s="65">
         <f t="shared" si="16"/>
         <v>36</v>
       </c>
       <c r="E41" s="65" t="s">
+        <v>153</v>
+      </c>
+      <c r="F41" s="66" t="s">
         <v>154</v>
-      </c>
-      <c r="F41" s="66" t="s">
-        <v>155</v>
       </c>
       <c r="G41" s="72">
         <v>0.78120000000000001</v>
@@ -6010,7 +6060,7 @@
       <c r="H41" s="74">
         <v>96688.36</v>
       </c>
-      <c r="I41" s="159">
+      <c r="I41" s="158">
         <f t="shared" si="9"/>
         <v>96688.36</v>
       </c>
@@ -6050,26 +6100,26 @@
         <v>0.36000000000000015</v>
       </c>
       <c r="U41" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="42" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="42" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="52"/>
       <c r="B42" s="64">
         <v>1</v>
       </c>
       <c r="C42" s="64" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D42" s="65">
         <f t="shared" si="16"/>
         <v>37</v>
       </c>
       <c r="E42" s="64" t="s">
+        <v>153</v>
+      </c>
+      <c r="F42" s="66" t="s">
         <v>154</v>
-      </c>
-      <c r="F42" s="66" t="s">
-        <v>155</v>
       </c>
       <c r="G42" s="86">
         <v>1.2153</v>
@@ -6077,7 +6127,7 @@
       <c r="H42" s="73">
         <v>150416.37</v>
       </c>
-      <c r="I42" s="159">
+      <c r="I42" s="158">
         <v>150416.37</v>
       </c>
       <c r="J42" s="75"/>
@@ -6116,25 +6166,25 @@
         <v>0.37000000000000016</v>
       </c>
       <c r="U42" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="43" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="43" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="65">
         <v>2</v>
       </c>
       <c r="C43" s="87" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D43" s="65">
         <f t="shared" si="16"/>
         <v>38</v>
       </c>
       <c r="E43" s="64" t="s">
+        <v>157</v>
+      </c>
+      <c r="F43" s="64" t="s">
         <v>158</v>
-      </c>
-      <c r="F43" s="64" t="s">
-        <v>159</v>
       </c>
       <c r="G43" s="86">
         <v>0.95489999999999997</v>
@@ -6142,7 +6192,7 @@
       <c r="H43" s="73">
         <v>118186.38</v>
       </c>
-      <c r="I43" s="159">
+      <c r="I43" s="158">
         <v>111896.38</v>
       </c>
       <c r="J43" s="75"/>
@@ -6181,19 +6231,19 @@
         <v>0.38000000000000017</v>
       </c>
     </row>
-    <row r="44" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="65">
         <v>2</v>
       </c>
       <c r="C44" s="87" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D44" s="65">
         <f t="shared" si="16"/>
         <v>39</v>
       </c>
       <c r="E44" s="64" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F44" s="85"/>
       <c r="G44" s="86">
@@ -6202,7 +6252,7 @@
       <c r="H44" s="73">
         <v>536048.39</v>
       </c>
-      <c r="I44" s="159"/>
+      <c r="I44" s="158"/>
       <c r="J44" s="75"/>
       <c r="K44" s="76">
         <f t="shared" si="10"/>
@@ -6239,22 +6289,22 @@
         <v>0.39000000000000018</v>
       </c>
     </row>
-    <row r="45" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="65">
         <v>2</v>
       </c>
       <c r="C45" s="87" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D45" s="65">
         <f t="shared" si="16"/>
         <v>40</v>
       </c>
       <c r="E45" s="64" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F45" s="64" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G45" s="86">
         <v>1.1545000000000001</v>
@@ -6262,7 +6312,7 @@
       <c r="H45" s="73">
         <v>138941.4</v>
       </c>
-      <c r="I45" s="159">
+      <c r="I45" s="158">
         <f>H45</f>
         <v>138941.4</v>
       </c>
@@ -6302,22 +6352,22 @@
         <v>0.40000000000000019</v>
       </c>
     </row>
-    <row r="46" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="65">
         <v>3</v>
       </c>
       <c r="C46" s="87" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D46" s="65">
         <f t="shared" si="16"/>
         <v>41</v>
       </c>
       <c r="E46" s="64" t="s">
+        <v>161</v>
+      </c>
+      <c r="F46" s="64" t="s">
         <v>162</v>
-      </c>
-      <c r="F46" s="64" t="s">
-        <v>163</v>
       </c>
       <c r="G46" s="86">
         <v>0.95489999999999997</v>
@@ -6325,7 +6375,7 @@
       <c r="H46" s="73">
         <v>114927.41</v>
       </c>
-      <c r="I46" s="159">
+      <c r="I46" s="158">
         <f>118375.41</f>
         <v>118375.41</v>
       </c>
@@ -6365,19 +6415,19 @@
         <v>0.4100000000000002</v>
       </c>
     </row>
-    <row r="47" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="65">
         <v>3</v>
       </c>
       <c r="C47" s="87" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D47" s="65">
         <f t="shared" si="16"/>
         <v>42</v>
       </c>
       <c r="E47" s="64" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F47" s="85"/>
       <c r="G47" s="86">
@@ -6386,7 +6436,7 @@
       <c r="H47" s="73">
         <v>93470.42</v>
       </c>
-      <c r="I47" s="159">
+      <c r="I47" s="158">
         <f>H47</f>
         <v>93470.42</v>
       </c>
@@ -6426,19 +6476,19 @@
         <v>0.42000000000000021</v>
       </c>
     </row>
-    <row r="48" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B48" s="65">
         <v>3</v>
       </c>
       <c r="C48" s="87" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D48" s="65">
         <f t="shared" si="16"/>
         <v>43</v>
       </c>
       <c r="E48" s="64" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F48" s="85"/>
       <c r="G48" s="86">
@@ -6447,7 +6497,7 @@
       <c r="H48" s="73">
         <v>142891.43</v>
       </c>
-      <c r="I48" s="159">
+      <c r="I48" s="158">
         <f>H48</f>
         <v>142891.43</v>
       </c>
@@ -6487,22 +6537,22 @@
         <v>0.43000000000000022</v>
       </c>
     </row>
-    <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49" s="65">
         <v>4</v>
       </c>
       <c r="C49" s="87" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D49" s="65">
         <f t="shared" si="16"/>
         <v>44</v>
       </c>
       <c r="E49" s="64" t="s">
+        <v>165</v>
+      </c>
+      <c r="F49" s="85" t="s">
         <v>166</v>
-      </c>
-      <c r="F49" s="85" t="s">
-        <v>167</v>
       </c>
       <c r="G49" s="86">
         <v>0.95489999999999997</v>
@@ -6510,7 +6560,7 @@
       <c r="H49" s="73">
         <v>118186.44</v>
       </c>
-      <c r="I49" s="159">
+      <c r="I49" s="158">
         <f>H49</f>
         <v>118186.44</v>
       </c>
@@ -6550,19 +6600,19 @@
         <v>0.44000000000000022</v>
       </c>
     </row>
-    <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="65">
         <v>4</v>
       </c>
       <c r="C50" s="87" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D50" s="65">
         <f t="shared" si="16"/>
         <v>45</v>
       </c>
       <c r="E50" s="64" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F50" s="64"/>
       <c r="G50" s="86">
@@ -6571,7 +6621,7 @@
       <c r="H50" s="73">
         <v>93468.45</v>
       </c>
-      <c r="I50" s="159">
+      <c r="I50" s="158">
         <f>93470</f>
         <v>93470</v>
       </c>
@@ -6611,25 +6661,25 @@
         <v>0.45000000000000023</v>
       </c>
       <c r="U50" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="51" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="51" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="65">
         <v>4</v>
       </c>
       <c r="C51" s="87" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D51" s="65">
         <f t="shared" si="16"/>
         <v>46</v>
       </c>
       <c r="E51" s="64" t="s">
+        <v>169</v>
+      </c>
+      <c r="F51" s="64" t="s">
         <v>170</v>
-      </c>
-      <c r="F51" s="64" t="s">
-        <v>171</v>
       </c>
       <c r="G51" s="86">
         <v>1.1545000000000001</v>
@@ -6637,7 +6687,7 @@
       <c r="H51" s="73">
         <v>142891.46</v>
       </c>
-      <c r="I51" s="159">
+      <c r="I51" s="158">
         <f t="shared" ref="I51:I59" si="18">H51</f>
         <v>142891.46</v>
       </c>
@@ -6677,22 +6727,22 @@
         <v>0.46000000000000024</v>
       </c>
     </row>
-    <row r="52" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="65">
         <v>5</v>
       </c>
       <c r="C52" s="87" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D52" s="65">
         <f t="shared" si="16"/>
         <v>47</v>
       </c>
       <c r="E52" s="64" t="s">
+        <v>171</v>
+      </c>
+      <c r="F52" s="85" t="s">
         <v>172</v>
-      </c>
-      <c r="F52" s="85" t="s">
-        <v>173</v>
       </c>
       <c r="G52" s="86">
         <v>0.95489999999999997</v>
@@ -6700,7 +6750,7 @@
       <c r="H52" s="73">
         <v>118186.47</v>
       </c>
-      <c r="I52" s="159">
+      <c r="I52" s="158">
         <f t="shared" si="18"/>
         <v>118186.47</v>
       </c>
@@ -6740,22 +6790,22 @@
         <v>0.47000000000000025</v>
       </c>
     </row>
-    <row r="53" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="65">
         <v>5</v>
       </c>
       <c r="C53" s="87" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D53" s="65">
         <f t="shared" si="16"/>
         <v>48</v>
       </c>
       <c r="E53" s="64" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F53" s="64" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G53" s="86">
         <v>0.75519999999999998</v>
@@ -6763,7 +6813,7 @@
       <c r="H53" s="73">
         <v>93470.48</v>
       </c>
-      <c r="I53" s="159">
+      <c r="I53" s="158">
         <f t="shared" si="18"/>
         <v>93470.48</v>
       </c>
@@ -6803,22 +6853,22 @@
         <v>0.48000000000000026</v>
       </c>
     </row>
-    <row r="54" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="65">
         <v>5</v>
       </c>
       <c r="C54" s="87" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D54" s="65">
         <f t="shared" si="16"/>
         <v>49</v>
       </c>
       <c r="E54" s="64" t="s">
+        <v>174</v>
+      </c>
+      <c r="F54" s="64" t="s">
         <v>175</v>
-      </c>
-      <c r="F54" s="64" t="s">
-        <v>176</v>
       </c>
       <c r="G54" s="86">
         <v>1.1545000000000001</v>
@@ -6826,7 +6876,7 @@
       <c r="H54" s="73">
         <v>142891.49</v>
       </c>
-      <c r="I54" s="159">
+      <c r="I54" s="158">
         <f t="shared" si="18"/>
         <v>142891.49</v>
       </c>
@@ -6866,19 +6916,19 @@
         <v>0.49000000000000027</v>
       </c>
     </row>
-    <row r="55" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B55" s="65">
         <v>6</v>
       </c>
       <c r="C55" s="87" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D55" s="65">
         <f t="shared" si="16"/>
         <v>50</v>
       </c>
       <c r="E55" s="64" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F55" s="64"/>
       <c r="G55" s="86">
@@ -6887,7 +6937,7 @@
       <c r="H55" s="73">
         <v>121732.5</v>
       </c>
-      <c r="I55" s="159">
+      <c r="I55" s="158">
         <f t="shared" si="18"/>
         <v>121732.5</v>
       </c>
@@ -6927,19 +6977,19 @@
         <v>0.50000000000000022</v>
       </c>
     </row>
-    <row r="56" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B56" s="65">
         <v>6</v>
       </c>
       <c r="C56" s="87" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D56" s="65">
         <f t="shared" si="16"/>
         <v>51</v>
       </c>
       <c r="E56" s="64" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F56" s="64"/>
       <c r="G56" s="86">
@@ -6948,7 +6998,7 @@
       <c r="H56" s="73">
         <v>96274.51</v>
       </c>
-      <c r="I56" s="159">
+      <c r="I56" s="158">
         <v>93470</v>
       </c>
       <c r="J56" s="75"/>
@@ -6987,22 +7037,22 @@
         <v>0.51000000000000023</v>
       </c>
       <c r="U56" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="57" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="57" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B57" s="65">
         <v>6</v>
       </c>
       <c r="C57" s="87" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D57" s="65">
         <f t="shared" si="16"/>
         <v>52</v>
       </c>
       <c r="E57" s="64" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F57" s="85"/>
       <c r="G57" s="86">
@@ -7011,7 +7061,7 @@
       <c r="H57" s="73">
         <v>142891.51999999999</v>
       </c>
-      <c r="I57" s="159">
+      <c r="I57" s="158">
         <f t="shared" si="18"/>
         <v>142891.51999999999</v>
       </c>
@@ -7051,19 +7101,19 @@
         <v>0.52000000000000024</v>
       </c>
     </row>
-    <row r="58" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B58" s="65">
         <v>7</v>
       </c>
       <c r="C58" s="87" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D58" s="65">
         <f t="shared" si="16"/>
         <v>53</v>
       </c>
       <c r="E58" s="64" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F58" s="85"/>
       <c r="G58" s="86">
@@ -7072,7 +7122,7 @@
       <c r="H58" s="73">
         <v>118186.53</v>
       </c>
-      <c r="I58" s="159">
+      <c r="I58" s="158">
         <f t="shared" si="18"/>
         <v>118186.53</v>
       </c>
@@ -7112,19 +7162,19 @@
         <v>0.53000000000000025</v>
       </c>
     </row>
-    <row r="59" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B59" s="65">
         <v>7</v>
       </c>
       <c r="C59" s="87" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D59" s="65">
         <f t="shared" si="16"/>
         <v>54</v>
       </c>
       <c r="E59" s="64" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F59" s="64"/>
       <c r="G59" s="86">
@@ -7133,7 +7183,7 @@
       <c r="H59" s="73">
         <v>93470.54</v>
       </c>
-      <c r="I59" s="159">
+      <c r="I59" s="158">
         <f t="shared" si="18"/>
         <v>93470.54</v>
       </c>
@@ -7173,22 +7223,22 @@
         <v>0.54000000000000026</v>
       </c>
     </row>
-    <row r="60" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60" s="65">
         <v>7</v>
       </c>
       <c r="C60" s="87" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D60" s="65">
         <f t="shared" si="16"/>
         <v>55</v>
       </c>
       <c r="E60" s="64" t="s">
+        <v>182</v>
+      </c>
+      <c r="F60" s="64" t="s">
         <v>183</v>
-      </c>
-      <c r="F60" s="64" t="s">
-        <v>184</v>
       </c>
       <c r="G60" s="86">
         <v>1.1545000000000001</v>
@@ -7196,7 +7246,7 @@
       <c r="H60" s="73">
         <v>570239.55000000005</v>
       </c>
-      <c r="I60" s="159"/>
+      <c r="I60" s="158"/>
       <c r="J60" s="75"/>
       <c r="K60" s="76">
         <f t="shared" si="10"/>
@@ -7233,22 +7283,22 @@
         <v>0.55000000000000027</v>
       </c>
     </row>
-    <row r="61" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B61" s="65">
         <v>8</v>
       </c>
       <c r="C61" s="87" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D61" s="65">
         <f t="shared" si="16"/>
         <v>56</v>
       </c>
       <c r="E61" s="64" t="s">
+        <v>184</v>
+      </c>
+      <c r="F61" s="85" t="s">
         <v>185</v>
-      </c>
-      <c r="F61" s="85" t="s">
-        <v>186</v>
       </c>
       <c r="G61" s="86">
         <v>0.95489999999999997</v>
@@ -7256,7 +7306,7 @@
       <c r="H61" s="73">
         <v>118186.56</v>
       </c>
-      <c r="I61" s="159">
+      <c r="I61" s="158">
         <f>H61</f>
         <v>118186.56</v>
       </c>
@@ -7294,22 +7344,22 @@
         <v>0.56000000000000028</v>
       </c>
     </row>
-    <row r="62" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="65">
         <v>8</v>
       </c>
       <c r="C62" s="87" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D62" s="65">
         <f t="shared" si="16"/>
         <v>57</v>
       </c>
       <c r="E62" s="64" t="s">
+        <v>186</v>
+      </c>
+      <c r="F62" s="85" t="s">
         <v>187</v>
-      </c>
-      <c r="F62" s="85" t="s">
-        <v>188</v>
       </c>
       <c r="G62" s="86">
         <v>0.75519999999999998</v>
@@ -7317,7 +7367,7 @@
       <c r="H62" s="73">
         <v>93904.57</v>
       </c>
-      <c r="I62" s="159">
+      <c r="I62" s="158">
         <v>96721.57</v>
       </c>
       <c r="J62" s="75"/>
@@ -7356,19 +7406,19 @@
         <v>0.57000000000000028</v>
       </c>
     </row>
-    <row r="63" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B63" s="65">
         <v>8</v>
       </c>
       <c r="C63" s="87" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D63" s="65">
         <f t="shared" si="16"/>
         <v>58</v>
       </c>
       <c r="E63" s="64" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F63" s="85"/>
       <c r="G63" s="86">
@@ -7377,7 +7427,7 @@
       <c r="H63" s="73">
         <v>142891.57999999999</v>
       </c>
-      <c r="I63" s="159">
+      <c r="I63" s="158">
         <f>H63</f>
         <v>142891.57999999999</v>
       </c>
@@ -7417,22 +7467,22 @@
         <v>0.58000000000000029</v>
       </c>
     </row>
-    <row r="64" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B64" s="65">
         <v>9</v>
       </c>
       <c r="C64" s="87" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D64" s="65">
         <f t="shared" si="16"/>
         <v>59</v>
       </c>
       <c r="E64" s="64" t="s">
+        <v>189</v>
+      </c>
+      <c r="F64" s="207" t="s">
         <v>190</v>
-      </c>
-      <c r="F64" s="239" t="s">
-        <v>191</v>
       </c>
       <c r="G64" s="86">
         <v>0.95489999999999997</v>
@@ -7440,7 +7490,7 @@
       <c r="H64" s="73">
         <v>233441.59</v>
       </c>
-      <c r="I64" s="159">
+      <c r="I64" s="158">
         <f>2*108637+16168</f>
         <v>233442</v>
       </c>
@@ -7480,19 +7530,19 @@
         <v>0.5900000000000003</v>
       </c>
     </row>
-    <row r="65" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B65" s="65">
         <v>9</v>
       </c>
       <c r="C65" s="87" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D65" s="65">
         <f t="shared" si="16"/>
         <v>60</v>
       </c>
       <c r="E65" s="64" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F65" s="85"/>
       <c r="G65" s="86">
@@ -7501,7 +7551,7 @@
       <c r="H65" s="73">
         <v>96125.6</v>
       </c>
-      <c r="I65" s="159"/>
+      <c r="I65" s="158"/>
       <c r="J65" s="75"/>
       <c r="K65" s="76">
         <f t="shared" si="10"/>
@@ -7538,22 +7588,22 @@
         <v>0.60000000000000031</v>
       </c>
       <c r="U65" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="66" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B66" s="65">
         <v>9</v>
       </c>
       <c r="C66" s="87" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D66" s="65">
         <f t="shared" si="16"/>
         <v>61</v>
       </c>
       <c r="E66" s="64" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F66" s="64"/>
       <c r="G66" s="86">
@@ -7562,7 +7612,7 @@
       <c r="H66" s="73">
         <v>142891.60999999999</v>
       </c>
-      <c r="I66" s="159">
+      <c r="I66" s="158">
         <f>H66</f>
         <v>142891.60999999999</v>
       </c>
@@ -7602,25 +7652,25 @@
         <v>0.61000000000000032</v>
       </c>
       <c r="U66" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="67" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B67" s="65">
         <v>10</v>
       </c>
       <c r="C67" s="87" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D67" s="65">
         <f t="shared" si="16"/>
         <v>62</v>
       </c>
       <c r="E67" s="64" t="s">
+        <v>195</v>
+      </c>
+      <c r="F67" s="85" t="s">
         <v>196</v>
-      </c>
-      <c r="F67" s="85" t="s">
-        <v>197</v>
       </c>
       <c r="G67" s="86">
         <v>0.95489999999999997</v>
@@ -7628,7 +7678,7 @@
       <c r="H67" s="73">
         <v>118186.62</v>
       </c>
-      <c r="I67" s="159">
+      <c r="I67" s="158">
         <f>H67</f>
         <v>118186.62</v>
       </c>
@@ -7668,25 +7718,25 @@
         <v>0.62000000000000033</v>
       </c>
       <c r="U67" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="68" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="68" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B68" s="65">
         <v>10</v>
       </c>
       <c r="C68" s="87" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D68" s="65">
         <f t="shared" si="16"/>
         <v>63</v>
       </c>
       <c r="E68" s="64" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F68" s="64" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G68" s="86">
         <v>0.75519999999999998</v>
@@ -7694,7 +7744,7 @@
       <c r="H68" s="73">
         <v>96039.63</v>
       </c>
-      <c r="I68" s="159">
+      <c r="I68" s="158">
         <f>H68</f>
         <v>96039.63</v>
       </c>
@@ -7734,19 +7784,19 @@
         <v>0.63000000000000034</v>
       </c>
     </row>
-    <row r="69" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B69" s="65">
         <v>10</v>
       </c>
       <c r="C69" s="87" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D69" s="65">
         <f t="shared" si="16"/>
         <v>64</v>
       </c>
       <c r="E69" s="64" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F69" s="64"/>
       <c r="G69" s="86">
@@ -7755,7 +7805,7 @@
       <c r="H69" s="73">
         <v>142891.64000000001</v>
       </c>
-      <c r="I69" s="159">
+      <c r="I69" s="158">
         <f>H69</f>
         <v>142891.64000000001</v>
       </c>
@@ -7795,19 +7845,19 @@
         <v>0.64000000000000035</v>
       </c>
     </row>
-    <row r="70" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B70" s="65">
         <v>11</v>
       </c>
       <c r="C70" s="87" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D70" s="65">
         <f t="shared" si="16"/>
         <v>65</v>
       </c>
       <c r="E70" s="64" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F70" s="85"/>
       <c r="G70" s="86">
@@ -7816,7 +7866,7 @@
       <c r="H70" s="73">
         <v>118186.65</v>
       </c>
-      <c r="I70" s="159">
+      <c r="I70" s="158">
         <v>121732.65</v>
       </c>
       <c r="J70" s="75"/>
@@ -7855,22 +7905,22 @@
         <v>0.65000000000000036</v>
       </c>
     </row>
-    <row r="71" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B71" s="65">
         <v>11</v>
       </c>
       <c r="C71" s="87" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D71" s="65">
         <f t="shared" si="16"/>
         <v>66</v>
       </c>
       <c r="E71" s="64" t="s">
+        <v>200</v>
+      </c>
+      <c r="F71" s="85" t="s">
         <v>201</v>
-      </c>
-      <c r="F71" s="85" t="s">
-        <v>202</v>
       </c>
       <c r="G71" s="86">
         <v>0.75519999999999998</v>
@@ -7878,7 +7928,7 @@
       <c r="H71" s="73">
         <v>90892.66</v>
       </c>
-      <c r="I71" s="159"/>
+      <c r="I71" s="158"/>
       <c r="J71" s="75"/>
       <c r="K71" s="76">
         <f t="shared" si="19"/>
@@ -7915,19 +7965,19 @@
         <v>0.66000000000000036</v>
       </c>
     </row>
-    <row r="72" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B72" s="65">
         <v>11</v>
       </c>
       <c r="C72" s="87" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D72" s="65">
         <f t="shared" si="16"/>
         <v>67</v>
       </c>
       <c r="E72" s="64" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F72" s="64"/>
       <c r="G72" s="86">
@@ -7936,7 +7986,7 @@
       <c r="H72" s="73">
         <v>142891.67000000001</v>
       </c>
-      <c r="I72" s="159">
+      <c r="I72" s="158">
         <f>H72</f>
         <v>142891.67000000001</v>
       </c>
@@ -7976,19 +8026,19 @@
         <v>0.67000000000000037</v>
       </c>
     </row>
-    <row r="73" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B73" s="65">
         <v>12</v>
       </c>
       <c r="C73" s="88" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D73" s="65">
         <f t="shared" si="16"/>
         <v>68</v>
       </c>
       <c r="E73" s="89" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F73" s="89"/>
       <c r="G73" s="90">
@@ -7997,7 +8047,7 @@
       <c r="H73" s="91">
         <v>118186.68</v>
       </c>
-      <c r="I73" s="159">
+      <c r="I73" s="158">
         <f>H73</f>
         <v>118186.68</v>
       </c>
@@ -8037,19 +8087,19 @@
         <v>0.68000000000000038</v>
       </c>
     </row>
-    <row r="74" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B74" s="65">
         <v>12</v>
       </c>
       <c r="C74" s="87" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D74" s="65">
         <f t="shared" si="16"/>
         <v>69</v>
       </c>
       <c r="E74" s="65" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F74" s="97"/>
       <c r="G74" s="90">
@@ -8058,7 +8108,7 @@
       <c r="H74" s="91">
         <v>93470.69</v>
       </c>
-      <c r="I74" s="159">
+      <c r="I74" s="158">
         <f>H74</f>
         <v>93470.69</v>
       </c>
@@ -8098,19 +8148,19 @@
         <v>0.69000000000000039</v>
       </c>
     </row>
-    <row r="75" spans="2:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B75" s="65">
         <v>12</v>
       </c>
       <c r="C75" s="87" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D75" s="65">
         <f t="shared" si="16"/>
         <v>70</v>
       </c>
       <c r="E75" s="65" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F75" s="97"/>
       <c r="G75" s="90">
@@ -8119,7 +8169,7 @@
       <c r="H75" s="91">
         <v>142940.70000000001</v>
       </c>
-      <c r="I75" s="159">
+      <c r="I75" s="158">
         <f>H75</f>
         <v>142940.70000000001</v>
       </c>
@@ -8159,7 +8209,7 @@
         <v>0.7000000000000004</v>
       </c>
     </row>
-    <row r="76" spans="2:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B76" s="65"/>
       <c r="C76" s="87"/>
       <c r="D76" s="87"/>
@@ -8179,7 +8229,7 @@
       <c r="R76" s="82"/>
       <c r="S76" s="43"/>
     </row>
-    <row r="77" spans="2:21" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:21" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B77" s="65"/>
       <c r="C77" s="87"/>
       <c r="D77" s="87"/>
@@ -8199,7 +8249,7 @@
       <c r="R77" s="82"/>
       <c r="S77" s="43"/>
     </row>
-    <row r="78" spans="2:21" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:21" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B78" s="65"/>
       <c r="C78" s="87"/>
       <c r="D78" s="87"/>
@@ -8219,9 +8269,9 @@
       <c r="R78" s="82"/>
       <c r="S78" s="43"/>
     </row>
-    <row r="79" spans="2:21" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:21" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" s="98"/>
-      <c r="C79" s="137"/>
+      <c r="C79" s="136"/>
       <c r="D79" s="88"/>
       <c r="E79" s="65"/>
       <c r="F79" s="66"/>
@@ -8239,7 +8289,7 @@
       <c r="R79" s="82"/>
       <c r="S79" s="43"/>
     </row>
-    <row r="80" spans="2:21" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:21" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B80" s="65"/>
       <c r="C80" s="65"/>
       <c r="D80" s="65"/>
@@ -8259,9 +8309,9 @@
       <c r="R80" s="102"/>
       <c r="S80" s="43"/>
     </row>
-    <row r="81" spans="2:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B81" s="103"/>
-      <c r="C81" s="138"/>
+      <c r="C81" s="137"/>
       <c r="D81" s="104"/>
       <c r="E81" s="105"/>
       <c r="F81" s="105"/>
@@ -8308,108 +8358,100 @@
       </c>
       <c r="R81" s="107"/>
     </row>
-    <row r="82" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E82" s="50"/>
       <c r="F82" s="50"/>
     </row>
-    <row r="83" spans="2:18" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="84" spans="2:18" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E84" s="211" t="str">
+    <row r="83" spans="2:18" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="84" spans="2:18" ht="9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E84" s="218" t="str">
         <f>RESUMEN!A14</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. CASO CONTRARIO SE INFORMARA VIA CARTA DOCUMENTO A LA UNIDAD FUNCIONAL QUE CREEMOS QUE CORRESPONDE, CUYO COSTO SERA IMPUTADO A LA UNIDAD FUNCIONAL SOSPECHADA.</v>
       </c>
-      <c r="F84" s="212"/>
-      <c r="G84" s="212"/>
-      <c r="H84" s="212"/>
-      <c r="I84" s="212"/>
-      <c r="J84" s="212"/>
-      <c r="K84" s="212"/>
-      <c r="L84" s="212"/>
-      <c r="M84" s="212"/>
-      <c r="N84" s="212"/>
-      <c r="O84" s="212"/>
-      <c r="P84" s="212"/>
-    </row>
-    <row r="85" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E85" s="212"/>
-      <c r="F85" s="212"/>
-      <c r="G85" s="212"/>
-      <c r="H85" s="212"/>
-      <c r="I85" s="212"/>
-      <c r="J85" s="212"/>
-      <c r="K85" s="212"/>
-      <c r="L85" s="212"/>
-      <c r="M85" s="212"/>
-      <c r="N85" s="212"/>
-      <c r="O85" s="212"/>
-      <c r="P85" s="212"/>
-    </row>
-    <row r="86" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E86" s="212"/>
-      <c r="F86" s="212"/>
-      <c r="G86" s="212"/>
-      <c r="H86" s="212"/>
-      <c r="I86" s="212"/>
-      <c r="J86" s="212"/>
-      <c r="K86" s="212"/>
-      <c r="L86" s="212"/>
-      <c r="M86" s="212"/>
-      <c r="N86" s="212"/>
-      <c r="O86" s="212"/>
-      <c r="P86" s="212"/>
-    </row>
-    <row r="87" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E87" s="212"/>
-      <c r="F87" s="212"/>
-      <c r="G87" s="212"/>
-      <c r="H87" s="212"/>
-      <c r="I87" s="212"/>
-      <c r="J87" s="212"/>
-      <c r="K87" s="212"/>
-      <c r="L87" s="212"/>
-      <c r="M87" s="212"/>
-      <c r="N87" s="212"/>
-      <c r="O87" s="212"/>
-      <c r="P87" s="212"/>
-    </row>
-    <row r="88" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E88" s="212"/>
-      <c r="F88" s="212"/>
-      <c r="G88" s="212"/>
-      <c r="H88" s="212"/>
-      <c r="I88" s="212"/>
-      <c r="J88" s="212"/>
-      <c r="K88" s="212"/>
-      <c r="L88" s="212"/>
-      <c r="M88" s="212"/>
-      <c r="N88" s="212"/>
-      <c r="O88" s="212"/>
-      <c r="P88" s="212"/>
-    </row>
-    <row r="89" spans="2:18" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E89" s="212"/>
-      <c r="F89" s="212"/>
-      <c r="G89" s="212"/>
-      <c r="H89" s="212"/>
-      <c r="I89" s="212"/>
-      <c r="J89" s="212"/>
-      <c r="K89" s="212"/>
-      <c r="L89" s="212"/>
-      <c r="M89" s="212"/>
-      <c r="N89" s="212"/>
-      <c r="O89" s="212"/>
-      <c r="P89" s="212"/>
+      <c r="F84" s="211"/>
+      <c r="G84" s="211"/>
+      <c r="H84" s="211"/>
+      <c r="I84" s="211"/>
+      <c r="J84" s="211"/>
+      <c r="K84" s="211"/>
+      <c r="L84" s="211"/>
+      <c r="M84" s="211"/>
+      <c r="N84" s="211"/>
+      <c r="O84" s="211"/>
+      <c r="P84" s="211"/>
+    </row>
+    <row r="85" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E85" s="211"/>
+      <c r="F85" s="211"/>
+      <c r="G85" s="211"/>
+      <c r="H85" s="211"/>
+      <c r="I85" s="211"/>
+      <c r="J85" s="211"/>
+      <c r="K85" s="211"/>
+      <c r="L85" s="211"/>
+      <c r="M85" s="211"/>
+      <c r="N85" s="211"/>
+      <c r="O85" s="211"/>
+      <c r="P85" s="211"/>
+    </row>
+    <row r="86" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E86" s="211"/>
+      <c r="F86" s="211"/>
+      <c r="G86" s="211"/>
+      <c r="H86" s="211"/>
+      <c r="I86" s="211"/>
+      <c r="J86" s="211"/>
+      <c r="K86" s="211"/>
+      <c r="L86" s="211"/>
+      <c r="M86" s="211"/>
+      <c r="N86" s="211"/>
+      <c r="O86" s="211"/>
+      <c r="P86" s="211"/>
+    </row>
+    <row r="87" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E87" s="211"/>
+      <c r="F87" s="211"/>
+      <c r="G87" s="211"/>
+      <c r="H87" s="211"/>
+      <c r="I87" s="211"/>
+      <c r="J87" s="211"/>
+      <c r="K87" s="211"/>
+      <c r="L87" s="211"/>
+      <c r="M87" s="211"/>
+      <c r="N87" s="211"/>
+      <c r="O87" s="211"/>
+      <c r="P87" s="211"/>
+    </row>
+    <row r="88" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E88" s="211"/>
+      <c r="F88" s="211"/>
+      <c r="G88" s="211"/>
+      <c r="H88" s="211"/>
+      <c r="I88" s="211"/>
+      <c r="J88" s="211"/>
+      <c r="K88" s="211"/>
+      <c r="L88" s="211"/>
+      <c r="M88" s="211"/>
+      <c r="N88" s="211"/>
+      <c r="O88" s="211"/>
+      <c r="P88" s="211"/>
+    </row>
+    <row r="89" spans="2:18" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E89" s="211"/>
+      <c r="F89" s="211"/>
+      <c r="G89" s="211"/>
+      <c r="H89" s="211"/>
+      <c r="I89" s="211"/>
+      <c r="J89" s="211"/>
+      <c r="K89" s="211"/>
+      <c r="L89" s="211"/>
+      <c r="M89" s="211"/>
+      <c r="N89" s="211"/>
+      <c r="O89" s="211"/>
+      <c r="P89" s="211"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="R4:R5"/>
-    <mergeCell ref="P2:R2"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="O4:O5"/>
-    <mergeCell ref="G1:P1"/>
-    <mergeCell ref="Q4:Q5"/>
-    <mergeCell ref="M4:M5"/>
-    <mergeCell ref="N4:N5"/>
     <mergeCell ref="E84:P89"/>
     <mergeCell ref="D4:D5"/>
     <mergeCell ref="J4:J5"/>
@@ -8421,6 +8463,14 @@
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="F4:F5"/>
     <mergeCell ref="H4:H5"/>
+    <mergeCell ref="R4:R5"/>
+    <mergeCell ref="P2:R2"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="O4:O5"/>
+    <mergeCell ref="G1:P1"/>
+    <mergeCell ref="Q4:Q5"/>
+    <mergeCell ref="M4:M5"/>
+    <mergeCell ref="N4:N5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -8430,11 +8480,11 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="C5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="5" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C5" s="192" t="s">
-        <v>241</v>
+    <row r="5" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C5" s="189" t="s">
+        <v>226</v>
       </c>
     </row>
   </sheetData>

--- a/GORRITI/Julio/GORRITI-Julio.xlsx
+++ b/GORRITI/Julio/GORRITI-Julio.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\GORRITI\Julio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3184AF86-8984-4942-8751-42002D77C402}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1A6B5D0-D8BB-426D-851E-29D457939FD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -21,14 +21,14 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$R$90</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'PRORRATEO DE PRUEBA  EMERGENCIA'!$A$1:$R$90</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$130</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$131</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="240">
   <si>
     <t>MAIL: consorciogorriti368@gmail.com</t>
   </si>
@@ -732,9 +732,6 @@
     <t>Doartero - compra de materiales iluminacion</t>
   </si>
   <si>
-    <t>PREVISION ORDINARIA</t>
-  </si>
-  <si>
     <t>Sr Oscar - Pintura uf 59</t>
   </si>
   <si>
@@ -742,6 +739,15 @@
   </si>
   <si>
     <t>Presupuesto</t>
+  </si>
+  <si>
+    <t>Efectivo</t>
+  </si>
+  <si>
+    <t>PREVISION ORDINARIA - ADECUACION EDESUR - LIMPIEZA DE TANQUES - GASTOS VARIOS QUE NO SE REALIZAN POR FALTA DE CAJA</t>
+  </si>
+  <si>
+    <t>Ingreso sin identificar ya identificado Diciembre 24</t>
   </si>
 </sst>
 </file>
@@ -1036,7 +1042,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="36">
+  <borders count="37">
     <border>
       <left/>
       <right/>
@@ -1469,14 +1475,30 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="237">
+  <cellXfs count="239">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1646,7 +1668,6 @@
     <xf numFmtId="165" fontId="22" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="7" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="10" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1767,27 +1788,29 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="171" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="170" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1795,32 +1818,30 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="168" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1832,25 +1853,37 @@
     <xf numFmtId="0" fontId="16" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="10" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="20" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="171" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="170" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="7">
     <cellStyle name="Millares" xfId="3" builtinId="3"/>
+    <cellStyle name="Millares 2" xfId="6" xr:uid="{597077D9-9C69-4BDC-9DD8-85C218DCA8E3}"/>
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
     <cellStyle name="Moneda 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Moneda 2 2" xfId="5" xr:uid="{2349FA81-2132-404A-A966-625621B7782C}"/>
+    <cellStyle name="Moneda 3" xfId="4" xr:uid="{665C8742-CD70-4B07-8D73-3FFF859DA874}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2211,7 +2244,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M134"/>
+  <dimension ref="A1:M135"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.5703125" customWidth="1"/>
@@ -2226,37 +2259,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="191"/>
-      <c r="B1" s="192"/>
-      <c r="C1" s="193"/>
-      <c r="D1" s="193"/>
-      <c r="E1" s="194"/>
+      <c r="A1" s="190"/>
+      <c r="B1" s="191"/>
+      <c r="C1" s="192"/>
+      <c r="D1" s="192"/>
+      <c r="E1" s="193"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="15"/>
-      <c r="B2" s="190" t="s">
+      <c r="B2" s="189" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="69"/>
-      <c r="D2" s="190"/>
+      <c r="D2" s="189"/>
       <c r="E2" s="70"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="15"/>
-      <c r="B3" s="190" t="s">
+      <c r="B3" s="189" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="190"/>
-      <c r="D3" s="190"/>
+      <c r="C3" s="189"/>
+      <c r="D3" s="189"/>
       <c r="E3" s="70"/>
     </row>
     <row r="4" spans="1:5" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="15"/>
-      <c r="B4" s="195" t="s">
+      <c r="B4" s="194" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="190"/>
-      <c r="D4" s="196" t="s">
+      <c r="C4" s="189"/>
+      <c r="D4" s="195" t="s">
         <v>3</v>
       </c>
       <c r="E4" s="70"/>
@@ -2279,8 +2312,8 @@
       <c r="B6" s="18" t="s">
         <v>207</v>
       </c>
-      <c r="C6" s="197"/>
-      <c r="D6" s="190" t="s">
+      <c r="C6" s="196"/>
+      <c r="D6" s="189" t="s">
         <v>7</v>
       </c>
       <c r="E6" s="16"/>
@@ -2297,56 +2330,56 @@
       <c r="E7" s="19"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="206" t="s">
+      <c r="B9" s="211" t="s">
         <v>206</v>
       </c>
-      <c r="C9" s="201"/>
+      <c r="C9" s="212"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="201"/>
-      <c r="C10" s="201"/>
+      <c r="B10" s="212"/>
+      <c r="C10" s="212"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B11" s="201"/>
-      <c r="C11" s="201"/>
+      <c r="B11" s="212"/>
+      <c r="C11" s="212"/>
     </row>
     <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="210" t="s">
+      <c r="A14" s="215" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="201"/>
-      <c r="C14" s="201"/>
-      <c r="D14" s="201"/>
-      <c r="E14" s="201"/>
+      <c r="B14" s="212"/>
+      <c r="C14" s="212"/>
+      <c r="D14" s="212"/>
+      <c r="E14" s="212"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="201"/>
-      <c r="B15" s="201"/>
-      <c r="C15" s="201"/>
-      <c r="D15" s="201"/>
-      <c r="E15" s="201"/>
+      <c r="A15" s="212"/>
+      <c r="B15" s="212"/>
+      <c r="C15" s="212"/>
+      <c r="D15" s="212"/>
+      <c r="E15" s="212"/>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="201"/>
-      <c r="B16" s="201"/>
-      <c r="C16" s="201"/>
-      <c r="D16" s="201"/>
-      <c r="E16" s="201"/>
-    </row>
-    <row r="17" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="201"/>
-      <c r="B17" s="201"/>
-      <c r="C17" s="201"/>
-      <c r="D17" s="201"/>
-      <c r="E17" s="201"/>
-    </row>
-    <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="212"/>
+      <c r="B16" s="212"/>
+      <c r="C16" s="212"/>
+      <c r="D16" s="212"/>
+      <c r="E16" s="212"/>
+    </row>
+    <row r="17" spans="1:8" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="212"/>
+      <c r="B17" s="212"/>
+      <c r="C17" s="212"/>
+      <c r="D17" s="212"/>
+      <c r="E17" s="212"/>
+    </row>
+    <row r="18" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:7" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>11</v>
       </c>
@@ -2355,7 +2388,7 @@
       <c r="D21" s="9"/>
       <c r="E21" s="14"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="33" t="s">
         <v>12</v>
       </c>
@@ -2364,121 +2397,129 @@
       <c r="D22" s="32"/>
       <c r="E22" s="32"/>
     </row>
-    <row r="23" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>13</v>
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
-      <c r="D23" s="157">
+      <c r="D23" s="156">
         <v>1271490</v>
       </c>
-      <c r="E23" s="153"/>
-    </row>
-    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E23" s="152"/>
+    </row>
+    <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5"/>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
-      <c r="D24" s="157"/>
+      <c r="D24" s="156"/>
       <c r="E24" s="112"/>
     </row>
-    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5"/>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
-      <c r="D25" s="157"/>
+      <c r="D25" s="156"/>
       <c r="E25" s="112"/>
     </row>
-    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
-      <c r="D26" s="157">
+      <c r="D26" s="156">
         <v>0</v>
       </c>
       <c r="E26" s="112"/>
     </row>
-    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
-      <c r="D27" s="157"/>
+      <c r="D27" s="156"/>
       <c r="E27" s="112"/>
       <c r="G27" s="20"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="56" t="s">
         <v>15</v>
       </c>
       <c r="B28" s="56"/>
       <c r="C28" s="56"/>
-      <c r="D28" s="158">
+      <c r="D28" s="157">
         <f>SUM(D23:D27)</f>
         <v>1271490</v>
       </c>
-      <c r="E28" s="159"/>
-      <c r="G28" s="233">
+      <c r="E28" s="158"/>
+      <c r="G28" s="203">
         <f>D28+D30</f>
         <v>2313543</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>16</v>
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
-      <c r="D29" s="157">
+      <c r="D29" s="156">
         <v>1042053</v>
       </c>
-      <c r="E29" s="153"/>
-      <c r="G29" s="235">
-        <f>-700000-500000</f>
-        <v>-1200000</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E29" s="152"/>
+      <c r="G29" s="205">
+        <f>700000</f>
+        <v>700000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="56" t="s">
         <v>15</v>
       </c>
       <c r="B30" s="56"/>
       <c r="C30" s="56"/>
-      <c r="D30" s="158">
+      <c r="D30" s="157">
         <f>SUM(D29:D29)</f>
         <v>1042053</v>
       </c>
-      <c r="E30" s="159"/>
-      <c r="G30" s="234">
-        <f>G28+G29</f>
-        <v>1113543</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E30" s="158"/>
+      <c r="G30" s="204">
+        <f>G28-G29</f>
+        <v>1613543</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="B31" s="231"/>
-      <c r="C31" s="231"/>
-      <c r="D31" s="157">
+      <c r="B31" s="201"/>
+      <c r="C31" s="201"/>
+      <c r="D31" s="156">
         <v>98440</v>
       </c>
-      <c r="E31" s="183"/>
-      <c r="G31" s="234"/>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E31" s="182"/>
+      <c r="G31" s="204">
+        <v>-500000</v>
+      </c>
+      <c r="H31" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="56" t="s">
         <v>15</v>
       </c>
       <c r="B32" s="56"/>
       <c r="C32" s="56"/>
-      <c r="D32" s="158">
+      <c r="D32" s="157">
         <f>SUM(D31)</f>
         <v>98440</v>
       </c>
-      <c r="E32" s="159"/>
-      <c r="G32" s="234"/>
+      <c r="E32" s="158"/>
+      <c r="G32" s="204">
+        <f>G30+G31</f>
+        <v>1113543</v>
+      </c>
     </row>
     <row r="33" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="50" t="s">
@@ -2487,7 +2528,7 @@
       <c r="B33" s="50"/>
       <c r="C33" s="50"/>
       <c r="D33" s="119"/>
-      <c r="E33" s="161">
+      <c r="E33" s="160">
         <f>D28+D30+D32</f>
         <v>2411983</v>
       </c>
@@ -2499,35 +2540,35 @@
       </c>
       <c r="B34" s="33"/>
       <c r="C34" s="33"/>
-      <c r="D34" s="162"/>
-      <c r="E34" s="163"/>
+      <c r="D34" s="161"/>
+      <c r="E34" s="162"/>
     </row>
     <row r="35" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="209" t="s">
+      <c r="A35" s="214" t="s">
         <v>202</v>
       </c>
-      <c r="B35" s="203"/>
-      <c r="C35" s="183"/>
-      <c r="D35" s="157">
+      <c r="B35" s="210"/>
+      <c r="C35" s="182"/>
+      <c r="D35" s="156">
         <v>60000</v>
       </c>
-      <c r="E35" s="182" t="s">
+      <c r="E35" s="181" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="202" t="s">
+      <c r="A36" s="213" t="s">
         <v>209</v>
       </c>
-      <c r="B36" s="211"/>
+      <c r="B36" s="216"/>
       <c r="C36" s="51"/>
-      <c r="D36" s="157">
+      <c r="D36" s="156">
         <v>249000</v>
       </c>
-      <c r="E36" s="182" t="s">
+      <c r="E36" s="181" t="s">
         <v>210</v>
       </c>
-      <c r="H36" s="137"/>
+      <c r="H36" s="136"/>
     </row>
     <row r="37" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="27" t="s">
@@ -2535,8 +2576,8 @@
       </c>
       <c r="B37" s="27"/>
       <c r="C37" s="27"/>
-      <c r="D37" s="164"/>
-      <c r="E37" s="165">
+      <c r="D37" s="163"/>
+      <c r="E37" s="164">
         <f>SUM(D35:D36)</f>
         <v>309000</v>
       </c>
@@ -2547,28 +2588,28 @@
       </c>
       <c r="B38" s="27"/>
       <c r="C38" s="27"/>
-      <c r="D38" s="166"/>
-      <c r="E38" s="167"/>
+      <c r="D38" s="165"/>
+      <c r="E38" s="166"/>
     </row>
     <row r="39" spans="1:8" s="36" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="204" t="s">
+      <c r="A39" s="209" t="s">
         <v>21</v>
       </c>
-      <c r="B39" s="203"/>
+      <c r="B39" s="210"/>
       <c r="C39" s="53"/>
-      <c r="D39" s="189">
+      <c r="D39" s="188">
         <v>144149</v>
       </c>
-      <c r="E39" s="168" t="s">
+      <c r="E39" s="167" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="204"/>
-      <c r="B40" s="203"/>
+      <c r="A40" s="209"/>
+      <c r="B40" s="210"/>
       <c r="C40" s="53"/>
-      <c r="D40" s="169"/>
-      <c r="E40" s="168"/>
+      <c r="D40" s="168"/>
+      <c r="E40" s="167"/>
     </row>
     <row r="41" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="27" t="s">
@@ -2576,7 +2617,7 @@
       </c>
       <c r="B41" s="27"/>
       <c r="C41" s="27"/>
-      <c r="D41" s="164"/>
+      <c r="D41" s="163"/>
       <c r="E41" s="113">
         <f>SUM(D39:D40)</f>
         <v>144149</v>
@@ -2586,10 +2627,10 @@
       <c r="A42" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="B42" s="154"/>
-      <c r="C42" s="154"/>
-      <c r="D42" s="170"/>
-      <c r="E42" s="171"/>
+      <c r="B42" s="153"/>
+      <c r="C42" s="153"/>
+      <c r="D42" s="169"/>
+      <c r="E42" s="170"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
@@ -2597,13 +2638,13 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="51"/>
-      <c r="D43" s="232">
+      <c r="D43" s="202">
         <v>2581613.04</v>
       </c>
-      <c r="E43" s="172" t="s">
+      <c r="E43" s="171" t="s">
         <v>223</v>
       </c>
-      <c r="G43" s="137"/>
+      <c r="G43" s="136"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
@@ -2613,10 +2654,10 @@
         <v>25</v>
       </c>
       <c r="C44" s="5"/>
-      <c r="D44" s="169">
+      <c r="D44" s="168">
         <v>202628.43</v>
       </c>
-      <c r="E44" s="173" t="s">
+      <c r="E44" s="172" t="s">
         <v>217</v>
       </c>
     </row>
@@ -2629,10 +2670,10 @@
         <v>26</v>
       </c>
       <c r="C45" s="5"/>
-      <c r="D45" s="169">
+      <c r="D45" s="168">
         <v>365477.51</v>
       </c>
-      <c r="E45" s="173" t="str">
+      <c r="E45" s="172" t="str">
         <f>E44</f>
         <v>Debito 14/07</v>
       </c>
@@ -2646,10 +2687,10 @@
         <v>27</v>
       </c>
       <c r="C46" s="5"/>
-      <c r="D46" s="169">
+      <c r="D46" s="168">
         <v>22514.27</v>
       </c>
-      <c r="E46" s="174" t="str">
+      <c r="E46" s="173" t="str">
         <f>E45</f>
         <v>Debito 14/07</v>
       </c>
@@ -2658,9 +2699,9 @@
       <c r="A47" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="B47" s="154"/>
-      <c r="C47" s="154"/>
-      <c r="D47" s="175"/>
+      <c r="B47" s="153"/>
+      <c r="C47" s="153"/>
+      <c r="D47" s="174"/>
       <c r="E47" s="113">
         <f>SUM(D43:D46)</f>
         <v>3172233.2500000005</v>
@@ -2670,10 +2711,10 @@
       <c r="A48" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="B48" s="154"/>
-      <c r="C48" s="154"/>
-      <c r="D48" s="170"/>
-      <c r="E48" s="171"/>
+      <c r="B48" s="153"/>
+      <c r="C48" s="153"/>
+      <c r="D48" s="169"/>
+      <c r="E48" s="170"/>
     </row>
     <row r="49" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
@@ -2681,10 +2722,10 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
-      <c r="D49" s="169">
+      <c r="D49" s="168">
         <v>918866.69</v>
       </c>
-      <c r="E49" s="180" t="s">
+      <c r="E49" s="179" t="s">
         <v>213</v>
       </c>
     </row>
@@ -2692,12 +2733,12 @@
       <c r="A50" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B50" s="185"/>
+      <c r="B50" s="184"/>
       <c r="C50" s="5"/>
-      <c r="D50" s="169">
+      <c r="D50" s="168">
         <v>23882.62</v>
       </c>
-      <c r="E50" s="180" t="s">
+      <c r="E50" s="179" t="s">
         <v>213</v>
       </c>
     </row>
@@ -2707,10 +2748,10 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
-      <c r="D51" s="169">
+      <c r="D51" s="168">
         <v>14748.22</v>
       </c>
-      <c r="E51" s="176" t="str">
+      <c r="E51" s="175" t="str">
         <f>E50</f>
         <v>Transf 07/07</v>
       </c>
@@ -2719,12 +2760,12 @@
       <c r="A52" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B52" s="185"/>
+      <c r="B52" s="184"/>
       <c r="C52" s="5"/>
-      <c r="D52" s="169">
+      <c r="D52" s="168">
         <v>12392.89</v>
       </c>
-      <c r="E52" s="180" t="str">
+      <c r="E52" s="179" t="str">
         <f>E51</f>
         <v>Transf 07/07</v>
       </c>
@@ -2735,10 +2776,10 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5"/>
-      <c r="D53" s="169">
+      <c r="D53" s="168">
         <v>9890.09</v>
       </c>
-      <c r="E53" s="186" t="s">
+      <c r="E53" s="185" t="s">
         <v>211</v>
       </c>
     </row>
@@ -2748,10 +2789,10 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
-      <c r="D54" s="169">
+      <c r="D54" s="168">
         <v>1474687.08</v>
       </c>
-      <c r="E54" s="186" t="s">
+      <c r="E54" s="185" t="s">
         <v>224</v>
       </c>
     </row>
@@ -2761,32 +2802,32 @@
       </c>
       <c r="B55" s="5"/>
       <c r="C55" s="5"/>
-      <c r="D55" s="169">
+      <c r="D55" s="168">
         <v>23728.51</v>
       </c>
-      <c r="E55" s="186" t="s">
+      <c r="E55" s="185" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="204" t="s">
+      <c r="A56" s="209" t="s">
         <v>35</v>
       </c>
-      <c r="B56" s="203"/>
+      <c r="B56" s="210"/>
       <c r="C56" s="5"/>
-      <c r="D56" s="169">
+      <c r="D56" s="168">
         <v>2168902.4500000002</v>
       </c>
-      <c r="E56" s="186" t="s">
+      <c r="E56" s="185" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="204"/>
-      <c r="B57" s="203"/>
-      <c r="C57" s="155"/>
-      <c r="D57" s="207"/>
-      <c r="E57" s="208"/>
+      <c r="A57" s="209"/>
+      <c r="B57" s="210"/>
+      <c r="C57" s="154"/>
+      <c r="D57" s="206"/>
+      <c r="E57" s="207"/>
     </row>
     <row r="58" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="27" t="s">
@@ -2794,7 +2835,7 @@
       </c>
       <c r="B58" s="27"/>
       <c r="C58" s="27"/>
-      <c r="D58" s="164"/>
+      <c r="D58" s="163"/>
       <c r="E58" s="113">
         <f>SUM(D49:D57)</f>
         <v>4647098.55</v>
@@ -2806,19 +2847,19 @@
       </c>
       <c r="B59" s="27"/>
       <c r="C59" s="27"/>
-      <c r="D59" s="164"/>
-      <c r="E59" s="177"/>
+      <c r="D59" s="163"/>
+      <c r="E59" s="176"/>
     </row>
     <row r="60" spans="1:5" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="202" t="s">
+      <c r="A60" s="213" t="s">
         <v>228</v>
       </c>
-      <c r="B60" s="203"/>
+      <c r="B60" s="210"/>
       <c r="C60" s="54"/>
-      <c r="D60" s="169">
+      <c r="D60" s="168">
         <v>48400</v>
       </c>
-      <c r="E60" s="180" t="s">
+      <c r="E60" s="179" t="s">
         <v>229</v>
       </c>
     </row>
@@ -2826,12 +2867,12 @@
       <c r="A61" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B61" s="156"/>
+      <c r="B61" s="155"/>
       <c r="C61" s="5"/>
-      <c r="D61" s="169">
+      <c r="D61" s="168">
         <v>55700</v>
       </c>
-      <c r="E61" s="180" t="s">
+      <c r="E61" s="179" t="s">
         <v>212</v>
       </c>
     </row>
@@ -2839,119 +2880,119 @@
       <c r="A62" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B62" s="156"/>
+      <c r="B62" s="155"/>
       <c r="C62" s="5"/>
-      <c r="D62" s="169">
+      <c r="D62" s="168">
         <v>135000</v>
       </c>
-      <c r="E62" s="181" t="s">
+      <c r="E62" s="180" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="202" t="s">
+      <c r="A63" s="213" t="s">
         <v>225</v>
       </c>
-      <c r="B63" s="211"/>
+      <c r="B63" s="216"/>
       <c r="C63" s="5"/>
-      <c r="D63" s="169">
+      <c r="D63" s="168">
         <v>770000</v>
       </c>
-      <c r="E63" s="181" t="s">
+      <c r="E63" s="180" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="202" t="s">
+      <c r="A64" s="213" t="s">
         <v>232</v>
       </c>
-      <c r="B64" s="211"/>
+      <c r="B64" s="216"/>
       <c r="C64" s="5"/>
-      <c r="D64" s="169">
-        <v>40000</v>
-      </c>
-      <c r="E64" s="181" t="s">
+      <c r="D64" s="168">
+        <v>40020.120000000003</v>
+      </c>
+      <c r="E64" s="180" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="65" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="202" t="s">
+      <c r="A65" s="213" t="s">
         <v>227</v>
       </c>
-      <c r="B65" s="211"/>
-      <c r="C65" s="228"/>
+      <c r="B65" s="216"/>
+      <c r="C65" s="199"/>
       <c r="D65" s="116">
         <v>300000</v>
       </c>
-      <c r="E65" s="181" t="s">
+      <c r="E65" s="180" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="66" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="202" t="s">
+      <c r="A66" s="213" t="s">
         <v>233</v>
       </c>
-      <c r="B66" s="211"/>
+      <c r="B66" s="216"/>
       <c r="C66" s="51"/>
       <c r="D66" s="116">
         <v>125475</v>
       </c>
-      <c r="E66" s="181" t="s">
+      <c r="E66" s="180" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="67" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="202" t="s">
+      <c r="A67" s="213" t="s">
         <v>214</v>
       </c>
-      <c r="B67" s="203"/>
+      <c r="B67" s="210"/>
       <c r="C67" s="5"/>
       <c r="D67" s="116">
         <v>150000</v>
       </c>
-      <c r="E67" s="181" t="s">
+      <c r="E67" s="180" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="68" spans="1:10" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="202" t="s">
+      <c r="A68" s="213" t="s">
         <v>216</v>
       </c>
-      <c r="B68" s="211"/>
+      <c r="B68" s="216"/>
       <c r="C68" s="5"/>
       <c r="D68" s="116">
         <f>65050+57650</f>
         <v>122700</v>
       </c>
-      <c r="E68" s="181" t="s">
+      <c r="E68" s="180" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="198" t="s">
-        <v>235</v>
-      </c>
-      <c r="B69" s="199"/>
+      <c r="A69" s="197" t="s">
+        <v>234</v>
+      </c>
+      <c r="B69" s="198"/>
       <c r="C69" s="5"/>
       <c r="D69" s="116">
-        <v>280000</v>
-      </c>
-      <c r="E69" s="181"/>
+        <v>390000</v>
+      </c>
+      <c r="E69" s="180"/>
     </row>
     <row r="70" spans="1:10" ht="22.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="204" t="s">
+      <c r="A70" s="209" t="s">
         <v>220</v>
       </c>
-      <c r="B70" s="203"/>
+      <c r="B70" s="210"/>
       <c r="C70" s="5"/>
       <c r="D70" s="116">
         <v>8000</v>
       </c>
-      <c r="E70" s="181" t="s">
+      <c r="E70" s="180" t="s">
         <v>218</v>
       </c>
-      <c r="I70" s="204"/>
-      <c r="J70" s="203"/>
+      <c r="I70" s="209"/>
+      <c r="J70" s="210"/>
     </row>
     <row r="71" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="27" t="s">
@@ -2960,9 +3001,9 @@
       <c r="B71" s="33"/>
       <c r="C71" s="33"/>
       <c r="D71" s="32"/>
-      <c r="E71" s="178">
+      <c r="E71" s="177">
         <f>SUM(D60:D70)</f>
-        <v>2035275</v>
+        <v>2145295.12</v>
       </c>
     </row>
     <row r="72" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2971,8 +3012,8 @@
       </c>
       <c r="B72" s="67"/>
       <c r="C72" s="27"/>
-      <c r="D72" s="160"/>
-      <c r="E72" s="177"/>
+      <c r="D72" s="159"/>
+      <c r="E72" s="176"/>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
@@ -2980,11 +3021,11 @@
       </c>
       <c r="B73" s="5"/>
       <c r="C73" s="5"/>
-      <c r="D73" s="169">
+      <c r="D73" s="168">
         <f>156032.49</f>
         <v>156032.49</v>
       </c>
-      <c r="E73" s="179"/>
+      <c r="E73" s="178"/>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
@@ -2992,7 +3033,7 @@
       </c>
       <c r="B74" s="5"/>
       <c r="C74" s="5"/>
-      <c r="D74" s="169"/>
+      <c r="D74" s="168"/>
       <c r="E74" s="118"/>
       <c r="G74" t="s">
         <v>221</v>
@@ -3017,19 +3058,21 @@
       <c r="D76" s="112"/>
       <c r="E76" s="120"/>
     </row>
-    <row r="77" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="28" t="s">
-        <v>234</v>
-      </c>
-      <c r="B77" s="28"/>
-      <c r="C77" s="28"/>
-      <c r="D77" s="121"/>
-      <c r="E77" s="122"/>
+    <row r="77" spans="1:10" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="219" t="s">
+        <v>238</v>
+      </c>
+      <c r="B77" s="220"/>
+      <c r="C77" s="220"/>
+      <c r="D77" s="221"/>
+      <c r="E77" s="121">
+        <v>1500000</v>
+      </c>
     </row>
     <row r="78" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="1"/>
-      <c r="D78" s="123"/>
-      <c r="E78" s="124"/>
+      <c r="D78" s="122"/>
+      <c r="E78" s="123"/>
       <c r="F78" s="42"/>
     </row>
     <row r="79" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -3038,22 +3081,22 @@
       </c>
       <c r="B79" s="10"/>
       <c r="C79" s="4"/>
-      <c r="D79" s="125"/>
-      <c r="E79" s="229">
+      <c r="D79" s="124"/>
+      <c r="E79" s="200">
         <f>(SUM(E30:E77))</f>
-        <v>12875771.290000001</v>
-      </c>
-      <c r="F79" s="152"/>
+        <v>14485791.410000002</v>
+      </c>
+      <c r="F79" s="151"/>
       <c r="G79" s="42"/>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D80" s="123"/>
-      <c r="E80" s="123"/>
-      <c r="G80" s="152"/>
+      <c r="D80" s="122"/>
+      <c r="E80" s="122"/>
+      <c r="G80" s="151"/>
     </row>
     <row r="81" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D81" s="123"/>
-      <c r="E81" s="123"/>
+      <c r="D81" s="122"/>
+      <c r="E81" s="122"/>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="11" t="s">
@@ -3061,26 +3104,26 @@
       </c>
       <c r="B82" s="12"/>
       <c r="C82" s="13"/>
-      <c r="D82" s="126"/>
-      <c r="E82" s="127"/>
+      <c r="D82" s="125"/>
+      <c r="E82" s="126"/>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83" s="204"/>
-      <c r="B83" s="203"/>
+      <c r="A83" s="209"/>
+      <c r="B83" s="210"/>
       <c r="C83" s="5"/>
-      <c r="D83" s="142"/>
+      <c r="D83" s="141"/>
       <c r="E83" s="114"/>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A84" s="204"/>
-      <c r="B84" s="203"/>
+      <c r="A84" s="209"/>
+      <c r="B84" s="210"/>
       <c r="C84" s="5"/>
       <c r="D84" s="116"/>
       <c r="E84" s="114"/>
     </row>
     <row r="85" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="202"/>
-      <c r="B85" s="203"/>
+      <c r="A85" s="213"/>
+      <c r="B85" s="210"/>
       <c r="C85" s="5"/>
       <c r="D85" s="116"/>
       <c r="E85" s="114"/>
@@ -3133,7 +3176,7 @@
       </c>
       <c r="B94" s="109">
         <f>E79</f>
-        <v>12875771.290000001</v>
+        <v>14485791.410000002</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -3142,7 +3185,7 @@
       </c>
       <c r="B95" s="109">
         <f>E79-E77</f>
-        <v>12875771.290000001</v>
+        <v>12985791.410000002</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -3165,31 +3208,31 @@
     </row>
     <row r="98" spans="1:5" ht="34.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="99" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="200"/>
-      <c r="B99" s="201"/>
-      <c r="C99" s="201"/>
-      <c r="D99" s="201"/>
-      <c r="E99" s="201"/>
+      <c r="A99" s="217"/>
+      <c r="B99" s="212"/>
+      <c r="C99" s="212"/>
+      <c r="D99" s="212"/>
+      <c r="E99" s="212"/>
     </row>
     <row r="100" spans="1:5" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="201"/>
-      <c r="B100" s="201"/>
-      <c r="C100" s="201"/>
-      <c r="D100" s="201"/>
-      <c r="E100" s="201"/>
+      <c r="A100" s="212"/>
+      <c r="B100" s="212"/>
+      <c r="C100" s="212"/>
+      <c r="D100" s="212"/>
+      <c r="E100" s="212"/>
     </row>
     <row r="101" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="201"/>
-      <c r="B101" s="201"/>
-      <c r="C101" s="201"/>
-      <c r="D101" s="201"/>
-      <c r="E101" s="201"/>
+      <c r="A101" s="212"/>
+      <c r="B101" s="212"/>
+      <c r="C101" s="212"/>
+      <c r="D101" s="212"/>
+      <c r="E101" s="212"/>
     </row>
     <row r="103" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="B103" s="138"/>
+      <c r="B103" s="137"/>
       <c r="C103" s="22"/>
     </row>
     <row r="104" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
@@ -3205,7 +3248,7 @@
       </c>
       <c r="B105" s="38">
         <f>PRORRATEO!I81</f>
-        <v>12414643.369999997</v>
+        <v>12524643.369999997</v>
       </c>
       <c r="C105" s="22"/>
     </row>
@@ -3221,7 +3264,7 @@
         <v>52</v>
       </c>
       <c r="B107" s="118">
-        <f>B129</f>
+        <f>B130</f>
         <v>0</v>
       </c>
       <c r="C107" s="22"/>
@@ -3232,7 +3275,7 @@
       <c r="C108" s="22"/>
     </row>
     <row r="109" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="132" t="s">
+      <c r="A109" s="131" t="s">
         <v>53</v>
       </c>
       <c r="B109" s="46"/>
@@ -3244,7 +3287,7 @@
       </c>
       <c r="B110" s="46">
         <f>-B95</f>
-        <v>-12875771.290000001</v>
+        <v>-12985791.410000002</v>
       </c>
       <c r="C110" s="22"/>
     </row>
@@ -3264,7 +3307,7 @@
       </c>
       <c r="B112" s="58">
         <f>SUM(B104:B111)</f>
-        <v>-461127.92000000365</v>
+        <v>-461148.04000000469</v>
       </c>
       <c r="C112" s="25"/>
       <c r="D112" s="42"/>
@@ -3273,8 +3316,8 @@
       <c r="B113" s="39"/>
       <c r="C113" s="25"/>
       <c r="D113" s="42"/>
-      <c r="E113" s="139"/>
-      <c r="F113" s="140"/>
+      <c r="E113" s="138"/>
+      <c r="F113" s="139"/>
     </row>
     <row r="114" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B114" s="40"/>
@@ -3285,10 +3328,10 @@
       <c r="C115" s="35"/>
     </row>
     <row r="116" spans="1:6" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="144" t="s">
+      <c r="A116" s="143" t="s">
         <v>56</v>
       </c>
-      <c r="B116" s="145">
+      <c r="B116" s="144">
         <v>412214.68062303029</v>
       </c>
       <c r="C116" s="35"/>
@@ -3298,16 +3341,16 @@
       <c r="A117" s="53" t="s">
         <v>57</v>
       </c>
-      <c r="B117" s="149">
+      <c r="B117" s="148">
         <f>-B95</f>
-        <v>-12875771.290000001</v>
+        <v>-12985791.410000002</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="53" t="s">
         <v>58</v>
       </c>
-      <c r="B118" s="149">
+      <c r="B118" s="148">
         <f>-B96</f>
         <v>0</v>
       </c>
@@ -3316,112 +3359,129 @@
       <c r="A119" s="53" t="s">
         <v>59</v>
       </c>
-      <c r="B119" s="149">
-        <f>B129</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B119" s="148">
+        <f>B130</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A120" s="53" t="s">
+        <v>239</v>
+      </c>
+      <c r="B120" s="208">
+        <v>-112065.15</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A121" s="53" t="s">
         <v>60</v>
       </c>
-      <c r="B120" s="150">
+      <c r="B121" s="149">
         <f>PRORRATEO!I81</f>
-        <v>12414643.369999997</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A121" s="151" t="s">
+        <v>12524643.369999997</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A122" s="150" t="s">
         <v>61</v>
       </c>
-      <c r="B121" s="187"/>
-    </row>
-    <row r="122" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="147" t="s">
+      <c r="B122" s="186"/>
+    </row>
+    <row r="123" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A123" s="146" t="s">
         <v>62</v>
       </c>
-      <c r="B122" s="148">
-        <f>SUM(B116:C121)</f>
-        <v>-48913.239376973361</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A123" s="146"/>
-      <c r="B123" s="146"/>
-    </row>
-    <row r="124" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A125" s="205" t="s">
+      <c r="B123" s="147">
+        <f>SUM(B116:C122)</f>
+        <v>-160998.50937697478</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A124" s="145"/>
+      <c r="B124" s="145"/>
+    </row>
+    <row r="125" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A126" s="218" t="s">
         <v>63</v>
       </c>
-      <c r="B125" s="201"/>
-      <c r="C125" s="201"/>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A126" s="201"/>
-      <c r="B126" s="201"/>
-      <c r="C126" s="201"/>
-    </row>
-    <row r="127" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="129"/>
-      <c r="B127" s="34"/>
-      <c r="C127" s="34">
+      <c r="B126" s="212"/>
+      <c r="C126" s="212"/>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A127" s="212"/>
+      <c r="B127" s="212"/>
+      <c r="C127" s="212"/>
+    </row>
+    <row r="128" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A128" s="128"/>
+      <c r="B128" s="34"/>
+      <c r="C128" s="34">
         <v>40000</v>
       </c>
     </row>
-    <row r="128" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="129"/>
-      <c r="B128" s="131"/>
-      <c r="C128" s="39"/>
-    </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A129" s="43" t="s">
+    <row r="129" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A129" s="128"/>
+      <c r="B129" s="130"/>
+      <c r="C129" s="39"/>
+    </row>
+    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A130" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="B129" s="130">
-        <f>SUM(B127:B128)</f>
-        <v>0</v>
-      </c>
-      <c r="C129" s="44"/>
-    </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="M130" s="8"/>
-    </row>
-    <row r="131" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="200"/>
-      <c r="B131" s="201"/>
-      <c r="C131" s="201"/>
-      <c r="D131" s="201"/>
-      <c r="E131" s="201"/>
-    </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A132" s="201"/>
-      <c r="B132" s="201"/>
-      <c r="C132" s="201"/>
-      <c r="D132" s="201"/>
-      <c r="E132" s="201"/>
+      <c r="B130" s="129">
+        <f>SUM(B128:B129)</f>
+        <v>0</v>
+      </c>
+      <c r="C130" s="44"/>
+    </row>
+    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M131" s="8"/>
+    </row>
+    <row r="132" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A132" s="217"/>
+      <c r="B132" s="212"/>
+      <c r="C132" s="212"/>
+      <c r="D132" s="212"/>
+      <c r="E132" s="212"/>
     </row>
     <row r="133" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A133" s="201"/>
-      <c r="B133" s="201"/>
-      <c r="C133" s="201"/>
-      <c r="D133" s="201"/>
-      <c r="E133" s="201"/>
+      <c r="A133" s="212"/>
+      <c r="B133" s="212"/>
+      <c r="C133" s="212"/>
+      <c r="D133" s="212"/>
+      <c r="E133" s="212"/>
     </row>
     <row r="134" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A134" s="201"/>
-      <c r="B134" s="201"/>
-      <c r="C134" s="201"/>
-      <c r="D134" s="201"/>
-      <c r="E134" s="201"/>
+      <c r="A134" s="212"/>
+      <c r="B134" s="212"/>
+      <c r="C134" s="212"/>
+      <c r="D134" s="212"/>
+      <c r="E134" s="212"/>
+    </row>
+    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A135" s="212"/>
+      <c r="B135" s="212"/>
+      <c r="C135" s="212"/>
+      <c r="D135" s="212"/>
+      <c r="E135" s="212"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A132:E135"/>
+    <mergeCell ref="A99:E101"/>
+    <mergeCell ref="A85:B85"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="A84:B84"/>
+    <mergeCell ref="A83:B83"/>
+    <mergeCell ref="A126:C127"/>
+    <mergeCell ref="A77:D77"/>
     <mergeCell ref="I70:J70"/>
     <mergeCell ref="B9:C11"/>
     <mergeCell ref="A67:B67"/>
     <mergeCell ref="A70:B70"/>
-    <mergeCell ref="D57:E57"/>
     <mergeCell ref="A39:B39"/>
     <mergeCell ref="A35:B35"/>
     <mergeCell ref="A14:E17"/>
@@ -3432,15 +3492,6 @@
     <mergeCell ref="A40:B40"/>
     <mergeCell ref="A56:B56"/>
     <mergeCell ref="A66:B66"/>
-    <mergeCell ref="A131:E134"/>
-    <mergeCell ref="A99:E101"/>
-    <mergeCell ref="A85:B85"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A64:B64"/>
-    <mergeCell ref="A60:B60"/>
-    <mergeCell ref="A84:B84"/>
-    <mergeCell ref="A83:B83"/>
-    <mergeCell ref="A125:C126"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3483,16 +3534,16 @@
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
       <c r="F1" s="6"/>
-      <c r="G1" s="225"/>
-      <c r="H1" s="201"/>
-      <c r="I1" s="201"/>
-      <c r="J1" s="201"/>
-      <c r="K1" s="201"/>
-      <c r="L1" s="201"/>
-      <c r="M1" s="201"/>
-      <c r="N1" s="201"/>
-      <c r="O1" s="201"/>
-      <c r="P1" s="201"/>
+      <c r="G1" s="228"/>
+      <c r="H1" s="212"/>
+      <c r="I1" s="212"/>
+      <c r="J1" s="212"/>
+      <c r="K1" s="212"/>
+      <c r="L1" s="212"/>
+      <c r="M1" s="212"/>
+      <c r="N1" s="212"/>
+      <c r="O1" s="212"/>
+      <c r="P1" s="212"/>
       <c r="Q1" s="6"/>
       <c r="R1" s="6"/>
     </row>
@@ -3517,12 +3568,16 @@
       <c r="M2" s="7"/>
       <c r="N2" s="6"/>
       <c r="O2" s="6"/>
-      <c r="P2" s="222">
-        <v>12376831.439999999</v>
-      </c>
-      <c r="Q2" s="201"/>
-      <c r="R2" s="201"/>
+      <c r="P2" s="224">
+        <f>U2</f>
+        <v>14485791.410000002</v>
+      </c>
+      <c r="Q2" s="212"/>
+      <c r="R2" s="212"/>
       <c r="S2" s="20"/>
+      <c r="U2">
+        <v>14485791.410000002</v>
+      </c>
     </row>
     <row r="3" spans="1:21" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
@@ -3545,82 +3600,82 @@
       <c r="R3" s="59"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A4" s="217" t="s">
+      <c r="A4" s="235" t="s">
         <v>65</v>
       </c>
-      <c r="B4" s="219" t="s">
+      <c r="B4" s="237" t="s">
         <v>66</v>
       </c>
-      <c r="C4" s="133"/>
-      <c r="D4" s="212" t="s">
+      <c r="C4" s="132"/>
+      <c r="D4" s="225" t="s">
         <v>67</v>
       </c>
-      <c r="E4" s="212" t="s">
+      <c r="E4" s="225" t="s">
         <v>68</v>
       </c>
-      <c r="F4" s="214" t="s">
+      <c r="F4" s="234" t="s">
         <v>69</v>
       </c>
-      <c r="G4" s="212" t="s">
+      <c r="G4" s="225" t="s">
         <v>70</v>
       </c>
-      <c r="H4" s="216" t="s">
+      <c r="H4" s="232" t="s">
         <v>71</v>
       </c>
-      <c r="I4" s="212" t="s">
+      <c r="I4" s="225" t="s">
         <v>51</v>
       </c>
-      <c r="J4" s="214" t="s">
+      <c r="J4" s="234" t="s">
         <v>72</v>
       </c>
-      <c r="K4" s="218" t="s">
+      <c r="K4" s="236" t="s">
         <v>73</v>
       </c>
-      <c r="L4" s="216" t="s">
+      <c r="L4" s="232" t="s">
         <v>74</v>
       </c>
-      <c r="M4" s="227" t="s">
+      <c r="M4" s="231" t="s">
         <v>75</v>
       </c>
-      <c r="N4" s="216" t="s">
+      <c r="N4" s="232" t="s">
         <v>76</v>
       </c>
-      <c r="O4" s="223" t="s">
+      <c r="O4" s="226" t="s">
         <v>77</v>
       </c>
       <c r="P4" s="62" t="s">
         <v>78</v>
       </c>
-      <c r="Q4" s="226" t="s">
+      <c r="Q4" s="229" t="s">
         <v>79</v>
       </c>
-      <c r="R4" s="221" t="s">
+      <c r="R4" s="222" t="s">
         <v>80</v>
       </c>
       <c r="U4" s="42"/>
     </row>
     <row r="5" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="213"/>
-      <c r="B5" s="220"/>
-      <c r="C5" s="134"/>
-      <c r="D5" s="213"/>
-      <c r="E5" s="213"/>
-      <c r="F5" s="215"/>
-      <c r="G5" s="213"/>
-      <c r="H5" s="215"/>
-      <c r="I5" s="213"/>
-      <c r="J5" s="215"/>
-      <c r="K5" s="215"/>
-      <c r="L5" s="215"/>
-      <c r="M5" s="213"/>
-      <c r="N5" s="215"/>
-      <c r="O5" s="224"/>
+      <c r="A5" s="223"/>
+      <c r="B5" s="230"/>
+      <c r="C5" s="133"/>
+      <c r="D5" s="223"/>
+      <c r="E5" s="223"/>
+      <c r="F5" s="233"/>
+      <c r="G5" s="223"/>
+      <c r="H5" s="233"/>
+      <c r="I5" s="223"/>
+      <c r="J5" s="233"/>
+      <c r="K5" s="233"/>
+      <c r="L5" s="233"/>
+      <c r="M5" s="223"/>
+      <c r="N5" s="233"/>
+      <c r="O5" s="227"/>
       <c r="P5" s="60" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 14/08</v>
       </c>
-      <c r="Q5" s="220"/>
-      <c r="R5" s="213"/>
+      <c r="Q5" s="230"/>
+      <c r="R5" s="223"/>
     </row>
     <row r="6" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
@@ -3643,7 +3698,7 @@
       <c r="H6" s="72">
         <v>63505.01</v>
       </c>
-      <c r="I6" s="230">
+      <c r="I6" s="73">
         <f>786304-I13-I7-I47-I48-I59-I69-I73</f>
         <v>63505.19</v>
       </c>
@@ -3661,22 +3716,22 @@
       </c>
       <c r="N6" s="77">
         <f t="shared" ref="N6:N37" si="2">P$2*G6%</f>
-        <v>63505.522118640001</v>
+        <v>74326.595724710016</v>
       </c>
       <c r="O6" s="78">
         <v>0</v>
       </c>
       <c r="P6" s="79">
         <f t="shared" ref="P6:P37" si="3">ROUND(SUM(K6:O6),0) + S6</f>
-        <v>63505.01</v>
+        <v>74326.009999999995</v>
       </c>
       <c r="Q6" s="80">
         <f t="shared" ref="Q6:Q37" si="4">ROUND(P6*6% + P6,0) + S6</f>
-        <v>67315.009999999995</v>
+        <v>78786.009999999995</v>
       </c>
       <c r="R6" s="81">
         <f t="shared" ref="R6:R37" si="5">ROUND(P6*3%,0) + P6</f>
-        <v>65410.01</v>
+        <v>76556.009999999995</v>
       </c>
       <c r="S6" s="42">
         <v>0.01</v>
@@ -3707,8 +3762,8 @@
       <c r="H7" s="72">
         <v>75734.02</v>
       </c>
-      <c r="I7" s="230">
-        <f>H7</f>
+      <c r="I7" s="73">
+        <f t="shared" ref="I7:I13" si="7">H7</f>
         <v>75734.02</v>
       </c>
       <c r="J7" s="74"/>
@@ -3725,25 +3780,25 @@
       </c>
       <c r="N7" s="77">
         <f t="shared" si="2"/>
-        <v>75733.831581360006</v>
+        <v>88638.557637790014</v>
       </c>
       <c r="O7" s="78">
         <v>0</v>
       </c>
       <c r="P7" s="79">
         <f t="shared" si="3"/>
-        <v>75734.02</v>
+        <v>88639.02</v>
       </c>
       <c r="Q7" s="80">
         <f t="shared" si="4"/>
-        <v>80278.02</v>
+        <v>93957.02</v>
       </c>
       <c r="R7" s="81">
         <f t="shared" si="5"/>
-        <v>78006.02</v>
+        <v>91298.02</v>
       </c>
       <c r="S7" s="42">
-        <f t="shared" ref="S7:S38" si="7">S6+0.01</f>
+        <f t="shared" ref="S7:S38" si="8">S6+0.01</f>
         <v>0.02</v>
       </c>
       <c r="T7" s="42"/>
@@ -3770,8 +3825,8 @@
       <c r="H8" s="72">
         <v>75684.03</v>
       </c>
-      <c r="I8" s="230">
-        <f>H8</f>
+      <c r="I8" s="73">
+        <f t="shared" si="7"/>
         <v>75684.03</v>
       </c>
       <c r="J8" s="74"/>
@@ -3788,25 +3843,25 @@
       </c>
       <c r="N8" s="77">
         <f t="shared" si="2"/>
-        <v>75684.324255600004</v>
+        <v>88580.614472150017</v>
       </c>
       <c r="O8" s="78">
         <v>0</v>
       </c>
       <c r="P8" s="79">
         <f t="shared" si="3"/>
-        <v>75684.03</v>
+        <v>88581.03</v>
       </c>
       <c r="Q8" s="80">
         <f t="shared" si="4"/>
-        <v>80225.03</v>
+        <v>93896.03</v>
       </c>
       <c r="R8" s="81">
         <f t="shared" si="5"/>
-        <v>77955.03</v>
+        <v>91238.03</v>
       </c>
       <c r="S8" s="42">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.03</v>
       </c>
     </row>
@@ -3832,8 +3887,8 @@
       <c r="H9" s="72">
         <v>62293.04</v>
       </c>
-      <c r="I9" s="230">
-        <f>H9</f>
+      <c r="I9" s="73">
+        <f t="shared" si="7"/>
         <v>62293.04</v>
       </c>
       <c r="J9" s="74"/>
@@ -3850,25 +3905,25 @@
       </c>
       <c r="N9" s="77">
         <f t="shared" si="2"/>
-        <v>62292.592637519985</v>
+        <v>72906.988166530005</v>
       </c>
       <c r="O9" s="78">
         <v>0</v>
       </c>
       <c r="P9" s="79">
         <f t="shared" si="3"/>
-        <v>62293.04</v>
+        <v>72907.039999999994</v>
       </c>
       <c r="Q9" s="80">
         <f t="shared" si="4"/>
-        <v>66031.039999999994</v>
+        <v>77281.039999999994</v>
       </c>
       <c r="R9" s="81">
         <f t="shared" si="5"/>
-        <v>64162.04</v>
+        <v>75094.039999999994</v>
       </c>
       <c r="S9" s="42">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.04</v>
       </c>
       <c r="U9" s="42"/>
@@ -3895,8 +3950,8 @@
       <c r="H10" s="72">
         <v>62293.05</v>
       </c>
-      <c r="I10" s="230">
-        <f>H10</f>
+      <c r="I10" s="73">
+        <f t="shared" si="7"/>
         <v>62293.05</v>
       </c>
       <c r="J10" s="74"/>
@@ -3913,25 +3968,25 @@
       </c>
       <c r="N10" s="77">
         <f t="shared" si="2"/>
-        <v>62292.592637519985</v>
+        <v>72906.988166530005</v>
       </c>
       <c r="O10" s="78">
         <v>0</v>
       </c>
       <c r="P10" s="79">
         <f t="shared" si="3"/>
-        <v>62293.05</v>
+        <v>72907.05</v>
       </c>
       <c r="Q10" s="80">
         <f t="shared" si="4"/>
-        <v>66031.05</v>
+        <v>77281.05</v>
       </c>
       <c r="R10" s="81">
         <f t="shared" si="5"/>
-        <v>64162.05</v>
+        <v>75094.05</v>
       </c>
       <c r="S10" s="42">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.05</v>
       </c>
       <c r="U10" s="42"/>
@@ -3960,8 +4015,8 @@
       <c r="H11" s="72">
         <v>92814.06</v>
       </c>
-      <c r="I11" s="230">
-        <f>H11</f>
+      <c r="I11" s="73">
+        <f t="shared" si="7"/>
         <v>92814.06</v>
       </c>
       <c r="J11" s="74"/>
@@ -3978,25 +4033,25 @@
       </c>
       <c r="N11" s="77">
         <f t="shared" si="2"/>
-        <v>92813.858968560002</v>
+        <v>108628.94978359003</v>
       </c>
       <c r="O11" s="78">
         <v>0</v>
       </c>
       <c r="P11" s="79">
         <f t="shared" si="3"/>
-        <v>92814.06</v>
+        <v>108629.06</v>
       </c>
       <c r="Q11" s="80">
         <f t="shared" si="4"/>
-        <v>98383.06</v>
+        <v>115147.06</v>
       </c>
       <c r="R11" s="81">
         <f t="shared" si="5"/>
-        <v>95598.06</v>
+        <v>111888.06</v>
       </c>
       <c r="S11" s="42">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
@@ -4024,8 +4079,8 @@
       <c r="H12" s="72">
         <v>67144.070000000007</v>
       </c>
-      <c r="I12" s="230">
-        <f>H12</f>
+      <c r="I12" s="73">
+        <f t="shared" si="7"/>
         <v>67144.070000000007</v>
       </c>
       <c r="J12" s="74"/>
@@ -4042,25 +4097,25 @@
       </c>
       <c r="N12" s="77">
         <f t="shared" si="2"/>
-        <v>67144.310561999999</v>
+        <v>78585.418399250018</v>
       </c>
       <c r="O12" s="78">
         <v>0</v>
       </c>
       <c r="P12" s="79">
         <f t="shared" si="3"/>
-        <v>67144.070000000007</v>
+        <v>78585.070000000007</v>
       </c>
       <c r="Q12" s="80">
         <f t="shared" si="4"/>
-        <v>71173.070000000007</v>
+        <v>83300.070000000007</v>
       </c>
       <c r="R12" s="81">
         <f t="shared" si="5"/>
-        <v>69158.070000000007</v>
+        <v>80943.070000000007</v>
       </c>
       <c r="S12" s="42">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
@@ -4086,8 +4141,8 @@
       <c r="H13" s="72">
         <v>56154.080000000002</v>
       </c>
-      <c r="I13" s="230">
-        <f>H13</f>
+      <c r="I13" s="73">
+        <f t="shared" si="7"/>
         <v>56154.080000000002</v>
       </c>
       <c r="J13" s="74"/>
@@ -4104,25 +4159,25 @@
       </c>
       <c r="N13" s="77">
         <f t="shared" si="2"/>
-        <v>56153.684243280004</v>
+        <v>65722.035627170015</v>
       </c>
       <c r="O13" s="78">
         <v>0</v>
       </c>
       <c r="P13" s="79">
         <f t="shared" si="3"/>
-        <v>56154.080000000002</v>
+        <v>65722.080000000002</v>
       </c>
       <c r="Q13" s="80">
         <f t="shared" si="4"/>
-        <v>59523.08</v>
+        <v>69665.08</v>
       </c>
       <c r="R13" s="81">
         <f t="shared" si="5"/>
-        <v>57839.08</v>
+        <v>67694.080000000002</v>
       </c>
       <c r="S13" s="42">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.08</v>
       </c>
     </row>
@@ -4150,7 +4205,7 @@
       <c r="H14" s="72">
         <v>131755.09</v>
       </c>
-      <c r="I14" s="230">
+      <c r="I14" s="73">
         <v>200000.09</v>
       </c>
       <c r="J14" s="74"/>
@@ -4167,25 +4222,25 @@
       </c>
       <c r="N14" s="77">
         <f t="shared" si="2"/>
-        <v>64904.104071359994</v>
+        <v>75963.490154040002</v>
       </c>
       <c r="O14" s="78">
         <v>0</v>
       </c>
       <c r="P14" s="79">
         <f t="shared" si="3"/>
-        <v>-3340.91</v>
+        <v>7718.09</v>
       </c>
       <c r="Q14" s="80">
         <f t="shared" si="4"/>
-        <v>-3540.91</v>
+        <v>8181.09</v>
       </c>
       <c r="R14" s="81">
         <f t="shared" si="5"/>
-        <v>-3440.91</v>
+        <v>7950.09</v>
       </c>
       <c r="S14" s="42">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.09</v>
       </c>
       <c r="U14" t="s">
@@ -4216,7 +4271,7 @@
       <c r="H15" s="72">
         <v>106530.1</v>
       </c>
-      <c r="I15" s="230">
+      <c r="I15" s="73">
         <v>200000.1</v>
       </c>
       <c r="J15" s="74"/>
@@ -4233,25 +4288,25 @@
       </c>
       <c r="N15" s="77">
         <f t="shared" si="2"/>
-        <v>52477.765305599998</v>
+        <v>61419.755578400007</v>
       </c>
       <c r="O15" s="78">
         <v>0</v>
       </c>
       <c r="P15" s="79">
         <f t="shared" si="3"/>
-        <v>-40991.9</v>
+        <v>-32049.9</v>
       </c>
       <c r="Q15" s="80">
         <f t="shared" si="4"/>
-        <v>-43450.9</v>
+        <v>-33972.9</v>
       </c>
       <c r="R15" s="81">
         <f t="shared" si="5"/>
-        <v>-42221.9</v>
+        <v>-33010.9</v>
       </c>
       <c r="S15" s="42">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>9.9999999999999992E-2</v>
       </c>
       <c r="U15" t="s">
@@ -4282,7 +4337,7 @@
       <c r="H16" s="72">
         <v>3639445.11</v>
       </c>
-      <c r="I16" s="230"/>
+      <c r="I16" s="73"/>
       <c r="J16" s="74"/>
       <c r="K16" s="75">
         <f t="shared" si="0"/>
@@ -4297,25 +4352,25 @@
       </c>
       <c r="N16" s="77">
         <f t="shared" si="2"/>
-        <v>285075.55855751998</v>
+        <v>333651.23354653007</v>
       </c>
       <c r="O16" s="78">
         <v>0</v>
       </c>
       <c r="P16" s="79">
         <f t="shared" si="3"/>
-        <v>4033704.11</v>
+        <v>4082280.11</v>
       </c>
       <c r="Q16" s="80">
         <f t="shared" si="4"/>
-        <v>4275726.1100000003</v>
+        <v>4327217.1100000003</v>
       </c>
       <c r="R16" s="81">
         <f t="shared" si="5"/>
-        <v>4154715.11</v>
+        <v>4204748.1099999994</v>
       </c>
       <c r="S16" s="42">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.10999999999999999</v>
       </c>
     </row>
@@ -4345,7 +4400,7 @@
       <c r="H17" s="72">
         <v>350484.12</v>
       </c>
-      <c r="I17" s="230">
+      <c r="I17" s="73">
         <f>H17</f>
         <v>350484.12</v>
       </c>
@@ -4363,25 +4418,25 @@
       </c>
       <c r="N17" s="77">
         <f t="shared" si="2"/>
-        <v>340276.22677991999</v>
+        <v>398257.86323513003</v>
       </c>
       <c r="O17" s="78">
         <v>0</v>
       </c>
       <c r="P17" s="79">
         <f t="shared" si="3"/>
-        <v>340276.12</v>
+        <v>398258.12</v>
       </c>
       <c r="Q17" s="80">
         <f t="shared" si="4"/>
-        <v>360693.12</v>
+        <v>422154.12</v>
       </c>
       <c r="R17" s="81">
         <f t="shared" si="5"/>
-        <v>350484.12</v>
+        <v>410206.12</v>
       </c>
       <c r="S17" s="42">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.11999999999999998</v>
       </c>
     </row>
@@ -4411,7 +4466,7 @@
       <c r="H18" s="72">
         <v>285076.13</v>
       </c>
-      <c r="I18" s="230">
+      <c r="I18" s="73">
         <f>H18</f>
         <v>285076.13</v>
       </c>
@@ -4429,25 +4484,25 @@
       </c>
       <c r="N18" s="77">
         <f t="shared" si="2"/>
-        <v>285075.55855751998</v>
+        <v>333651.23354653007</v>
       </c>
       <c r="O18" s="78">
         <v>0</v>
       </c>
       <c r="P18" s="79">
         <f t="shared" si="3"/>
-        <v>285076.13</v>
+        <v>333651.13</v>
       </c>
       <c r="Q18" s="80">
         <f t="shared" si="4"/>
-        <v>302181.13</v>
+        <v>353670.13</v>
       </c>
       <c r="R18" s="81">
         <f t="shared" si="5"/>
-        <v>293628.13</v>
+        <v>343661.13</v>
       </c>
       <c r="S18" s="42">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.12999999999999998</v>
       </c>
     </row>
@@ -4477,7 +4532,7 @@
       <c r="H19" s="72">
         <v>621056.14</v>
       </c>
-      <c r="I19" s="230">
+      <c r="I19" s="73">
         <f>40000</f>
         <v>40000</v>
       </c>
@@ -4495,25 +4550,25 @@
       </c>
       <c r="N19" s="77">
         <f t="shared" si="2"/>
-        <v>326352.29140991997</v>
+        <v>381961.34789888002</v>
       </c>
       <c r="O19" s="78">
         <v>0</v>
       </c>
       <c r="P19" s="79">
         <f t="shared" si="3"/>
-        <v>924840.14</v>
+        <v>980449.14</v>
       </c>
       <c r="Q19" s="80">
         <f t="shared" si="4"/>
-        <v>980331.14</v>
+        <v>1039276.14</v>
       </c>
       <c r="R19" s="81">
         <f t="shared" si="5"/>
-        <v>952585.14</v>
+        <v>1009862.14</v>
       </c>
       <c r="S19" s="42">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.13999999999999999</v>
       </c>
       <c r="U19" t="s">
@@ -4544,7 +4599,7 @@
       <c r="H20" s="72">
         <v>291313.15000000002</v>
       </c>
-      <c r="I20" s="230">
+      <c r="I20" s="73">
         <f>H20</f>
         <v>291313.15000000002</v>
       </c>
@@ -4562,25 +4617,25 @@
       </c>
       <c r="N20" s="77">
         <f t="shared" si="2"/>
-        <v>291313.48160328</v>
+        <v>340952.07241717004</v>
       </c>
       <c r="O20" s="78">
         <v>0</v>
       </c>
       <c r="P20" s="79">
         <f t="shared" si="3"/>
-        <v>291313.15000000002</v>
+        <v>340952.15</v>
       </c>
       <c r="Q20" s="80">
         <f t="shared" si="4"/>
-        <v>308792.15000000002</v>
+        <v>361409.15</v>
       </c>
       <c r="R20" s="81">
         <f t="shared" si="5"/>
-        <v>300052.15000000002</v>
+        <v>351181.15</v>
       </c>
       <c r="S20" s="42">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.15</v>
       </c>
     </row>
@@ -4610,7 +4665,7 @@
       <c r="H21" s="72">
         <v>327701.15999999997</v>
       </c>
-      <c r="I21" s="230">
+      <c r="I21" s="73">
         <f>H21</f>
         <v>327701.15999999997</v>
       </c>
@@ -4628,25 +4683,25 @@
       </c>
       <c r="N21" s="77">
         <f t="shared" si="2"/>
-        <v>327701.36603688</v>
+        <v>383540.29916257004</v>
       </c>
       <c r="O21" s="78">
         <v>0</v>
       </c>
       <c r="P21" s="79">
         <f t="shared" si="3"/>
-        <v>327701.15999999997</v>
+        <v>383540.16</v>
       </c>
       <c r="Q21" s="80">
         <f t="shared" si="4"/>
-        <v>347363.16</v>
+        <v>406553.16</v>
       </c>
       <c r="R21" s="81">
         <f t="shared" si="5"/>
-        <v>337532.15999999997</v>
+        <v>395046.16</v>
       </c>
       <c r="S21" s="42">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.16</v>
       </c>
       <c r="U21" s="41"/>
@@ -4677,7 +4732,7 @@
       <c r="H22" s="73">
         <v>287576.17</v>
       </c>
-      <c r="I22" s="230">
+      <c r="I22" s="73">
         <f>H22</f>
         <v>287576.17</v>
       </c>
@@ -4695,25 +4750,25 @@
       </c>
       <c r="N22" s="77">
         <f t="shared" si="2"/>
-        <v>287575.67850840004</v>
+        <v>336577.36341135006</v>
       </c>
       <c r="O22" s="78">
         <v>0</v>
       </c>
       <c r="P22" s="79">
         <f t="shared" si="3"/>
-        <v>287576.17</v>
+        <v>336577.17</v>
       </c>
       <c r="Q22" s="80">
         <f t="shared" si="4"/>
-        <v>304831.17</v>
+        <v>356772.17</v>
       </c>
       <c r="R22" s="81">
         <f t="shared" si="5"/>
-        <v>296203.17</v>
+        <v>346674.17</v>
       </c>
       <c r="S22" s="42">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.17</v>
       </c>
     </row>
@@ -4734,7 +4789,7 @@
       <c r="E23" s="64" t="s">
         <v>119</v>
       </c>
-      <c r="F23" s="143" t="s">
+      <c r="F23" s="142" t="s">
         <v>120</v>
       </c>
       <c r="G23" s="71">
@@ -4743,7 +4798,7 @@
       <c r="H23" s="72">
         <v>342670.18</v>
       </c>
-      <c r="I23" s="230">
+      <c r="I23" s="73">
         <f>H23</f>
         <v>342670.18</v>
       </c>
@@ -4761,28 +4816,28 @@
       </c>
       <c r="N23" s="77">
         <f t="shared" si="2"/>
-        <v>332689.22910719999</v>
+        <v>389378.07310080004</v>
       </c>
       <c r="O23" s="78">
         <v>0</v>
       </c>
       <c r="P23" s="79">
         <f t="shared" si="3"/>
-        <v>332689.18</v>
+        <v>389378.18</v>
       </c>
       <c r="Q23" s="80">
         <f t="shared" si="4"/>
-        <v>352651.18</v>
+        <v>412741.18</v>
       </c>
       <c r="R23" s="81">
         <f t="shared" si="5"/>
-        <v>342670.18</v>
+        <v>401059.18</v>
       </c>
       <c r="S23" s="42">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.18000000000000002</v>
       </c>
-      <c r="U23" s="153" t="s">
+      <c r="U23" s="152" t="s">
         <v>120</v>
       </c>
     </row>
@@ -4810,7 +4865,7 @@
       <c r="H24" s="72">
         <v>292093.19</v>
       </c>
-      <c r="I24" s="230">
+      <c r="I24" s="73">
         <f>H24+100000</f>
         <v>392093.19</v>
       </c>
@@ -4828,25 +4883,25 @@
       </c>
       <c r="N24" s="77">
         <f t="shared" si="2"/>
-        <v>292093.221984</v>
+        <v>341864.67727600003</v>
       </c>
       <c r="O24" s="78">
         <v>0</v>
       </c>
       <c r="P24" s="79">
         <f t="shared" si="3"/>
-        <v>192093.19</v>
+        <v>241865.19</v>
       </c>
       <c r="Q24" s="80">
         <f t="shared" si="4"/>
-        <v>203619.19</v>
+        <v>256377.19</v>
       </c>
       <c r="R24" s="81">
         <f t="shared" si="5"/>
-        <v>197856.19</v>
+        <v>249121.19</v>
       </c>
       <c r="S24" s="42">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.19000000000000003</v>
       </c>
     </row>
@@ -4874,7 +4929,7 @@
       <c r="H25" s="72">
         <v>326615.2</v>
       </c>
-      <c r="I25" s="230">
+      <c r="I25" s="73">
         <v>327000</v>
       </c>
       <c r="J25" s="74"/>
@@ -4891,25 +4946,25 @@
       </c>
       <c r="N25" s="77">
         <f t="shared" si="2"/>
-        <v>336439.40903352003</v>
+        <v>393767.26789803011</v>
       </c>
       <c r="O25" s="78">
         <v>0</v>
       </c>
       <c r="P25" s="79">
         <f t="shared" si="3"/>
-        <v>336055.2</v>
+        <v>393382.2</v>
       </c>
       <c r="Q25" s="80">
         <f t="shared" si="4"/>
-        <v>356219.2</v>
+        <v>416985.2</v>
       </c>
       <c r="R25" s="81">
         <f t="shared" si="5"/>
-        <v>346137.2</v>
+        <v>405183.2</v>
       </c>
       <c r="S25" s="42">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.20000000000000004</v>
       </c>
     </row>
@@ -4937,7 +4992,7 @@
       <c r="H26" s="72">
         <v>285076.21000000002</v>
       </c>
-      <c r="I26" s="230">
+      <c r="I26" s="73">
         <f>H26</f>
         <v>285076.21000000002</v>
       </c>
@@ -4955,25 +5010,25 @@
       </c>
       <c r="N26" s="77">
         <f t="shared" si="2"/>
-        <v>285075.55855751998</v>
+        <v>333651.23354653007</v>
       </c>
       <c r="O26" s="78">
         <v>0</v>
       </c>
       <c r="P26" s="79">
         <f t="shared" si="3"/>
-        <v>285076.21000000002</v>
+        <v>333651.21000000002</v>
       </c>
       <c r="Q26" s="80">
         <f t="shared" si="4"/>
-        <v>302181.21000000002</v>
+        <v>353670.21</v>
       </c>
       <c r="R26" s="81">
         <f t="shared" si="5"/>
-        <v>293628.21000000002</v>
+        <v>343661.21</v>
       </c>
       <c r="S26" s="42">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.21000000000000005</v>
       </c>
     </row>
@@ -5003,7 +5058,7 @@
       <c r="H27" s="72">
         <v>653120.22</v>
       </c>
-      <c r="I27" s="230">
+      <c r="I27" s="73">
         <f>885587.22</f>
         <v>885587.22</v>
       </c>
@@ -5021,25 +5076,25 @@
       </c>
       <c r="N27" s="77">
         <f t="shared" si="2"/>
-        <v>326253.27675840002</v>
-      </c>
-      <c r="O27" s="184">
+        <v>381845.46156760008</v>
+      </c>
+      <c r="O27" s="183">
         <v>0</v>
       </c>
       <c r="P27" s="79">
         <f t="shared" si="3"/>
-        <v>93786.22</v>
+        <v>149378.22</v>
       </c>
       <c r="Q27" s="80">
         <f t="shared" si="4"/>
-        <v>99413.22</v>
+        <v>158341.22</v>
       </c>
       <c r="R27" s="81">
         <f t="shared" si="5"/>
-        <v>96600.22</v>
+        <v>153859.22</v>
       </c>
       <c r="S27" s="42">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.22000000000000006</v>
       </c>
       <c r="T27" s="65" t="s">
@@ -5073,7 +5128,7 @@
       <c r="H28" s="72">
         <v>285076.23</v>
       </c>
-      <c r="I28" s="230">
+      <c r="I28" s="73">
         <v>290000.23</v>
       </c>
       <c r="J28" s="74"/>
@@ -5090,25 +5145,25 @@
       </c>
       <c r="N28" s="77">
         <f t="shared" si="2"/>
-        <v>285075.55855751998</v>
+        <v>333651.23354653007</v>
       </c>
       <c r="O28" s="78">
         <v>0</v>
       </c>
       <c r="P28" s="79">
         <f t="shared" si="3"/>
-        <v>280152.23</v>
+        <v>328727.23</v>
       </c>
       <c r="Q28" s="80">
         <f t="shared" si="4"/>
-        <v>296961.23</v>
+        <v>348451.23</v>
       </c>
       <c r="R28" s="81">
         <f t="shared" si="5"/>
-        <v>288557.23</v>
+        <v>338589.23</v>
       </c>
       <c r="S28" s="42">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.23000000000000007</v>
       </c>
     </row>
@@ -5136,8 +5191,8 @@
       <c r="H29" s="72">
         <v>323766.24</v>
       </c>
-      <c r="I29" s="230">
-        <f t="shared" ref="I28:I34" si="8">H29</f>
+      <c r="I29" s="73">
+        <f t="shared" ref="I29:I34" si="9">H29</f>
         <v>323766.24</v>
       </c>
       <c r="J29" s="74"/>
@@ -5154,25 +5209,25 @@
       </c>
       <c r="N29" s="77">
         <f t="shared" si="2"/>
-        <v>323765.53363895998</v>
+        <v>378933.81749419001</v>
       </c>
       <c r="O29" s="78">
         <v>0</v>
       </c>
       <c r="P29" s="79">
         <f t="shared" si="3"/>
-        <v>323766.24</v>
+        <v>378934.24</v>
       </c>
       <c r="Q29" s="80">
         <f t="shared" si="4"/>
-        <v>343192.24</v>
+        <v>401670.24</v>
       </c>
       <c r="R29" s="81">
         <f t="shared" si="5"/>
-        <v>333479.24</v>
+        <v>390302.24</v>
       </c>
       <c r="S29" s="42">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.24000000000000007</v>
       </c>
     </row>
@@ -5200,8 +5255,8 @@
       <c r="H30" s="72">
         <v>291313.25</v>
       </c>
-      <c r="I30" s="230">
-        <f t="shared" si="8"/>
+      <c r="I30" s="73">
+        <f t="shared" si="9"/>
         <v>291313.25</v>
       </c>
       <c r="J30" s="74"/>
@@ -5218,25 +5273,25 @@
       </c>
       <c r="N30" s="77">
         <f t="shared" si="2"/>
-        <v>291313.48160328</v>
+        <v>340952.07241717004</v>
       </c>
       <c r="O30" s="78">
         <v>0</v>
       </c>
       <c r="P30" s="79">
         <f t="shared" si="3"/>
-        <v>291313.25</v>
+        <v>340952.25</v>
       </c>
       <c r="Q30" s="80">
         <f t="shared" si="4"/>
-        <v>308792.25</v>
+        <v>361409.25</v>
       </c>
       <c r="R30" s="81">
         <f t="shared" si="5"/>
-        <v>300052.25</v>
+        <v>351181.25</v>
       </c>
       <c r="S30" s="42">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.25000000000000006</v>
       </c>
     </row>
@@ -5266,8 +5321,8 @@
       <c r="H31" s="72">
         <v>327602.26</v>
       </c>
-      <c r="I31" s="230">
-        <f t="shared" si="8"/>
+      <c r="I31" s="73">
+        <f t="shared" si="9"/>
         <v>327602.26</v>
       </c>
       <c r="J31" s="74"/>
@@ -5284,25 +5339,25 @@
       </c>
       <c r="N31" s="77">
         <f t="shared" si="2"/>
-        <v>327602.35138536</v>
+        <v>383424.41283129004</v>
       </c>
       <c r="O31" s="78">
         <v>0</v>
       </c>
       <c r="P31" s="79">
         <f t="shared" si="3"/>
-        <v>327602.26</v>
+        <v>383424.26</v>
       </c>
       <c r="Q31" s="80">
         <f t="shared" si="4"/>
-        <v>347258.26</v>
+        <v>406430.26</v>
       </c>
       <c r="R31" s="81">
         <f t="shared" si="5"/>
-        <v>337430.26</v>
+        <v>394927.26</v>
       </c>
       <c r="S31" s="42">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.26000000000000006</v>
       </c>
     </row>
@@ -5330,7 +5385,7 @@
       <c r="H32" s="72">
         <v>291313.27</v>
       </c>
-      <c r="I32" s="230">
+      <c r="I32" s="73">
         <v>300052.27</v>
       </c>
       <c r="J32" s="74"/>
@@ -5347,25 +5402,25 @@
       </c>
       <c r="N32" s="77">
         <f t="shared" si="2"/>
-        <v>291313.48160328</v>
+        <v>340952.07241717004</v>
       </c>
       <c r="O32" s="78">
         <v>0</v>
       </c>
       <c r="P32" s="79">
         <f t="shared" si="3"/>
-        <v>282574.27</v>
+        <v>332213.27</v>
       </c>
       <c r="Q32" s="80">
         <f t="shared" si="4"/>
-        <v>299529.27</v>
+        <v>352146.27</v>
       </c>
       <c r="R32" s="81">
         <f t="shared" si="5"/>
-        <v>291051.27</v>
+        <v>342179.27</v>
       </c>
       <c r="S32" s="42">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.27000000000000007</v>
       </c>
     </row>
@@ -5393,8 +5448,8 @@
       <c r="H33" s="72">
         <v>330003.28000000003</v>
       </c>
-      <c r="I33" s="230">
-        <f t="shared" si="8"/>
+      <c r="I33" s="73">
+        <f t="shared" si="9"/>
         <v>330003.28000000003</v>
       </c>
       <c r="J33" s="74"/>
@@ -5411,25 +5466,25 @@
       </c>
       <c r="N33" s="77">
         <f t="shared" si="2"/>
-        <v>330003.45668472</v>
-      </c>
-      <c r="O33" s="128">
+        <v>386234.65636483009</v>
+      </c>
+      <c r="O33" s="127">
         <v>0</v>
       </c>
       <c r="P33" s="79">
         <f t="shared" si="3"/>
-        <v>330003.28000000003</v>
+        <v>386235.28</v>
       </c>
       <c r="Q33" s="80">
         <f t="shared" si="4"/>
-        <v>349803.28</v>
+        <v>409409.28000000003</v>
       </c>
       <c r="R33" s="81">
         <f t="shared" si="5"/>
-        <v>339903.28</v>
+        <v>397822.28</v>
       </c>
       <c r="S33" s="42">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.28000000000000008</v>
       </c>
     </row>
@@ -5459,8 +5514,8 @@
       <c r="H34" s="72">
         <v>321435.28999999998</v>
       </c>
-      <c r="I34" s="230">
-        <f t="shared" si="8"/>
+      <c r="I34" s="73">
+        <f t="shared" si="9"/>
         <v>321435.28999999998</v>
       </c>
       <c r="J34" s="74"/>
@@ -5477,25 +5532,25 @@
       </c>
       <c r="N34" s="77">
         <f t="shared" si="2"/>
-        <v>302935.32632544002</v>
-      </c>
-      <c r="O34" s="188">
+        <v>354554.23055116006</v>
+      </c>
+      <c r="O34" s="187">
         <v>18500</v>
       </c>
       <c r="P34" s="79">
         <f t="shared" si="3"/>
-        <v>321435.28999999998</v>
+        <v>373054.29</v>
       </c>
       <c r="Q34" s="80">
         <f t="shared" si="4"/>
-        <v>340721.29</v>
+        <v>395438.29</v>
       </c>
       <c r="R34" s="81">
         <f t="shared" si="5"/>
-        <v>331078.28999999998</v>
+        <v>384246.29</v>
       </c>
       <c r="S34" s="42">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.29000000000000009</v>
       </c>
     </row>
@@ -5523,7 +5578,7 @@
       <c r="H35" s="72">
         <v>336439.3</v>
       </c>
-      <c r="I35" s="230">
+      <c r="I35" s="73">
         <f>H35</f>
         <v>336439.3</v>
       </c>
@@ -5541,25 +5596,25 @@
       </c>
       <c r="N35" s="77">
         <f t="shared" si="2"/>
-        <v>336439.40903352003</v>
+        <v>393767.26789803011</v>
       </c>
       <c r="O35" s="78">
         <v>0</v>
       </c>
       <c r="P35" s="79">
         <f t="shared" si="3"/>
-        <v>336439.3</v>
+        <v>393767.3</v>
       </c>
       <c r="Q35" s="80">
         <f t="shared" si="4"/>
-        <v>356626.3</v>
+        <v>417393.3</v>
       </c>
       <c r="R35" s="81">
         <f t="shared" si="5"/>
-        <v>346532.3</v>
+        <v>405580.3</v>
       </c>
       <c r="S35" s="42">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.3000000000000001</v>
       </c>
     </row>
@@ -5589,7 +5644,7 @@
       <c r="H36" s="73">
         <v>284989.31</v>
       </c>
-      <c r="I36" s="230">
+      <c r="I36" s="73">
         <f>H36</f>
         <v>284989.31</v>
       </c>
@@ -5605,27 +5660,27 @@
       <c r="M36" s="76">
         <v>0</v>
       </c>
-      <c r="N36" s="141">
+      <c r="N36" s="140">
         <f t="shared" si="2"/>
-        <v>284988.92073744</v>
+        <v>333549.83300666005</v>
       </c>
       <c r="O36" s="83">
         <v>0</v>
       </c>
       <c r="P36" s="79">
         <f t="shared" si="3"/>
-        <v>284989.31</v>
+        <v>333550.31</v>
       </c>
       <c r="Q36" s="80">
         <f t="shared" si="4"/>
-        <v>302089.31</v>
+        <v>353563.31</v>
       </c>
       <c r="R36" s="81">
         <f t="shared" si="5"/>
-        <v>293539.31</v>
+        <v>343557.31</v>
       </c>
       <c r="S36" s="42">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.31000000000000011</v>
       </c>
     </row>
@@ -5653,7 +5708,7 @@
       <c r="H37" s="72">
         <v>456011.32</v>
       </c>
-      <c r="I37" s="230">
+      <c r="I37" s="73">
         <v>328753.32</v>
       </c>
       <c r="J37" s="74"/>
@@ -5670,25 +5725,25 @@
       </c>
       <c r="N37" s="77">
         <f t="shared" si="2"/>
-        <v>328753.39670928003</v>
+        <v>384771.59143242007</v>
       </c>
       <c r="O37" s="78">
         <v>0</v>
       </c>
       <c r="P37" s="79">
         <f t="shared" si="3"/>
-        <v>459829.32</v>
+        <v>515847.32</v>
       </c>
       <c r="Q37" s="80">
         <f t="shared" si="4"/>
-        <v>487419.32</v>
+        <v>546798.31999999995</v>
       </c>
       <c r="R37" s="81">
         <f t="shared" si="5"/>
-        <v>473624.32000000001</v>
+        <v>531322.32000000007</v>
       </c>
       <c r="S37" s="42">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.32000000000000012</v>
       </c>
     </row>
@@ -5716,43 +5771,43 @@
       <c r="H38" s="72">
         <v>288912.33</v>
       </c>
-      <c r="I38" s="230">
-        <f t="shared" ref="I38:I41" si="9">H38</f>
+      <c r="I38" s="73">
+        <f t="shared" ref="I38:I41" si="10">H38</f>
         <v>288912.33</v>
       </c>
       <c r="J38" s="74"/>
       <c r="K38" s="75">
-        <f t="shared" ref="K38:K69" si="10">H38-I38</f>
+        <f t="shared" ref="K38:K69" si="11">H38-I38</f>
         <v>0</v>
       </c>
       <c r="L38" s="75">
-        <f t="shared" ref="L38:L69" si="11">IF(K38&gt;0,K38*3%,0)</f>
+        <f t="shared" ref="L38:L69" si="12">IF(K38&gt;0,K38*3%,0)</f>
         <v>0</v>
       </c>
       <c r="M38" s="76">
         <v>0</v>
       </c>
       <c r="N38" s="77">
-        <f t="shared" ref="N38:N69" si="12">P$2*G38%</f>
-        <v>288912.37630392</v>
+        <f t="shared" ref="N38:N69" si="13">P$2*G38%</f>
+        <v>338141.82888363005</v>
       </c>
       <c r="O38" s="78">
         <v>0</v>
       </c>
       <c r="P38" s="79">
-        <f t="shared" ref="P38:P69" si="13">ROUND(SUM(K38:O38),0) + S38</f>
-        <v>288912.33</v>
+        <f t="shared" ref="P38:P69" si="14">ROUND(SUM(K38:O38),0) + S38</f>
+        <v>338142.33</v>
       </c>
       <c r="Q38" s="80">
-        <f t="shared" ref="Q38:Q69" si="14">ROUND(P38*6% + P38,0) + S38</f>
-        <v>306247.33</v>
+        <f t="shared" ref="Q38:Q69" si="15">ROUND(P38*6% + P38,0) + S38</f>
+        <v>358431.33</v>
       </c>
       <c r="R38" s="81">
-        <f t="shared" ref="R38:R69" si="15">ROUND(P38*3%,0) + P38</f>
-        <v>297579.33</v>
+        <f t="shared" ref="R38:R69" si="16">ROUND(P38*3%,0) + P38</f>
+        <v>348286.33</v>
       </c>
       <c r="S38" s="42">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.33000000000000013</v>
       </c>
     </row>
@@ -5767,7 +5822,7 @@
         <v>103</v>
       </c>
       <c r="D39" s="64">
-        <f t="shared" ref="D39:D75" si="16">D38+1</f>
+        <f t="shared" ref="D39:D75" si="17">D38+1</f>
         <v>34</v>
       </c>
       <c r="E39" s="64" t="s">
@@ -5780,43 +5835,43 @@
       <c r="H39" s="72">
         <v>325003.34000000003</v>
       </c>
-      <c r="I39" s="230">
-        <f t="shared" si="9"/>
+      <c r="I39" s="73">
+        <f t="shared" si="10"/>
         <v>325003.34000000003</v>
       </c>
       <c r="J39" s="74"/>
       <c r="K39" s="75">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="L39" s="75">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M39" s="76">
         <v>0</v>
       </c>
       <c r="N39" s="77">
-        <f t="shared" si="12"/>
-        <v>325003.21678295999</v>
+        <f t="shared" si="13"/>
+        <v>380382.39663519006</v>
       </c>
       <c r="O39" s="78">
         <v>0</v>
       </c>
       <c r="P39" s="79">
-        <f t="shared" si="13"/>
-        <v>325003.34000000003</v>
+        <f t="shared" si="14"/>
+        <v>380382.34</v>
       </c>
       <c r="Q39" s="80">
-        <f t="shared" si="14"/>
-        <v>344504.34</v>
+        <f t="shared" si="15"/>
+        <v>403205.34</v>
       </c>
       <c r="R39" s="81">
-        <f t="shared" si="15"/>
-        <v>334753.34000000003</v>
+        <f t="shared" si="16"/>
+        <v>391793.34</v>
       </c>
       <c r="S39" s="42">
-        <f t="shared" ref="S39:S75" si="17">S38+0.01</f>
+        <f t="shared" ref="S39:S75" si="18">S38+0.01</f>
         <v>0.34000000000000014</v>
       </c>
     </row>
@@ -5831,7 +5886,7 @@
         <v>146</v>
       </c>
       <c r="D40" s="64">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>35</v>
       </c>
       <c r="E40" s="64" t="s">
@@ -5846,43 +5901,43 @@
       <c r="H40" s="72">
         <v>128374.35</v>
       </c>
-      <c r="I40" s="230">
-        <f t="shared" si="9"/>
+      <c r="I40" s="73">
+        <f t="shared" si="10"/>
         <v>128374.35</v>
       </c>
       <c r="J40" s="74"/>
       <c r="K40" s="75">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="L40" s="75">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M40" s="76">
         <v>0</v>
       </c>
       <c r="N40" s="77">
-        <f t="shared" si="12"/>
-        <v>124634.69260079999</v>
+        <f t="shared" si="13"/>
+        <v>145871.91949870001</v>
       </c>
       <c r="O40" s="78">
         <v>0</v>
       </c>
       <c r="P40" s="79">
-        <f t="shared" si="13"/>
-        <v>124635.35</v>
+        <f t="shared" si="14"/>
+        <v>145872.35</v>
       </c>
       <c r="Q40" s="80">
-        <f t="shared" si="14"/>
-        <v>132113.35</v>
+        <f t="shared" si="15"/>
+        <v>154625.35</v>
       </c>
       <c r="R40" s="81">
-        <f t="shared" si="15"/>
-        <v>128374.35</v>
+        <f t="shared" si="16"/>
+        <v>150248.35</v>
       </c>
       <c r="S40" s="42">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.35000000000000014</v>
       </c>
     </row>
@@ -5897,7 +5952,7 @@
         <v>149</v>
       </c>
       <c r="D41" s="64">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>36</v>
       </c>
       <c r="E41" s="64" t="s">
@@ -5912,43 +5967,43 @@
       <c r="H41" s="73">
         <v>99589.36</v>
       </c>
-      <c r="I41" s="230">
-        <f t="shared" si="9"/>
+      <c r="I41" s="73">
+        <f t="shared" si="10"/>
         <v>99589.36</v>
       </c>
       <c r="J41" s="74"/>
       <c r="K41" s="75">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="L41" s="75">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M41" s="76">
         <v>0</v>
       </c>
       <c r="N41" s="77">
-        <f t="shared" si="12"/>
-        <v>96687.807209279999</v>
+        <f t="shared" si="13"/>
+        <v>113163.00249492002</v>
       </c>
       <c r="O41" s="78">
         <v>0</v>
       </c>
       <c r="P41" s="79">
-        <f t="shared" si="13"/>
-        <v>96688.36</v>
+        <f t="shared" si="14"/>
+        <v>113163.36</v>
       </c>
       <c r="Q41" s="80">
-        <f t="shared" si="14"/>
-        <v>102490.36</v>
+        <f t="shared" si="15"/>
+        <v>119953.36</v>
       </c>
       <c r="R41" s="81">
-        <f t="shared" si="15"/>
-        <v>99589.36</v>
+        <f t="shared" si="16"/>
+        <v>116558.36</v>
       </c>
       <c r="S41" s="42">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.36000000000000015</v>
       </c>
       <c r="U41" t="s">
@@ -5964,7 +6019,7 @@
         <v>153</v>
       </c>
       <c r="D42" s="64">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>37</v>
       </c>
       <c r="E42" s="63" t="s">
@@ -5979,43 +6034,43 @@
       <c r="H42" s="72">
         <v>154928.37</v>
       </c>
-      <c r="I42" s="230">
+      <c r="I42" s="73">
         <f>H42</f>
         <v>154928.37</v>
       </c>
       <c r="J42" s="74"/>
       <c r="K42" s="75">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="L42" s="75">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M42" s="76">
         <v>0</v>
       </c>
       <c r="N42" s="77">
-        <f t="shared" si="12"/>
-        <v>150415.63249032001</v>
+        <f t="shared" si="13"/>
+        <v>176045.82300573002</v>
       </c>
       <c r="O42" s="78">
         <v>0</v>
       </c>
       <c r="P42" s="79">
-        <f t="shared" si="13"/>
-        <v>150416.37</v>
+        <f t="shared" si="14"/>
+        <v>176046.37</v>
       </c>
       <c r="Q42" s="80">
-        <f t="shared" si="14"/>
-        <v>159441.37</v>
+        <f t="shared" si="15"/>
+        <v>186609.37</v>
       </c>
       <c r="R42" s="81">
-        <f t="shared" si="15"/>
-        <v>154928.37</v>
+        <f t="shared" si="16"/>
+        <v>181327.37</v>
       </c>
       <c r="S42" s="42">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.37000000000000016</v>
       </c>
       <c r="U42" t="s">
@@ -6030,7 +6085,7 @@
         <v>146</v>
       </c>
       <c r="D43" s="64">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>38</v>
       </c>
       <c r="E43" s="63" t="s">
@@ -6045,43 +6100,43 @@
       <c r="H43" s="72">
         <v>124665.38</v>
       </c>
-      <c r="I43" s="230">
+      <c r="I43" s="73">
         <f>H43</f>
         <v>124665.38</v>
       </c>
       <c r="J43" s="74"/>
       <c r="K43" s="75">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="L43" s="75">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M43" s="76">
         <v>0</v>
       </c>
       <c r="N43" s="77">
-        <f t="shared" si="12"/>
-        <v>118186.36342056</v>
+        <f t="shared" si="13"/>
+        <v>138324.82217409002</v>
       </c>
       <c r="O43" s="78">
         <v>0</v>
       </c>
       <c r="P43" s="79">
-        <f t="shared" si="13"/>
-        <v>118186.38</v>
+        <f t="shared" si="14"/>
+        <v>138325.38</v>
       </c>
       <c r="Q43" s="80">
-        <f t="shared" si="14"/>
-        <v>125278.38</v>
+        <f t="shared" si="15"/>
+        <v>146625.38</v>
       </c>
       <c r="R43" s="81">
-        <f t="shared" si="15"/>
-        <v>121732.38</v>
+        <f t="shared" si="16"/>
+        <v>142475.38</v>
       </c>
       <c r="S43" s="42">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.38000000000000017</v>
       </c>
     </row>
@@ -6093,7 +6148,7 @@
         <v>149</v>
       </c>
       <c r="D44" s="64">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>39</v>
       </c>
       <c r="E44" s="63" t="s">
@@ -6106,40 +6161,40 @@
       <c r="H44" s="72">
         <v>645600.39</v>
       </c>
-      <c r="I44" s="230"/>
+      <c r="I44" s="73"/>
       <c r="J44" s="74"/>
       <c r="K44" s="75">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>645600.39</v>
       </c>
       <c r="L44" s="75">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>19368.011699999999</v>
       </c>
       <c r="M44" s="76">
         <v>0</v>
       </c>
       <c r="N44" s="77">
-        <f t="shared" si="12"/>
-        <v>93469.831034879986</v>
+        <f t="shared" si="13"/>
+        <v>109396.69672832001</v>
       </c>
       <c r="O44" s="78">
         <v>0</v>
       </c>
       <c r="P44" s="79">
-        <f t="shared" si="13"/>
-        <v>758438.39</v>
+        <f t="shared" si="14"/>
+        <v>774365.39</v>
       </c>
       <c r="Q44" s="80">
-        <f t="shared" si="14"/>
-        <v>803945.39</v>
+        <f t="shared" si="15"/>
+        <v>820827.39</v>
       </c>
       <c r="R44" s="81">
-        <f t="shared" si="15"/>
-        <v>781191.39</v>
+        <f t="shared" si="16"/>
+        <v>797596.39</v>
       </c>
       <c r="S44" s="42">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.39000000000000018</v>
       </c>
     </row>
@@ -6151,7 +6206,7 @@
         <v>153</v>
       </c>
       <c r="D45" s="64">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>40</v>
       </c>
       <c r="E45" s="63" t="s">
@@ -6166,42 +6221,42 @@
       <c r="H45" s="72">
         <v>142891.4</v>
       </c>
-      <c r="I45" s="230">
+      <c r="I45" s="73">
         <v>147148.4</v>
       </c>
       <c r="J45" s="74"/>
       <c r="K45" s="75">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-4257</v>
       </c>
       <c r="L45" s="75">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M45" s="76">
         <v>0</v>
       </c>
       <c r="N45" s="77">
-        <f t="shared" si="12"/>
-        <v>142890.51897480001</v>
+        <f t="shared" si="13"/>
+        <v>167238.46182845003</v>
       </c>
       <c r="O45" s="78">
         <v>0</v>
       </c>
       <c r="P45" s="79">
-        <f t="shared" si="13"/>
-        <v>138634.4</v>
+        <f t="shared" si="14"/>
+        <v>162981.4</v>
       </c>
       <c r="Q45" s="80">
-        <f t="shared" si="14"/>
-        <v>146952.4</v>
+        <f t="shared" si="15"/>
+        <v>172760.4</v>
       </c>
       <c r="R45" s="81">
-        <f t="shared" si="15"/>
-        <v>142793.4</v>
+        <f t="shared" si="16"/>
+        <v>167870.4</v>
       </c>
       <c r="S45" s="42">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.40000000000000019</v>
       </c>
     </row>
@@ -6213,7 +6268,7 @@
         <v>146</v>
       </c>
       <c r="D46" s="64">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>41</v>
       </c>
       <c r="E46" s="63" t="s">
@@ -6228,42 +6283,42 @@
       <c r="H46" s="72">
         <v>114738.41</v>
       </c>
-      <c r="I46" s="230">
+      <c r="I46" s="73">
         <v>118180.41</v>
       </c>
       <c r="J46" s="74"/>
       <c r="K46" s="75">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-3442</v>
       </c>
       <c r="L46" s="75">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M46" s="76">
         <v>0</v>
       </c>
       <c r="N46" s="77">
-        <f t="shared" si="12"/>
-        <v>118186.36342056</v>
+        <f t="shared" si="13"/>
+        <v>138324.82217409002</v>
       </c>
       <c r="O46" s="78">
         <v>0</v>
       </c>
       <c r="P46" s="79">
-        <f t="shared" si="13"/>
-        <v>114744.41</v>
+        <f t="shared" si="14"/>
+        <v>134883.41</v>
       </c>
       <c r="Q46" s="80">
-        <f t="shared" si="14"/>
-        <v>121629.41</v>
+        <f t="shared" si="15"/>
+        <v>142976.41</v>
       </c>
       <c r="R46" s="81">
-        <f t="shared" si="15"/>
-        <v>118186.41</v>
+        <f t="shared" si="16"/>
+        <v>138930.41</v>
       </c>
       <c r="S46" s="42">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.4100000000000002</v>
       </c>
     </row>
@@ -6275,7 +6330,7 @@
         <v>149</v>
       </c>
       <c r="D47" s="64">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>42</v>
       </c>
       <c r="E47" s="63" t="s">
@@ -6288,43 +6343,43 @@
       <c r="H47" s="72">
         <v>93470.42</v>
       </c>
-      <c r="I47" s="230">
+      <c r="I47" s="73">
         <f>H47</f>
         <v>93470.42</v>
       </c>
       <c r="J47" s="74"/>
       <c r="K47" s="75">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="L47" s="75">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M47" s="76">
         <v>0</v>
       </c>
       <c r="N47" s="77">
-        <f t="shared" si="12"/>
-        <v>93469.831034879986</v>
+        <f t="shared" si="13"/>
+        <v>109396.69672832001</v>
       </c>
       <c r="O47" s="78">
         <v>0</v>
       </c>
       <c r="P47" s="79">
-        <f t="shared" si="13"/>
-        <v>93470.42</v>
+        <f t="shared" si="14"/>
+        <v>109397.42</v>
       </c>
       <c r="Q47" s="80">
-        <f t="shared" si="14"/>
-        <v>99079.42</v>
+        <f t="shared" si="15"/>
+        <v>115961.42</v>
       </c>
       <c r="R47" s="81">
-        <f t="shared" si="15"/>
-        <v>96274.42</v>
+        <f t="shared" si="16"/>
+        <v>112679.42</v>
       </c>
       <c r="S47" s="42">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.42000000000000021</v>
       </c>
     </row>
@@ -6336,7 +6391,7 @@
         <v>153</v>
       </c>
       <c r="D48" s="64">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>43</v>
       </c>
       <c r="E48" s="63" t="s">
@@ -6349,43 +6404,43 @@
       <c r="H48" s="72">
         <v>142891.43</v>
       </c>
-      <c r="I48" s="230">
+      <c r="I48" s="73">
         <f>H48</f>
         <v>142891.43</v>
       </c>
       <c r="J48" s="74"/>
       <c r="K48" s="75">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="L48" s="75">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M48" s="76">
         <v>0</v>
       </c>
       <c r="N48" s="77">
-        <f t="shared" si="12"/>
-        <v>142890.51897480001</v>
+        <f t="shared" si="13"/>
+        <v>167238.46182845003</v>
       </c>
       <c r="O48" s="78">
         <v>0</v>
       </c>
       <c r="P48" s="79">
-        <f t="shared" si="13"/>
-        <v>142891.43</v>
+        <f t="shared" si="14"/>
+        <v>167238.43</v>
       </c>
       <c r="Q48" s="80">
-        <f t="shared" si="14"/>
-        <v>151465.43</v>
+        <f t="shared" si="15"/>
+        <v>177273.43</v>
       </c>
       <c r="R48" s="81">
-        <f t="shared" si="15"/>
-        <v>147178.43</v>
+        <f t="shared" si="16"/>
+        <v>172255.43</v>
       </c>
       <c r="S48" s="42">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.43000000000000022</v>
       </c>
     </row>
@@ -6397,7 +6452,7 @@
         <v>146</v>
       </c>
       <c r="D49" s="64">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>44</v>
       </c>
       <c r="E49" s="63" t="s">
@@ -6412,43 +6467,43 @@
       <c r="H49" s="72">
         <v>118186.44</v>
       </c>
-      <c r="I49" s="230">
+      <c r="I49" s="73">
         <f>H49</f>
         <v>118186.44</v>
       </c>
       <c r="J49" s="74"/>
       <c r="K49" s="75">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="L49" s="75">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M49" s="76">
         <v>0</v>
       </c>
       <c r="N49" s="77">
-        <f t="shared" si="12"/>
-        <v>118186.36342056</v>
+        <f t="shared" si="13"/>
+        <v>138324.82217409002</v>
       </c>
       <c r="O49" s="78">
         <v>0</v>
       </c>
       <c r="P49" s="79">
-        <f t="shared" si="13"/>
-        <v>118186.44</v>
+        <f t="shared" si="14"/>
+        <v>138325.44</v>
       </c>
       <c r="Q49" s="80">
-        <f t="shared" si="14"/>
-        <v>125278.44</v>
+        <f t="shared" si="15"/>
+        <v>146625.44</v>
       </c>
       <c r="R49" s="81">
-        <f t="shared" si="15"/>
-        <v>121732.44</v>
+        <f t="shared" si="16"/>
+        <v>142475.44</v>
       </c>
       <c r="S49" s="42">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.44000000000000022</v>
       </c>
     </row>
@@ -6460,7 +6515,7 @@
         <v>149</v>
       </c>
       <c r="D50" s="64">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>45</v>
       </c>
       <c r="E50" s="63" t="s">
@@ -6473,43 +6528,43 @@
       <c r="H50" s="72">
         <v>93468.45</v>
       </c>
-      <c r="I50" s="230">
+      <c r="I50" s="73">
         <f>93470</f>
         <v>93470</v>
       </c>
       <c r="J50" s="74"/>
       <c r="K50" s="75">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-1.5500000000029104</v>
       </c>
       <c r="L50" s="75">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M50" s="76">
         <v>0</v>
       </c>
       <c r="N50" s="77">
-        <f t="shared" si="12"/>
-        <v>93469.831034879986</v>
+        <f t="shared" si="13"/>
+        <v>109396.69672832001</v>
       </c>
       <c r="O50" s="78">
         <v>0</v>
       </c>
       <c r="P50" s="79">
-        <f t="shared" si="13"/>
-        <v>93468.45</v>
+        <f t="shared" si="14"/>
+        <v>109395.45</v>
       </c>
       <c r="Q50" s="80">
-        <f t="shared" si="14"/>
-        <v>99077.45</v>
+        <f t="shared" si="15"/>
+        <v>115959.45</v>
       </c>
       <c r="R50" s="81">
-        <f t="shared" si="15"/>
-        <v>96272.45</v>
+        <f t="shared" si="16"/>
+        <v>112677.45</v>
       </c>
       <c r="S50" s="42">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.45000000000000023</v>
       </c>
       <c r="U50" t="s">
@@ -6524,7 +6579,7 @@
         <v>153</v>
       </c>
       <c r="D51" s="64">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>46</v>
       </c>
       <c r="E51" s="63" t="s">
@@ -6539,40 +6594,40 @@
       <c r="H51" s="72">
         <v>142891.46</v>
       </c>
-      <c r="I51" s="230"/>
+      <c r="I51" s="73"/>
       <c r="J51" s="74"/>
       <c r="K51" s="75">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>142891.46</v>
       </c>
       <c r="L51" s="75">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>4286.7437999999993</v>
       </c>
       <c r="M51" s="76">
         <v>0</v>
       </c>
       <c r="N51" s="77">
-        <f t="shared" si="12"/>
-        <v>142890.51897480001</v>
+        <f t="shared" si="13"/>
+        <v>167238.46182845003</v>
       </c>
       <c r="O51" s="78">
         <v>0</v>
       </c>
       <c r="P51" s="79">
-        <f t="shared" si="13"/>
-        <v>290069.46000000002</v>
+        <f t="shared" si="14"/>
+        <v>314417.46000000002</v>
       </c>
       <c r="Q51" s="80">
-        <f t="shared" si="14"/>
-        <v>307474.46000000002</v>
+        <f t="shared" si="15"/>
+        <v>333283.46000000002</v>
       </c>
       <c r="R51" s="81">
-        <f t="shared" si="15"/>
-        <v>298771.46000000002</v>
+        <f t="shared" si="16"/>
+        <v>323850.46000000002</v>
       </c>
       <c r="S51" s="42">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.46000000000000024</v>
       </c>
     </row>
@@ -6584,7 +6639,7 @@
         <v>146</v>
       </c>
       <c r="D52" s="64">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>47</v>
       </c>
       <c r="E52" s="63" t="s">
@@ -6599,43 +6654,43 @@
       <c r="H52" s="72">
         <v>118186.47</v>
       </c>
-      <c r="I52" s="230">
-        <f t="shared" ref="I51:I59" si="18">H52</f>
+      <c r="I52" s="73">
+        <f t="shared" ref="I52:I59" si="19">H52</f>
         <v>118186.47</v>
       </c>
       <c r="J52" s="74"/>
       <c r="K52" s="75">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="L52" s="75">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M52" s="76">
         <v>0</v>
       </c>
       <c r="N52" s="77">
-        <f t="shared" si="12"/>
-        <v>118186.36342056</v>
+        <f t="shared" si="13"/>
+        <v>138324.82217409002</v>
       </c>
       <c r="O52" s="78">
         <v>0</v>
       </c>
       <c r="P52" s="79">
-        <f t="shared" si="13"/>
-        <v>118186.47</v>
+        <f t="shared" si="14"/>
+        <v>138325.47</v>
       </c>
       <c r="Q52" s="80">
-        <f t="shared" si="14"/>
-        <v>125278.47</v>
+        <f t="shared" si="15"/>
+        <v>146625.47</v>
       </c>
       <c r="R52" s="81">
-        <f t="shared" si="15"/>
-        <v>121732.47</v>
+        <f t="shared" si="16"/>
+        <v>142475.47</v>
       </c>
       <c r="S52" s="42">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.47000000000000025</v>
       </c>
     </row>
@@ -6647,7 +6702,7 @@
         <v>149</v>
       </c>
       <c r="D53" s="64">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>48</v>
       </c>
       <c r="E53" s="63" t="s">
@@ -6662,43 +6717,43 @@
       <c r="H53" s="72">
         <v>93470.48</v>
       </c>
-      <c r="I53" s="230">
-        <f t="shared" si="18"/>
+      <c r="I53" s="73">
+        <f t="shared" si="19"/>
         <v>93470.48</v>
       </c>
       <c r="J53" s="74"/>
       <c r="K53" s="75">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="L53" s="75">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M53" s="76">
         <v>0</v>
       </c>
       <c r="N53" s="77">
-        <f t="shared" si="12"/>
-        <v>93469.831034879986</v>
+        <f t="shared" si="13"/>
+        <v>109396.69672832001</v>
       </c>
       <c r="O53" s="78">
         <v>0</v>
       </c>
       <c r="P53" s="79">
-        <f t="shared" si="13"/>
-        <v>93470.48</v>
+        <f t="shared" si="14"/>
+        <v>109397.48</v>
       </c>
       <c r="Q53" s="80">
-        <f t="shared" si="14"/>
-        <v>99079.48</v>
+        <f t="shared" si="15"/>
+        <v>115961.48</v>
       </c>
       <c r="R53" s="81">
-        <f t="shared" si="15"/>
-        <v>96274.48</v>
+        <f t="shared" si="16"/>
+        <v>112679.48</v>
       </c>
       <c r="S53" s="42">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.48000000000000026</v>
       </c>
     </row>
@@ -6710,7 +6765,7 @@
         <v>153</v>
       </c>
       <c r="D54" s="64">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>49</v>
       </c>
       <c r="E54" s="63" t="s">
@@ -6725,43 +6780,43 @@
       <c r="H54" s="72">
         <v>142891.49</v>
       </c>
-      <c r="I54" s="230">
-        <f t="shared" si="18"/>
+      <c r="I54" s="73">
+        <f t="shared" si="19"/>
         <v>142891.49</v>
       </c>
       <c r="J54" s="74"/>
       <c r="K54" s="75">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="L54" s="75">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M54" s="76">
         <v>0</v>
       </c>
       <c r="N54" s="77">
-        <f t="shared" si="12"/>
-        <v>142890.51897480001</v>
+        <f t="shared" si="13"/>
+        <v>167238.46182845003</v>
       </c>
       <c r="O54" s="78">
         <v>0</v>
       </c>
       <c r="P54" s="79">
-        <f t="shared" si="13"/>
-        <v>142891.49</v>
+        <f t="shared" si="14"/>
+        <v>167238.49</v>
       </c>
       <c r="Q54" s="80">
-        <f t="shared" si="14"/>
-        <v>151465.49</v>
+        <f t="shared" si="15"/>
+        <v>177273.49</v>
       </c>
       <c r="R54" s="81">
-        <f t="shared" si="15"/>
-        <v>147178.49</v>
+        <f t="shared" si="16"/>
+        <v>172255.49</v>
       </c>
       <c r="S54" s="42">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.49000000000000027</v>
       </c>
     </row>
@@ -6773,7 +6828,7 @@
         <v>146</v>
       </c>
       <c r="D55" s="64">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>50</v>
       </c>
       <c r="E55" s="63" t="s">
@@ -6786,43 +6841,43 @@
       <c r="H55" s="72">
         <v>118186.5</v>
       </c>
-      <c r="I55" s="230">
-        <f t="shared" si="18"/>
+      <c r="I55" s="73">
+        <f t="shared" si="19"/>
         <v>118186.5</v>
       </c>
       <c r="J55" s="74"/>
       <c r="K55" s="75">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="L55" s="75">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M55" s="76">
         <v>0</v>
       </c>
       <c r="N55" s="77">
-        <f t="shared" si="12"/>
-        <v>118186.36342056</v>
+        <f t="shared" si="13"/>
+        <v>138324.82217409002</v>
       </c>
       <c r="O55" s="78">
         <v>0</v>
       </c>
       <c r="P55" s="79">
-        <f t="shared" si="13"/>
-        <v>118186.5</v>
+        <f t="shared" si="14"/>
+        <v>138325.5</v>
       </c>
       <c r="Q55" s="80">
-        <f t="shared" si="14"/>
-        <v>125278.5</v>
+        <f t="shared" si="15"/>
+        <v>146625.5</v>
       </c>
       <c r="R55" s="81">
-        <f t="shared" si="15"/>
-        <v>121732.5</v>
+        <f t="shared" si="16"/>
+        <v>142475.5</v>
       </c>
       <c r="S55" s="42">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.50000000000000022</v>
       </c>
     </row>
@@ -6834,7 +6889,7 @@
         <v>149</v>
       </c>
       <c r="D56" s="64">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>51</v>
       </c>
       <c r="E56" s="63" t="s">
@@ -6847,42 +6902,42 @@
       <c r="H56" s="72">
         <v>99249.51</v>
       </c>
-      <c r="I56" s="230">
+      <c r="I56" s="73">
         <v>96358</v>
       </c>
       <c r="J56" s="74"/>
       <c r="K56" s="75">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2891.5099999999948</v>
       </c>
       <c r="L56" s="75">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>86.745299999999844</v>
       </c>
       <c r="M56" s="76">
         <v>0</v>
       </c>
       <c r="N56" s="77">
-        <f t="shared" si="12"/>
-        <v>93469.831034879986</v>
+        <f t="shared" si="13"/>
+        <v>109396.69672832001</v>
       </c>
       <c r="O56" s="78">
         <v>0</v>
       </c>
       <c r="P56" s="79">
-        <f t="shared" si="13"/>
-        <v>96448.51</v>
+        <f t="shared" si="14"/>
+        <v>112375.51</v>
       </c>
       <c r="Q56" s="80">
-        <f t="shared" si="14"/>
-        <v>102235.51</v>
+        <f t="shared" si="15"/>
+        <v>119118.51</v>
       </c>
       <c r="R56" s="81">
-        <f t="shared" si="15"/>
-        <v>99341.51</v>
+        <f t="shared" si="16"/>
+        <v>115746.51</v>
       </c>
       <c r="S56" s="42">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.51000000000000023</v>
       </c>
       <c r="U56" t="s">
@@ -6897,7 +6952,7 @@
         <v>153</v>
       </c>
       <c r="D57" s="64">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>52</v>
       </c>
       <c r="E57" s="63" t="s">
@@ -6910,43 +6965,43 @@
       <c r="H57" s="72">
         <v>142891.51999999999</v>
       </c>
-      <c r="I57" s="230">
-        <f t="shared" si="18"/>
+      <c r="I57" s="73">
+        <f t="shared" si="19"/>
         <v>142891.51999999999</v>
       </c>
       <c r="J57" s="74"/>
       <c r="K57" s="75">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="L57" s="75">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M57" s="76">
         <v>0</v>
       </c>
       <c r="N57" s="77">
-        <f t="shared" si="12"/>
-        <v>142890.51897480001</v>
+        <f t="shared" si="13"/>
+        <v>167238.46182845003</v>
       </c>
       <c r="O57" s="78">
         <v>0</v>
       </c>
       <c r="P57" s="79">
-        <f t="shared" si="13"/>
-        <v>142891.51999999999</v>
+        <f t="shared" si="14"/>
+        <v>167238.51999999999</v>
       </c>
       <c r="Q57" s="80">
-        <f t="shared" si="14"/>
-        <v>151465.51999999999</v>
+        <f t="shared" si="15"/>
+        <v>177273.52</v>
       </c>
       <c r="R57" s="81">
-        <f t="shared" si="15"/>
-        <v>147178.51999999999</v>
+        <f t="shared" si="16"/>
+        <v>172255.52</v>
       </c>
       <c r="S57" s="42">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.52000000000000024</v>
       </c>
     </row>
@@ -6958,7 +7013,7 @@
         <v>146</v>
       </c>
       <c r="D58" s="64">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>53</v>
       </c>
       <c r="E58" s="63" t="s">
@@ -6971,43 +7026,43 @@
       <c r="H58" s="72">
         <v>118186.53</v>
       </c>
-      <c r="I58" s="230">
-        <f t="shared" si="18"/>
+      <c r="I58" s="73">
+        <f t="shared" si="19"/>
         <v>118186.53</v>
       </c>
       <c r="J58" s="74"/>
       <c r="K58" s="75">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="L58" s="75">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M58" s="76">
         <v>0</v>
       </c>
       <c r="N58" s="77">
-        <f t="shared" si="12"/>
-        <v>118186.36342056</v>
+        <f t="shared" si="13"/>
+        <v>138324.82217409002</v>
       </c>
       <c r="O58" s="78">
         <v>0</v>
       </c>
       <c r="P58" s="79">
-        <f t="shared" si="13"/>
-        <v>118186.53</v>
+        <f t="shared" si="14"/>
+        <v>138325.53</v>
       </c>
       <c r="Q58" s="80">
-        <f t="shared" si="14"/>
-        <v>125278.53</v>
+        <f t="shared" si="15"/>
+        <v>146625.53</v>
       </c>
       <c r="R58" s="81">
-        <f t="shared" si="15"/>
-        <v>121732.53</v>
+        <f t="shared" si="16"/>
+        <v>142475.53</v>
       </c>
       <c r="S58" s="42">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.53000000000000025</v>
       </c>
     </row>
@@ -7019,7 +7074,7 @@
         <v>149</v>
       </c>
       <c r="D59" s="64">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>54</v>
       </c>
       <c r="E59" s="63" t="s">
@@ -7032,43 +7087,43 @@
       <c r="H59" s="72">
         <v>93470.54</v>
       </c>
-      <c r="I59" s="230">
-        <f t="shared" si="18"/>
+      <c r="I59" s="73">
+        <f t="shared" si="19"/>
         <v>93470.54</v>
       </c>
       <c r="J59" s="74"/>
       <c r="K59" s="75">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="L59" s="75">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M59" s="76">
         <v>0</v>
       </c>
       <c r="N59" s="77">
-        <f t="shared" si="12"/>
-        <v>93469.831034879986</v>
+        <f t="shared" si="13"/>
+        <v>109396.69672832001</v>
       </c>
       <c r="O59" s="78">
         <v>0</v>
       </c>
       <c r="P59" s="79">
-        <f t="shared" si="13"/>
-        <v>93470.54</v>
+        <f t="shared" si="14"/>
+        <v>109397.54</v>
       </c>
       <c r="Q59" s="80">
-        <f t="shared" si="14"/>
-        <v>99079.54</v>
+        <f t="shared" si="15"/>
+        <v>115961.54</v>
       </c>
       <c r="R59" s="81">
-        <f t="shared" si="15"/>
-        <v>96274.54</v>
+        <f t="shared" si="16"/>
+        <v>112679.54</v>
       </c>
       <c r="S59" s="42">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.54000000000000026</v>
       </c>
     </row>
@@ -7080,7 +7135,7 @@
         <v>153</v>
       </c>
       <c r="D60" s="64">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>55</v>
       </c>
       <c r="E60" s="63" t="s">
@@ -7095,40 +7150,40 @@
       <c r="H60" s="72">
         <v>730237.55</v>
       </c>
-      <c r="I60" s="230"/>
+      <c r="I60" s="73"/>
       <c r="J60" s="74"/>
       <c r="K60" s="75">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>730237.55</v>
       </c>
       <c r="L60" s="75">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>21907.126500000002</v>
       </c>
       <c r="M60" s="76">
         <v>0</v>
       </c>
       <c r="N60" s="77">
-        <f t="shared" si="12"/>
-        <v>142890.51897480001</v>
+        <f t="shared" si="13"/>
+        <v>167238.46182845003</v>
       </c>
       <c r="O60" s="78">
         <v>0</v>
       </c>
       <c r="P60" s="79">
-        <f t="shared" si="13"/>
-        <v>895035.55</v>
+        <f t="shared" si="14"/>
+        <v>919383.55</v>
       </c>
       <c r="Q60" s="80">
-        <f t="shared" si="14"/>
-        <v>948738.55</v>
+        <f t="shared" si="15"/>
+        <v>974547.55</v>
       </c>
       <c r="R60" s="81">
-        <f t="shared" si="15"/>
-        <v>921886.55</v>
+        <f t="shared" si="16"/>
+        <v>946965.55</v>
       </c>
       <c r="S60" s="42">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.55000000000000027</v>
       </c>
     </row>
@@ -7140,7 +7195,7 @@
         <v>146</v>
       </c>
       <c r="D61" s="64">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>56</v>
       </c>
       <c r="E61" s="63" t="s">
@@ -7155,41 +7210,41 @@
       <c r="H61" s="72">
         <v>118186.56</v>
       </c>
-      <c r="I61" s="230">
+      <c r="I61" s="73">
         <f>H61</f>
         <v>118186.56</v>
       </c>
       <c r="J61" s="74"/>
       <c r="K61" s="75">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="L61" s="75">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M61" s="76">
         <v>0</v>
       </c>
       <c r="N61" s="77">
-        <f t="shared" si="12"/>
-        <v>118186.36342056</v>
+        <f t="shared" si="13"/>
+        <v>138324.82217409002</v>
       </c>
       <c r="O61" s="78"/>
       <c r="P61" s="79">
-        <f t="shared" si="13"/>
-        <v>118186.56</v>
+        <f t="shared" si="14"/>
+        <v>138325.56</v>
       </c>
       <c r="Q61" s="80">
-        <f t="shared" si="14"/>
-        <v>125278.56</v>
+        <f t="shared" si="15"/>
+        <v>146625.56</v>
       </c>
       <c r="R61" s="81">
-        <f t="shared" si="15"/>
-        <v>121732.56</v>
+        <f t="shared" si="16"/>
+        <v>142475.56</v>
       </c>
       <c r="S61" s="42">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.56000000000000028</v>
       </c>
     </row>
@@ -7201,7 +7256,7 @@
         <v>149</v>
       </c>
       <c r="D62" s="64">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>57</v>
       </c>
       <c r="E62" s="63" t="s">
@@ -7216,42 +7271,42 @@
       <c r="H62" s="72">
         <v>90653.57</v>
       </c>
-      <c r="I62" s="230">
+      <c r="I62" s="73">
         <v>96721.57</v>
       </c>
       <c r="J62" s="74"/>
       <c r="K62" s="75">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-6068</v>
       </c>
       <c r="L62" s="75">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M62" s="76">
         <v>0</v>
       </c>
       <c r="N62" s="77">
-        <f t="shared" si="12"/>
-        <v>93469.831034879986</v>
+        <f t="shared" si="13"/>
+        <v>109396.69672832001</v>
       </c>
       <c r="O62" s="78">
         <v>0</v>
       </c>
       <c r="P62" s="79">
-        <f t="shared" si="13"/>
-        <v>87402.57</v>
+        <f t="shared" si="14"/>
+        <v>103329.57</v>
       </c>
       <c r="Q62" s="80">
-        <f t="shared" si="14"/>
-        <v>92647.57</v>
+        <f t="shared" si="15"/>
+        <v>109529.57</v>
       </c>
       <c r="R62" s="81">
-        <f t="shared" si="15"/>
-        <v>90024.57</v>
+        <f t="shared" si="16"/>
+        <v>106429.57</v>
       </c>
       <c r="S62" s="42">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.57000000000000028</v>
       </c>
     </row>
@@ -7263,7 +7318,7 @@
         <v>153</v>
       </c>
       <c r="D63" s="64">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>58</v>
       </c>
       <c r="E63" s="63" t="s">
@@ -7276,43 +7331,43 @@
       <c r="H63" s="72">
         <v>142891.57999999999</v>
       </c>
-      <c r="I63" s="230">
+      <c r="I63" s="73">
         <f>H63</f>
         <v>142891.57999999999</v>
       </c>
       <c r="J63" s="74"/>
       <c r="K63" s="75">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="L63" s="75">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M63" s="76">
         <v>0</v>
       </c>
       <c r="N63" s="77">
-        <f t="shared" si="12"/>
-        <v>142890.51897480001</v>
+        <f t="shared" si="13"/>
+        <v>167238.46182845003</v>
       </c>
       <c r="O63" s="78">
         <v>0</v>
       </c>
       <c r="P63" s="79">
-        <f t="shared" si="13"/>
-        <v>142891.57999999999</v>
+        <f t="shared" si="14"/>
+        <v>167238.57999999999</v>
       </c>
       <c r="Q63" s="80">
-        <f t="shared" si="14"/>
-        <v>151465.57999999999</v>
+        <f t="shared" si="15"/>
+        <v>177273.58</v>
       </c>
       <c r="R63" s="81">
-        <f t="shared" si="15"/>
-        <v>147178.57999999999</v>
+        <f t="shared" si="16"/>
+        <v>172255.58</v>
       </c>
       <c r="S63" s="42">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.58000000000000029</v>
       </c>
     </row>
@@ -7324,7 +7379,7 @@
         <v>146</v>
       </c>
       <c r="D64" s="64">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>59</v>
       </c>
       <c r="E64" s="63" t="s">
@@ -7339,42 +7394,43 @@
       <c r="H64" s="72">
         <v>118186.59</v>
       </c>
-      <c r="I64" s="230">
-        <v>280000</v>
+      <c r="I64" s="73">
+        <f>RESUMEN!D69</f>
+        <v>390000</v>
       </c>
       <c r="J64" s="74"/>
       <c r="K64" s="75">
-        <f t="shared" si="10"/>
-        <v>-161813.41</v>
+        <f t="shared" si="11"/>
+        <v>-271813.41000000003</v>
       </c>
       <c r="L64" s="75">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M64" s="76">
         <v>0</v>
       </c>
       <c r="N64" s="77">
-        <f t="shared" si="12"/>
-        <v>118186.36342056</v>
+        <f t="shared" si="13"/>
+        <v>138324.82217409002</v>
       </c>
       <c r="O64" s="78">
         <v>0</v>
       </c>
       <c r="P64" s="79">
-        <f t="shared" si="13"/>
-        <v>-43626.41</v>
+        <f t="shared" si="14"/>
+        <v>-133488.41</v>
       </c>
       <c r="Q64" s="80">
-        <f t="shared" si="14"/>
-        <v>-46243.41</v>
+        <f t="shared" si="15"/>
+        <v>-141497.41</v>
       </c>
       <c r="R64" s="81">
-        <f t="shared" si="15"/>
-        <v>-44935.41</v>
+        <f t="shared" si="16"/>
+        <v>-137493.41</v>
       </c>
       <c r="S64" s="42">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.5900000000000003</v>
       </c>
     </row>
@@ -7386,7 +7442,7 @@
         <v>149</v>
       </c>
       <c r="D65" s="64">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>60</v>
       </c>
       <c r="E65" s="63" t="s">
@@ -7399,40 +7455,40 @@
       <c r="H65" s="72">
         <v>192479.6</v>
       </c>
-      <c r="I65" s="230"/>
+      <c r="I65" s="73"/>
       <c r="J65" s="74"/>
       <c r="K65" s="75">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>192479.6</v>
       </c>
       <c r="L65" s="75">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>5774.3879999999999</v>
       </c>
       <c r="M65" s="76">
         <v>0</v>
       </c>
       <c r="N65" s="77">
-        <f t="shared" si="12"/>
-        <v>93469.831034879986</v>
+        <f t="shared" si="13"/>
+        <v>109396.69672832001</v>
       </c>
       <c r="O65" s="78">
         <v>0</v>
       </c>
       <c r="P65" s="79">
-        <f t="shared" si="13"/>
-        <v>291724.59999999998</v>
+        <f t="shared" si="14"/>
+        <v>307651.59999999998</v>
       </c>
       <c r="Q65" s="80">
-        <f t="shared" si="14"/>
-        <v>309228.59999999998</v>
+        <f t="shared" si="15"/>
+        <v>326111.59999999998</v>
       </c>
       <c r="R65" s="81">
-        <f t="shared" si="15"/>
-        <v>300476.59999999998</v>
+        <f t="shared" si="16"/>
+        <v>316881.59999999998</v>
       </c>
       <c r="S65" s="42">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.60000000000000031</v>
       </c>
       <c r="U65" t="s">
@@ -7447,7 +7503,7 @@
         <v>153</v>
       </c>
       <c r="D66" s="64">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>61</v>
       </c>
       <c r="E66" s="63" t="s">
@@ -7460,43 +7516,43 @@
       <c r="H66" s="72">
         <v>142891.60999999999</v>
       </c>
-      <c r="I66" s="230">
+      <c r="I66" s="73">
         <f>H66</f>
         <v>142891.60999999999</v>
       </c>
       <c r="J66" s="74"/>
       <c r="K66" s="75">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="L66" s="75">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M66" s="76">
         <v>0</v>
       </c>
       <c r="N66" s="77">
-        <f t="shared" si="12"/>
-        <v>142890.51897480001</v>
+        <f t="shared" si="13"/>
+        <v>167238.46182845003</v>
       </c>
       <c r="O66" s="78">
         <v>0</v>
       </c>
       <c r="P66" s="79">
-        <f t="shared" si="13"/>
-        <v>142891.60999999999</v>
+        <f t="shared" si="14"/>
+        <v>167238.60999999999</v>
       </c>
       <c r="Q66" s="80">
-        <f t="shared" si="14"/>
-        <v>151465.60999999999</v>
+        <f t="shared" si="15"/>
+        <v>177273.61</v>
       </c>
       <c r="R66" s="81">
-        <f t="shared" si="15"/>
-        <v>147178.60999999999</v>
+        <f t="shared" si="16"/>
+        <v>172255.61</v>
       </c>
       <c r="S66" s="42">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.61000000000000032</v>
       </c>
       <c r="U66" t="s">
@@ -7511,7 +7567,7 @@
         <v>146</v>
       </c>
       <c r="D67" s="64">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>62</v>
       </c>
       <c r="E67" s="63" t="s">
@@ -7526,43 +7582,43 @@
       <c r="H67" s="72">
         <v>118186.62</v>
       </c>
-      <c r="I67" s="230">
+      <c r="I67" s="73">
         <f>H67</f>
         <v>118186.62</v>
       </c>
       <c r="J67" s="74"/>
       <c r="K67" s="75">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="L67" s="75">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M67" s="76">
         <v>0</v>
       </c>
       <c r="N67" s="77">
-        <f t="shared" si="12"/>
-        <v>118186.36342056</v>
+        <f t="shared" si="13"/>
+        <v>138324.82217409002</v>
       </c>
       <c r="O67" s="78">
         <v>0</v>
       </c>
       <c r="P67" s="79">
-        <f t="shared" si="13"/>
-        <v>118186.62</v>
+        <f t="shared" si="14"/>
+        <v>138325.62</v>
       </c>
       <c r="Q67" s="80">
-        <f t="shared" si="14"/>
-        <v>125278.62</v>
+        <f t="shared" si="15"/>
+        <v>146625.62</v>
       </c>
       <c r="R67" s="81">
-        <f t="shared" si="15"/>
-        <v>121732.62</v>
+        <f t="shared" si="16"/>
+        <v>142475.62</v>
       </c>
       <c r="S67" s="42">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.62000000000000033</v>
       </c>
       <c r="U67" t="s">
@@ -7577,7 +7633,7 @@
         <v>149</v>
       </c>
       <c r="D68" s="64">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>63</v>
       </c>
       <c r="E68" s="63" t="s">
@@ -7592,43 +7648,43 @@
       <c r="H68" s="72">
         <v>93470.63</v>
       </c>
-      <c r="I68" s="230">
+      <c r="I68" s="73">
         <f>H68</f>
         <v>93470.63</v>
       </c>
       <c r="J68" s="74"/>
       <c r="K68" s="75">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="L68" s="75">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M68" s="76">
         <v>0</v>
       </c>
       <c r="N68" s="77">
-        <f t="shared" si="12"/>
-        <v>93469.831034879986</v>
+        <f t="shared" si="13"/>
+        <v>109396.69672832001</v>
       </c>
       <c r="O68" s="78">
         <v>0</v>
       </c>
       <c r="P68" s="79">
-        <f t="shared" si="13"/>
-        <v>93470.63</v>
+        <f t="shared" si="14"/>
+        <v>109397.63</v>
       </c>
       <c r="Q68" s="80">
-        <f t="shared" si="14"/>
-        <v>99079.63</v>
+        <f t="shared" si="15"/>
+        <v>115961.63</v>
       </c>
       <c r="R68" s="81">
-        <f t="shared" si="15"/>
-        <v>96274.63</v>
+        <f t="shared" si="16"/>
+        <v>112679.63</v>
       </c>
       <c r="S68" s="42">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.63000000000000034</v>
       </c>
     </row>
@@ -7640,7 +7696,7 @@
         <v>153</v>
       </c>
       <c r="D69" s="64">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>64</v>
       </c>
       <c r="E69" s="63" t="s">
@@ -7653,43 +7709,43 @@
       <c r="H69" s="72">
         <v>142891.64000000001</v>
       </c>
-      <c r="I69" s="230">
+      <c r="I69" s="73">
         <f>H69</f>
         <v>142891.64000000001</v>
       </c>
       <c r="J69" s="74"/>
       <c r="K69" s="75">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="L69" s="75">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M69" s="76">
         <v>0</v>
       </c>
       <c r="N69" s="77">
-        <f t="shared" si="12"/>
-        <v>142890.51897480001</v>
+        <f t="shared" si="13"/>
+        <v>167238.46182845003</v>
       </c>
       <c r="O69" s="78">
         <v>0</v>
       </c>
       <c r="P69" s="79">
-        <f t="shared" si="13"/>
-        <v>142891.64000000001</v>
+        <f t="shared" si="14"/>
+        <v>167238.64000000001</v>
       </c>
       <c r="Q69" s="80">
-        <f t="shared" si="14"/>
-        <v>151465.64000000001</v>
+        <f t="shared" si="15"/>
+        <v>177273.64</v>
       </c>
       <c r="R69" s="81">
-        <f t="shared" si="15"/>
-        <v>147178.64000000001</v>
+        <f t="shared" si="16"/>
+        <v>172255.64</v>
       </c>
       <c r="S69" s="42">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.64000000000000035</v>
       </c>
     </row>
@@ -7701,7 +7757,7 @@
         <v>146</v>
       </c>
       <c r="D70" s="64">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>65</v>
       </c>
       <c r="E70" s="63" t="s">
@@ -7714,43 +7770,43 @@
       <c r="H70" s="72">
         <v>114640.65</v>
       </c>
-      <c r="I70" s="230">
+      <c r="I70" s="73">
         <f>H70</f>
         <v>114640.65</v>
       </c>
       <c r="J70" s="74"/>
       <c r="K70" s="75">
-        <f t="shared" ref="K70:K75" si="19">H70-I70</f>
+        <f t="shared" ref="K70:K75" si="20">H70-I70</f>
         <v>0</v>
       </c>
       <c r="L70" s="75">
-        <f t="shared" ref="L70:L75" si="20">IF(K70&gt;0,K70*3%,0)</f>
+        <f t="shared" ref="L70:L75" si="21">IF(K70&gt;0,K70*3%,0)</f>
         <v>0</v>
       </c>
       <c r="M70" s="76">
         <v>0</v>
       </c>
       <c r="N70" s="77">
-        <f t="shared" ref="N70:N75" si="21">P$2*G70%</f>
-        <v>118186.36342056</v>
+        <f t="shared" ref="N70:N75" si="22">P$2*G70%</f>
+        <v>138324.82217409002</v>
       </c>
       <c r="O70" s="78">
         <v>0</v>
       </c>
       <c r="P70" s="79">
-        <f t="shared" ref="P70:P75" si="22">ROUND(SUM(K70:O70),0) + S70</f>
-        <v>118186.65</v>
+        <f t="shared" ref="P70:P75" si="23">ROUND(SUM(K70:O70),0) + S70</f>
+        <v>138325.65</v>
       </c>
       <c r="Q70" s="80">
-        <f t="shared" ref="Q70:Q75" si="23">ROUND(P70*6% + P70,0) + S70</f>
-        <v>125278.65</v>
+        <f t="shared" ref="Q70:Q75" si="24">ROUND(P70*6% + P70,0) + S70</f>
+        <v>146625.65</v>
       </c>
       <c r="R70" s="81">
-        <f t="shared" ref="R70:R75" si="24">ROUND(P70*3%,0) + P70</f>
-        <v>121732.65</v>
+        <f t="shared" ref="R70:R75" si="25">ROUND(P70*3%,0) + P70</f>
+        <v>142475.65</v>
       </c>
       <c r="S70" s="42">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.65000000000000036</v>
       </c>
     </row>
@@ -7762,7 +7818,7 @@
         <v>149</v>
       </c>
       <c r="D71" s="64">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>66</v>
       </c>
       <c r="E71" s="63" t="s">
@@ -7777,40 +7833,40 @@
       <c r="H71" s="72">
         <v>187089.66</v>
       </c>
-      <c r="I71" s="230"/>
+      <c r="I71" s="73"/>
       <c r="J71" s="74"/>
       <c r="K71" s="75">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>187089.66</v>
       </c>
       <c r="L71" s="75">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5612.6898000000001</v>
       </c>
       <c r="M71" s="76">
         <v>0</v>
       </c>
       <c r="N71" s="77">
-        <f t="shared" si="21"/>
-        <v>93469.831034879986</v>
+        <f t="shared" si="22"/>
+        <v>109396.69672832001</v>
       </c>
       <c r="O71" s="78">
         <v>0</v>
       </c>
       <c r="P71" s="79">
-        <f t="shared" si="22"/>
-        <v>286172.65999999997</v>
+        <f t="shared" si="23"/>
+        <v>302099.65999999997</v>
       </c>
       <c r="Q71" s="80">
-        <f t="shared" si="23"/>
-        <v>303343.65999999997</v>
+        <f t="shared" si="24"/>
+        <v>320226.65999999997</v>
       </c>
       <c r="R71" s="81">
-        <f t="shared" si="24"/>
-        <v>294757.65999999997</v>
+        <f t="shared" si="25"/>
+        <v>311162.65999999997</v>
       </c>
       <c r="S71" s="42">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.66000000000000036</v>
       </c>
     </row>
@@ -7822,7 +7878,7 @@
         <v>153</v>
       </c>
       <c r="D72" s="64">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>67</v>
       </c>
       <c r="E72" s="63" t="s">
@@ -7835,42 +7891,42 @@
       <c r="H72" s="72">
         <v>142891.67000000001</v>
       </c>
-      <c r="I72" s="230">
+      <c r="I72" s="73">
         <v>147148.67000000001</v>
       </c>
       <c r="J72" s="74"/>
       <c r="K72" s="75">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-4257</v>
       </c>
       <c r="L72" s="75">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M72" s="76">
         <v>0</v>
       </c>
       <c r="N72" s="77">
-        <f t="shared" si="21"/>
-        <v>142890.51897480001</v>
+        <f t="shared" si="22"/>
+        <v>167238.46182845003</v>
       </c>
       <c r="O72" s="78">
         <v>0</v>
       </c>
       <c r="P72" s="79">
-        <f t="shared" si="22"/>
-        <v>138634.67000000001</v>
+        <f t="shared" si="23"/>
+        <v>162981.67000000001</v>
       </c>
       <c r="Q72" s="80">
-        <f t="shared" si="23"/>
-        <v>146953.67000000001</v>
+        <f t="shared" si="24"/>
+        <v>172761.67</v>
       </c>
       <c r="R72" s="81">
-        <f t="shared" si="24"/>
-        <v>142793.67000000001</v>
+        <f t="shared" si="25"/>
+        <v>167870.67</v>
       </c>
       <c r="S72" s="42">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.67000000000000037</v>
       </c>
     </row>
@@ -7882,7 +7938,7 @@
         <v>146</v>
       </c>
       <c r="D73" s="64">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>68</v>
       </c>
       <c r="E73" s="88" t="s">
@@ -7895,43 +7951,43 @@
       <c r="H73" s="90">
         <v>118186.68</v>
       </c>
-      <c r="I73" s="230">
+      <c r="I73" s="73">
         <f>H73</f>
         <v>118186.68</v>
       </c>
       <c r="J73" s="92"/>
       <c r="K73" s="93">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="L73" s="75">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M73" s="76">
         <v>0</v>
       </c>
       <c r="N73" s="94">
-        <f t="shared" si="21"/>
-        <v>118186.36342056</v>
+        <f t="shared" si="22"/>
+        <v>138324.82217409002</v>
       </c>
       <c r="O73" s="95">
         <v>0</v>
       </c>
       <c r="P73" s="79">
-        <f t="shared" si="22"/>
-        <v>118186.68</v>
+        <f t="shared" si="23"/>
+        <v>138325.68</v>
       </c>
       <c r="Q73" s="80">
-        <f t="shared" si="23"/>
-        <v>125278.68</v>
+        <f t="shared" si="24"/>
+        <v>146625.68</v>
       </c>
       <c r="R73" s="81">
-        <f t="shared" si="24"/>
-        <v>121732.68</v>
+        <f t="shared" si="25"/>
+        <v>142475.68</v>
       </c>
       <c r="S73" s="42">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.68000000000000038</v>
       </c>
     </row>
@@ -7943,7 +7999,7 @@
         <v>149</v>
       </c>
       <c r="D74" s="64">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>69</v>
       </c>
       <c r="E74" s="64" t="s">
@@ -7956,43 +8012,43 @@
       <c r="H74" s="90">
         <v>93470.69</v>
       </c>
-      <c r="I74" s="230">
+      <c r="I74" s="73">
         <f>H74</f>
         <v>93470.69</v>
       </c>
       <c r="J74" s="92"/>
       <c r="K74" s="93">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="L74" s="75">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M74" s="76">
         <v>0</v>
       </c>
       <c r="N74" s="94">
-        <f t="shared" si="21"/>
-        <v>93469.831034879986</v>
+        <f t="shared" si="22"/>
+        <v>109396.69672832001</v>
       </c>
       <c r="O74" s="95">
         <v>0</v>
       </c>
       <c r="P74" s="79">
-        <f t="shared" si="22"/>
-        <v>93470.69</v>
+        <f t="shared" si="23"/>
+        <v>109397.69</v>
       </c>
       <c r="Q74" s="80">
-        <f t="shared" si="23"/>
-        <v>99079.69</v>
+        <f t="shared" si="24"/>
+        <v>115962.69</v>
       </c>
       <c r="R74" s="81">
-        <f t="shared" si="24"/>
-        <v>96274.69</v>
+        <f t="shared" si="25"/>
+        <v>112679.69</v>
       </c>
       <c r="S74" s="42">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.69000000000000039</v>
       </c>
     </row>
@@ -8004,7 +8060,7 @@
         <v>153</v>
       </c>
       <c r="D75" s="64">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>70</v>
       </c>
       <c r="E75" s="64" t="s">
@@ -8017,43 +8073,43 @@
       <c r="H75" s="90">
         <v>142940.70000000001</v>
       </c>
-      <c r="I75" s="230">
+      <c r="I75" s="73">
         <f>H75</f>
         <v>142940.70000000001</v>
       </c>
       <c r="J75" s="92"/>
       <c r="K75" s="93">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="L75" s="75">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M75" s="76">
         <v>0</v>
       </c>
       <c r="N75" s="94">
-        <f t="shared" si="21"/>
-        <v>142940.02630055998</v>
+        <f t="shared" si="22"/>
+        <v>167296.40499409003</v>
       </c>
       <c r="O75" s="95">
         <v>0</v>
       </c>
       <c r="P75" s="79">
-        <f t="shared" si="22"/>
-        <v>142940.70000000001</v>
+        <f t="shared" si="23"/>
+        <v>167296.70000000001</v>
       </c>
       <c r="Q75" s="80">
-        <f t="shared" si="23"/>
-        <v>151517.70000000001</v>
+        <f t="shared" si="24"/>
+        <v>177335.7</v>
       </c>
       <c r="R75" s="81">
-        <f t="shared" si="24"/>
-        <v>147228.70000000001</v>
+        <f t="shared" si="25"/>
+        <v>172315.7</v>
       </c>
       <c r="S75" s="42">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.7000000000000004</v>
       </c>
     </row>
@@ -8119,7 +8175,7 @@
     </row>
     <row r="79" spans="2:21" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B79" s="97"/>
-      <c r="C79" s="135"/>
+      <c r="C79" s="134"/>
       <c r="D79" s="87"/>
       <c r="E79" s="64"/>
       <c r="F79" s="65"/>
@@ -8159,7 +8215,7 @@
     </row>
     <row r="81" spans="2:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B81" s="102"/>
-      <c r="C81" s="136"/>
+      <c r="C81" s="135"/>
       <c r="D81" s="103"/>
       <c r="E81" s="104"/>
       <c r="F81" s="104"/>
@@ -8173,7 +8229,7 @@
       </c>
       <c r="I81" s="61">
         <f>SUM(I6:I80)</f>
-        <v>12414643.369999997</v>
+        <v>12524643.369999997</v>
       </c>
       <c r="J81" s="52">
         <f>SUM(J6:J80)</f>
@@ -8181,7 +8237,7 @@
       </c>
       <c r="K81" s="61">
         <f>SUM(K6:K80)</f>
-        <v>5560880.4799999995</v>
+        <v>5450880.4799999995</v>
       </c>
       <c r="L81" s="61"/>
       <c r="M81" s="61">
@@ -8190,7 +8246,7 @@
       </c>
       <c r="N81" s="61">
         <f>SUM(N6:N80)</f>
-        <v>12376831.439999986</v>
+        <v>14485791.410000015</v>
       </c>
       <c r="O81" s="61">
         <f>SUM(O6:O80)</f>
@@ -8198,11 +8254,11 @@
       </c>
       <c r="P81" s="106">
         <f>SUM(P6:P80)</f>
-        <v>18143704.850000001</v>
+        <v>20142661.850000001</v>
       </c>
       <c r="Q81" s="106">
         <f>SUM(Q6:Q80)</f>
-        <v>19232357.849999998</v>
+        <v>21351243.849999998</v>
       </c>
       <c r="R81" s="106"/>
     </row>
@@ -8212,102 +8268,94 @@
     </row>
     <row r="83" spans="2:18" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="84" spans="2:18" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E84" s="200" t="str">
+      <c r="E84" s="217" t="str">
         <f>RESUMEN!A14</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. CASO CONTRARIO SE INFORMARA VIA CARTA DOCUMENTO A LA UNIDAD FUNCIONAL QUE CREEMOS QUE CORRESPONDE, CUYO COSTO SERA IMPUTADO A LA UNIDAD FUNCIONAL SOSPECHADA.</v>
       </c>
-      <c r="F84" s="201"/>
-      <c r="G84" s="201"/>
-      <c r="H84" s="201"/>
-      <c r="I84" s="201"/>
-      <c r="J84" s="201"/>
-      <c r="K84" s="201"/>
-      <c r="L84" s="201"/>
-      <c r="M84" s="201"/>
-      <c r="N84" s="201"/>
-      <c r="O84" s="201"/>
-      <c r="P84" s="201"/>
+      <c r="F84" s="212"/>
+      <c r="G84" s="212"/>
+      <c r="H84" s="212"/>
+      <c r="I84" s="212"/>
+      <c r="J84" s="212"/>
+      <c r="K84" s="212"/>
+      <c r="L84" s="212"/>
+      <c r="M84" s="212"/>
+      <c r="N84" s="212"/>
+      <c r="O84" s="212"/>
+      <c r="P84" s="212"/>
     </row>
     <row r="85" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E85" s="201"/>
-      <c r="F85" s="201"/>
-      <c r="G85" s="201"/>
-      <c r="H85" s="201"/>
-      <c r="I85" s="201"/>
-      <c r="J85" s="201"/>
-      <c r="K85" s="201"/>
-      <c r="L85" s="201"/>
-      <c r="M85" s="201"/>
-      <c r="N85" s="201"/>
-      <c r="O85" s="201"/>
-      <c r="P85" s="201"/>
+      <c r="E85" s="212"/>
+      <c r="F85" s="212"/>
+      <c r="G85" s="212"/>
+      <c r="H85" s="212"/>
+      <c r="I85" s="212"/>
+      <c r="J85" s="212"/>
+      <c r="K85" s="212"/>
+      <c r="L85" s="212"/>
+      <c r="M85" s="212"/>
+      <c r="N85" s="212"/>
+      <c r="O85" s="212"/>
+      <c r="P85" s="212"/>
     </row>
     <row r="86" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E86" s="201"/>
-      <c r="F86" s="201"/>
-      <c r="G86" s="201"/>
-      <c r="H86" s="201"/>
-      <c r="I86" s="201"/>
-      <c r="J86" s="201"/>
-      <c r="K86" s="201"/>
-      <c r="L86" s="201"/>
-      <c r="M86" s="201"/>
-      <c r="N86" s="201"/>
-      <c r="O86" s="201"/>
-      <c r="P86" s="201"/>
+      <c r="E86" s="212"/>
+      <c r="F86" s="212"/>
+      <c r="G86" s="212"/>
+      <c r="H86" s="212"/>
+      <c r="I86" s="212"/>
+      <c r="J86" s="212"/>
+      <c r="K86" s="212"/>
+      <c r="L86" s="212"/>
+      <c r="M86" s="212"/>
+      <c r="N86" s="212"/>
+      <c r="O86" s="212"/>
+      <c r="P86" s="212"/>
     </row>
     <row r="87" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E87" s="201"/>
-      <c r="F87" s="201"/>
-      <c r="G87" s="201"/>
-      <c r="H87" s="201"/>
-      <c r="I87" s="201"/>
-      <c r="J87" s="201"/>
-      <c r="K87" s="201"/>
-      <c r="L87" s="201"/>
-      <c r="M87" s="201"/>
-      <c r="N87" s="201"/>
-      <c r="O87" s="201"/>
-      <c r="P87" s="201"/>
+      <c r="E87" s="212"/>
+      <c r="F87" s="212"/>
+      <c r="G87" s="212"/>
+      <c r="H87" s="212"/>
+      <c r="I87" s="212"/>
+      <c r="J87" s="212"/>
+      <c r="K87" s="212"/>
+      <c r="L87" s="212"/>
+      <c r="M87" s="212"/>
+      <c r="N87" s="212"/>
+      <c r="O87" s="212"/>
+      <c r="P87" s="212"/>
     </row>
     <row r="88" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E88" s="201"/>
-      <c r="F88" s="201"/>
-      <c r="G88" s="201"/>
-      <c r="H88" s="201"/>
-      <c r="I88" s="201"/>
-      <c r="J88" s="201"/>
-      <c r="K88" s="201"/>
-      <c r="L88" s="201"/>
-      <c r="M88" s="201"/>
-      <c r="N88" s="201"/>
-      <c r="O88" s="201"/>
-      <c r="P88" s="201"/>
+      <c r="E88" s="212"/>
+      <c r="F88" s="212"/>
+      <c r="G88" s="212"/>
+      <c r="H88" s="212"/>
+      <c r="I88" s="212"/>
+      <c r="J88" s="212"/>
+      <c r="K88" s="212"/>
+      <c r="L88" s="212"/>
+      <c r="M88" s="212"/>
+      <c r="N88" s="212"/>
+      <c r="O88" s="212"/>
+      <c r="P88" s="212"/>
     </row>
     <row r="89" spans="2:18" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E89" s="201"/>
-      <c r="F89" s="201"/>
-      <c r="G89" s="201"/>
-      <c r="H89" s="201"/>
-      <c r="I89" s="201"/>
-      <c r="J89" s="201"/>
-      <c r="K89" s="201"/>
-      <c r="L89" s="201"/>
-      <c r="M89" s="201"/>
-      <c r="N89" s="201"/>
-      <c r="O89" s="201"/>
-      <c r="P89" s="201"/>
+      <c r="E89" s="212"/>
+      <c r="F89" s="212"/>
+      <c r="G89" s="212"/>
+      <c r="H89" s="212"/>
+      <c r="I89" s="212"/>
+      <c r="J89" s="212"/>
+      <c r="K89" s="212"/>
+      <c r="L89" s="212"/>
+      <c r="M89" s="212"/>
+      <c r="N89" s="212"/>
+      <c r="O89" s="212"/>
+      <c r="P89" s="212"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="R4:R5"/>
-    <mergeCell ref="P2:R2"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="O4:O5"/>
-    <mergeCell ref="G1:P1"/>
-    <mergeCell ref="Q4:Q5"/>
-    <mergeCell ref="M4:M5"/>
-    <mergeCell ref="N4:N5"/>
     <mergeCell ref="E84:P89"/>
     <mergeCell ref="D4:D5"/>
     <mergeCell ref="J4:J5"/>
@@ -8319,9 +8367,17 @@
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="F4:F5"/>
     <mergeCell ref="H4:H5"/>
+    <mergeCell ref="R4:R5"/>
+    <mergeCell ref="P2:R2"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="O4:O5"/>
+    <mergeCell ref="G1:P1"/>
+    <mergeCell ref="Q4:Q5"/>
+    <mergeCell ref="M4:M5"/>
+    <mergeCell ref="N4:N5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -8331,7 +8387,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="5" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C5" s="137"/>
+      <c r="C5" s="136"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8373,16 +8429,16 @@
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
       <c r="F1" s="6"/>
-      <c r="G1" s="225"/>
-      <c r="H1" s="201"/>
-      <c r="I1" s="201"/>
-      <c r="J1" s="201"/>
-      <c r="K1" s="201"/>
-      <c r="L1" s="201"/>
-      <c r="M1" s="201"/>
-      <c r="N1" s="201"/>
-      <c r="O1" s="201"/>
-      <c r="P1" s="201"/>
+      <c r="G1" s="228"/>
+      <c r="H1" s="212"/>
+      <c r="I1" s="212"/>
+      <c r="J1" s="212"/>
+      <c r="K1" s="212"/>
+      <c r="L1" s="212"/>
+      <c r="M1" s="212"/>
+      <c r="N1" s="212"/>
+      <c r="O1" s="212"/>
+      <c r="P1" s="212"/>
       <c r="Q1" s="6"/>
       <c r="R1" s="6"/>
     </row>
@@ -8392,7 +8448,7 @@
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
@@ -8401,17 +8457,17 @@
       <c r="J2" s="6"/>
       <c r="K2" s="6"/>
       <c r="L2" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="M2" s="7"/>
       <c r="N2" s="6"/>
       <c r="O2" s="6"/>
-      <c r="P2" s="222">
+      <c r="P2" s="224">
         <f>16770000+7700000</f>
         <v>24470000</v>
       </c>
-      <c r="Q2" s="201"/>
-      <c r="R2" s="201"/>
+      <c r="Q2" s="212"/>
+      <c r="R2" s="212"/>
       <c r="S2" s="20"/>
     </row>
     <row r="3" spans="1:21" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -8435,77 +8491,77 @@
       <c r="R3" s="59"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A4" s="217" t="s">
+      <c r="A4" s="235" t="s">
         <v>65</v>
       </c>
-      <c r="B4" s="219" t="s">
+      <c r="B4" s="237" t="s">
         <v>66</v>
       </c>
-      <c r="C4" s="133"/>
-      <c r="D4" s="212" t="s">
+      <c r="C4" s="132"/>
+      <c r="D4" s="225" t="s">
         <v>67</v>
       </c>
-      <c r="E4" s="212" t="s">
+      <c r="E4" s="225" t="s">
         <v>68</v>
       </c>
-      <c r="F4" s="214" t="s">
+      <c r="F4" s="234" t="s">
         <v>69</v>
       </c>
-      <c r="G4" s="212" t="s">
+      <c r="G4" s="225" t="s">
         <v>70</v>
       </c>
-      <c r="H4" s="216" t="s">
+      <c r="H4" s="232" t="s">
         <v>71</v>
       </c>
-      <c r="I4" s="212" t="s">
+      <c r="I4" s="225" t="s">
         <v>51</v>
       </c>
-      <c r="J4" s="214" t="s">
+      <c r="J4" s="234" t="s">
         <v>72</v>
       </c>
-      <c r="K4" s="218" t="s">
+      <c r="K4" s="236" t="s">
         <v>73</v>
       </c>
-      <c r="L4" s="216" t="s">
+      <c r="L4" s="232" t="s">
         <v>74</v>
       </c>
-      <c r="M4" s="227" t="s">
+      <c r="M4" s="231" t="s">
         <v>75</v>
       </c>
-      <c r="N4" s="216" t="s">
-        <v>237</v>
-      </c>
-      <c r="O4" s="223"/>
-      <c r="P4" s="221" t="s">
+      <c r="N4" s="232" t="s">
+        <v>236</v>
+      </c>
+      <c r="O4" s="226"/>
+      <c r="P4" s="222" t="s">
         <v>78</v>
       </c>
-      <c r="Q4" s="226" t="s">
+      <c r="Q4" s="229" t="s">
         <v>79</v>
       </c>
-      <c r="R4" s="221" t="s">
+      <c r="R4" s="222" t="s">
         <v>80</v>
       </c>
       <c r="U4" s="42"/>
     </row>
     <row r="5" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="213"/>
-      <c r="B5" s="220"/>
-      <c r="C5" s="134"/>
-      <c r="D5" s="213"/>
-      <c r="E5" s="213"/>
-      <c r="F5" s="215"/>
-      <c r="G5" s="213"/>
-      <c r="H5" s="215"/>
-      <c r="I5" s="213"/>
-      <c r="J5" s="215"/>
-      <c r="K5" s="215"/>
-      <c r="L5" s="215"/>
-      <c r="M5" s="213"/>
-      <c r="N5" s="215"/>
-      <c r="O5" s="224"/>
-      <c r="P5" s="236"/>
-      <c r="Q5" s="220"/>
-      <c r="R5" s="213"/>
+      <c r="A5" s="223"/>
+      <c r="B5" s="230"/>
+      <c r="C5" s="133"/>
+      <c r="D5" s="223"/>
+      <c r="E5" s="223"/>
+      <c r="F5" s="233"/>
+      <c r="G5" s="223"/>
+      <c r="H5" s="233"/>
+      <c r="I5" s="223"/>
+      <c r="J5" s="233"/>
+      <c r="K5" s="233"/>
+      <c r="L5" s="233"/>
+      <c r="M5" s="223"/>
+      <c r="N5" s="233"/>
+      <c r="O5" s="227"/>
+      <c r="P5" s="238"/>
+      <c r="Q5" s="230"/>
+      <c r="R5" s="223"/>
     </row>
     <row r="6" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
@@ -8526,7 +8582,7 @@
         <v>0.5131</v>
       </c>
       <c r="H6" s="72"/>
-      <c r="I6" s="230"/>
+      <c r="I6" s="73"/>
       <c r="J6" s="74"/>
       <c r="K6" s="75"/>
       <c r="L6" s="75"/>
@@ -8579,7 +8635,7 @@
         <v>0.6119</v>
       </c>
       <c r="H7" s="72"/>
-      <c r="I7" s="230"/>
+      <c r="I7" s="73"/>
       <c r="J7" s="74"/>
       <c r="K7" s="75"/>
       <c r="L7" s="75"/>
@@ -8631,7 +8687,7 @@
         <v>0.61150000000000004</v>
       </c>
       <c r="H8" s="72"/>
-      <c r="I8" s="230"/>
+      <c r="I8" s="73"/>
       <c r="J8" s="74"/>
       <c r="K8" s="75"/>
       <c r="L8" s="75"/>
@@ -8682,7 +8738,7 @@
         <v>0.50329999999999997</v>
       </c>
       <c r="H9" s="72"/>
-      <c r="I9" s="230"/>
+      <c r="I9" s="73"/>
       <c r="J9" s="74"/>
       <c r="K9" s="75"/>
       <c r="L9" s="75"/>
@@ -8734,7 +8790,7 @@
         <v>0.50329999999999997</v>
       </c>
       <c r="H10" s="72"/>
-      <c r="I10" s="230"/>
+      <c r="I10" s="73"/>
       <c r="J10" s="74"/>
       <c r="K10" s="75"/>
       <c r="L10" s="75"/>
@@ -8788,7 +8844,7 @@
         <v>0.74990000000000001</v>
       </c>
       <c r="H11" s="72"/>
-      <c r="I11" s="230"/>
+      <c r="I11" s="73"/>
       <c r="J11" s="74"/>
       <c r="K11" s="75"/>
       <c r="L11" s="75"/>
@@ -8841,7 +8897,7 @@
         <v>0.54249999999999998</v>
       </c>
       <c r="H12" s="72"/>
-      <c r="I12" s="230"/>
+      <c r="I12" s="73"/>
       <c r="J12" s="74"/>
       <c r="K12" s="75"/>
       <c r="L12" s="75"/>
@@ -8892,7 +8948,7 @@
         <v>0.45369999999999999</v>
       </c>
       <c r="H13" s="72"/>
-      <c r="I13" s="230"/>
+      <c r="I13" s="73"/>
       <c r="J13" s="74"/>
       <c r="K13" s="75"/>
       <c r="L13" s="75"/>
@@ -8945,7 +9001,7 @@
         <v>0.52439999999999998</v>
       </c>
       <c r="H14" s="72"/>
-      <c r="I14" s="230"/>
+      <c r="I14" s="73"/>
       <c r="J14" s="74"/>
       <c r="K14" s="75"/>
       <c r="L14" s="75"/>
@@ -9001,7 +9057,7 @@
         <v>0.42399999999999999</v>
       </c>
       <c r="H15" s="72"/>
-      <c r="I15" s="230"/>
+      <c r="I15" s="73"/>
       <c r="J15" s="74"/>
       <c r="K15" s="75"/>
       <c r="L15" s="75"/>
@@ -9057,7 +9113,7 @@
         <v>2.3033000000000001</v>
       </c>
       <c r="H16" s="72"/>
-      <c r="I16" s="230"/>
+      <c r="I16" s="73"/>
       <c r="J16" s="74"/>
       <c r="K16" s="75"/>
       <c r="L16" s="75"/>
@@ -9112,7 +9168,7 @@
         <v>2.7492999999999999</v>
       </c>
       <c r="H17" s="72"/>
-      <c r="I17" s="230"/>
+      <c r="I17" s="73"/>
       <c r="J17" s="74"/>
       <c r="K17" s="75"/>
       <c r="L17" s="75"/>
@@ -9167,7 +9223,7 @@
         <v>2.3033000000000001</v>
       </c>
       <c r="H18" s="72"/>
-      <c r="I18" s="230"/>
+      <c r="I18" s="73"/>
       <c r="J18" s="74"/>
       <c r="K18" s="75"/>
       <c r="L18" s="75"/>
@@ -9222,7 +9278,7 @@
         <v>2.6368</v>
       </c>
       <c r="H19" s="72"/>
-      <c r="I19" s="230"/>
+      <c r="I19" s="73"/>
       <c r="J19" s="74"/>
       <c r="K19" s="75"/>
       <c r="L19" s="75"/>
@@ -9278,7 +9334,7 @@
         <v>2.3536999999999999</v>
       </c>
       <c r="H20" s="72"/>
-      <c r="I20" s="230"/>
+      <c r="I20" s="73"/>
       <c r="J20" s="74"/>
       <c r="K20" s="75"/>
       <c r="L20" s="75"/>
@@ -9333,7 +9389,7 @@
         <v>2.6476999999999999</v>
       </c>
       <c r="H21" s="72"/>
-      <c r="I21" s="230"/>
+      <c r="I21" s="73"/>
       <c r="J21" s="74"/>
       <c r="K21" s="75"/>
       <c r="L21" s="75"/>
@@ -9389,7 +9445,7 @@
         <v>2.3235000000000001</v>
       </c>
       <c r="H22" s="73"/>
-      <c r="I22" s="230"/>
+      <c r="I22" s="73"/>
       <c r="J22" s="74"/>
       <c r="K22" s="75"/>
       <c r="L22" s="75"/>
@@ -9437,14 +9493,14 @@
       <c r="E23" s="64" t="s">
         <v>119</v>
       </c>
-      <c r="F23" s="143" t="s">
+      <c r="F23" s="142" t="s">
         <v>120</v>
       </c>
       <c r="G23" s="71">
         <v>2.6880000000000002</v>
       </c>
       <c r="H23" s="72"/>
-      <c r="I23" s="230"/>
+      <c r="I23" s="73"/>
       <c r="J23" s="74"/>
       <c r="K23" s="75"/>
       <c r="L23" s="75"/>
@@ -9474,7 +9530,7 @@
         <f t="shared" si="5"/>
         <v>0.18000000000000002</v>
       </c>
-      <c r="U23" s="153" t="s">
+      <c r="U23" s="152" t="s">
         <v>120</v>
       </c>
     </row>
@@ -9500,7 +9556,7 @@
         <v>2.36</v>
       </c>
       <c r="H24" s="72"/>
-      <c r="I24" s="230"/>
+      <c r="I24" s="73"/>
       <c r="J24" s="74"/>
       <c r="K24" s="75"/>
       <c r="L24" s="75"/>
@@ -9553,7 +9609,7 @@
         <v>2.7183000000000002</v>
       </c>
       <c r="H25" s="72"/>
-      <c r="I25" s="230"/>
+      <c r="I25" s="73"/>
       <c r="J25" s="74"/>
       <c r="K25" s="110"/>
       <c r="L25" s="75"/>
@@ -9606,7 +9662,7 @@
         <v>2.3033000000000001</v>
       </c>
       <c r="H26" s="72"/>
-      <c r="I26" s="230"/>
+      <c r="I26" s="73"/>
       <c r="J26" s="74"/>
       <c r="K26" s="75"/>
       <c r="L26" s="75"/>
@@ -9661,7 +9717,7 @@
         <v>2.6360000000000001</v>
       </c>
       <c r="H27" s="72"/>
-      <c r="I27" s="230"/>
+      <c r="I27" s="73"/>
       <c r="J27" s="74"/>
       <c r="K27" s="75"/>
       <c r="L27" s="75"/>
@@ -9672,7 +9728,7 @@
         <f t="shared" si="0"/>
         <v>645029.20000000007</v>
       </c>
-      <c r="O27" s="184">
+      <c r="O27" s="183">
         <v>0</v>
       </c>
       <c r="P27" s="79">
@@ -9720,7 +9776,7 @@
         <v>2.3033000000000001</v>
       </c>
       <c r="H28" s="72"/>
-      <c r="I28" s="230"/>
+      <c r="I28" s="73"/>
       <c r="J28" s="74"/>
       <c r="K28" s="75"/>
       <c r="L28" s="75"/>
@@ -9773,7 +9829,7 @@
         <v>2.6158999999999999</v>
       </c>
       <c r="H29" s="72"/>
-      <c r="I29" s="230"/>
+      <c r="I29" s="73"/>
       <c r="J29" s="74"/>
       <c r="K29" s="75"/>
       <c r="L29" s="75"/>
@@ -9826,7 +9882,7 @@
         <v>2.3536999999999999</v>
       </c>
       <c r="H30" s="72"/>
-      <c r="I30" s="230"/>
+      <c r="I30" s="73"/>
       <c r="J30" s="74"/>
       <c r="K30" s="75"/>
       <c r="L30" s="75"/>
@@ -9881,7 +9937,7 @@
         <v>2.6469</v>
       </c>
       <c r="H31" s="72"/>
-      <c r="I31" s="230"/>
+      <c r="I31" s="73"/>
       <c r="J31" s="74"/>
       <c r="K31" s="75"/>
       <c r="L31" s="75"/>
@@ -9934,7 +9990,7 @@
         <v>2.3536999999999999</v>
       </c>
       <c r="H32" s="72"/>
-      <c r="I32" s="230"/>
+      <c r="I32" s="73"/>
       <c r="J32" s="74"/>
       <c r="K32" s="75"/>
       <c r="L32" s="75"/>
@@ -9987,7 +10043,7 @@
         <v>2.6663000000000001</v>
       </c>
       <c r="H33" s="72"/>
-      <c r="I33" s="230"/>
+      <c r="I33" s="73"/>
       <c r="J33" s="74"/>
       <c r="K33" s="75"/>
       <c r="L33" s="75"/>
@@ -9998,7 +10054,7 @@
         <f t="shared" si="0"/>
         <v>652443.6100000001</v>
       </c>
-      <c r="O33" s="128">
+      <c r="O33" s="127">
         <v>0</v>
       </c>
       <c r="P33" s="79">
@@ -10042,7 +10098,7 @@
         <v>2.4476</v>
       </c>
       <c r="H34" s="72"/>
-      <c r="I34" s="230"/>
+      <c r="I34" s="73"/>
       <c r="J34" s="74"/>
       <c r="K34" s="75"/>
       <c r="L34" s="75"/>
@@ -10053,7 +10109,7 @@
         <f t="shared" si="0"/>
         <v>598927.72</v>
       </c>
-      <c r="O34" s="188">
+      <c r="O34" s="187">
         <v>18500</v>
       </c>
       <c r="P34" s="79">
@@ -10095,7 +10151,7 @@
         <v>2.7183000000000002</v>
       </c>
       <c r="H35" s="72"/>
-      <c r="I35" s="230"/>
+      <c r="I35" s="73"/>
       <c r="J35" s="74"/>
       <c r="K35" s="75"/>
       <c r="L35" s="75"/>
@@ -10150,14 +10206,14 @@
         <v>2.3026</v>
       </c>
       <c r="H36" s="73"/>
-      <c r="I36" s="230"/>
+      <c r="I36" s="73"/>
       <c r="J36" s="82"/>
       <c r="K36" s="75"/>
       <c r="L36" s="75"/>
       <c r="M36" s="76">
         <v>0</v>
       </c>
-      <c r="N36" s="141">
+      <c r="N36" s="140">
         <f t="shared" si="0"/>
         <v>563446.22000000009</v>
       </c>
@@ -10203,7 +10259,7 @@
         <v>2.6562000000000001</v>
       </c>
       <c r="H37" s="72"/>
-      <c r="I37" s="230"/>
+      <c r="I37" s="73"/>
       <c r="J37" s="74"/>
       <c r="K37" s="75"/>
       <c r="L37" s="75"/>
@@ -10256,7 +10312,7 @@
         <v>2.3342999999999998</v>
       </c>
       <c r="H38" s="72"/>
-      <c r="I38" s="230"/>
+      <c r="I38" s="73"/>
       <c r="J38" s="74"/>
       <c r="K38" s="75"/>
       <c r="L38" s="75"/>
@@ -10309,7 +10365,7 @@
         <v>2.6259000000000001</v>
       </c>
       <c r="H39" s="72"/>
-      <c r="I39" s="230"/>
+      <c r="I39" s="73"/>
       <c r="J39" s="74"/>
       <c r="K39" s="75"/>
       <c r="L39" s="75"/>
@@ -10364,7 +10420,7 @@
         <v>1.0069999999999999</v>
       </c>
       <c r="H40" s="72"/>
-      <c r="I40" s="230"/>
+      <c r="I40" s="73"/>
       <c r="J40" s="74"/>
       <c r="K40" s="75"/>
       <c r="L40" s="75"/>
@@ -10419,7 +10475,7 @@
         <v>0.78120000000000001</v>
       </c>
       <c r="H41" s="73"/>
-      <c r="I41" s="230"/>
+      <c r="I41" s="73"/>
       <c r="J41" s="74"/>
       <c r="K41" s="75"/>
       <c r="L41" s="75"/>
@@ -10475,7 +10531,7 @@
         <v>1.2153</v>
       </c>
       <c r="H42" s="72"/>
-      <c r="I42" s="230"/>
+      <c r="I42" s="73"/>
       <c r="J42" s="74"/>
       <c r="K42" s="75"/>
       <c r="L42" s="75"/>
@@ -10530,7 +10586,7 @@
         <v>0.95489999999999997</v>
       </c>
       <c r="H43" s="72"/>
-      <c r="I43" s="230"/>
+      <c r="I43" s="73"/>
       <c r="J43" s="74"/>
       <c r="K43" s="75"/>
       <c r="L43" s="75"/>
@@ -10580,7 +10636,7 @@
         <v>0.75519999999999998</v>
       </c>
       <c r="H44" s="72"/>
-      <c r="I44" s="230"/>
+      <c r="I44" s="73"/>
       <c r="J44" s="74"/>
       <c r="K44" s="75"/>
       <c r="L44" s="75"/>
@@ -10632,7 +10688,7 @@
         <v>1.1545000000000001</v>
       </c>
       <c r="H45" s="72"/>
-      <c r="I45" s="230"/>
+      <c r="I45" s="73"/>
       <c r="J45" s="74"/>
       <c r="K45" s="75"/>
       <c r="L45" s="75"/>
@@ -10684,7 +10740,7 @@
         <v>0.95489999999999997</v>
       </c>
       <c r="H46" s="72"/>
-      <c r="I46" s="230"/>
+      <c r="I46" s="73"/>
       <c r="J46" s="74"/>
       <c r="K46" s="75"/>
       <c r="L46" s="75"/>
@@ -10734,7 +10790,7 @@
         <v>0.75519999999999998</v>
       </c>
       <c r="H47" s="72"/>
-      <c r="I47" s="230"/>
+      <c r="I47" s="73"/>
       <c r="J47" s="74"/>
       <c r="K47" s="75"/>
       <c r="L47" s="75"/>
@@ -10784,7 +10840,7 @@
         <v>1.1545000000000001</v>
       </c>
       <c r="H48" s="72"/>
-      <c r="I48" s="230"/>
+      <c r="I48" s="73"/>
       <c r="J48" s="74"/>
       <c r="K48" s="75"/>
       <c r="L48" s="75"/>
@@ -10836,7 +10892,7 @@
         <v>0.95489999999999997</v>
       </c>
       <c r="H49" s="72"/>
-      <c r="I49" s="230"/>
+      <c r="I49" s="73"/>
       <c r="J49" s="74"/>
       <c r="K49" s="75"/>
       <c r="L49" s="75"/>
@@ -10886,7 +10942,7 @@
         <v>0.75519999999999998</v>
       </c>
       <c r="H50" s="72"/>
-      <c r="I50" s="230"/>
+      <c r="I50" s="73"/>
       <c r="J50" s="74"/>
       <c r="K50" s="75"/>
       <c r="L50" s="75"/>
@@ -10941,7 +10997,7 @@
         <v>1.1545000000000001</v>
       </c>
       <c r="H51" s="72"/>
-      <c r="I51" s="230"/>
+      <c r="I51" s="73"/>
       <c r="J51" s="74"/>
       <c r="K51" s="75"/>
       <c r="L51" s="75"/>
@@ -10993,7 +11049,7 @@
         <v>0.95489999999999997</v>
       </c>
       <c r="H52" s="72"/>
-      <c r="I52" s="230"/>
+      <c r="I52" s="73"/>
       <c r="J52" s="74"/>
       <c r="K52" s="75"/>
       <c r="L52" s="75"/>
@@ -11045,7 +11101,7 @@
         <v>0.75519999999999998</v>
       </c>
       <c r="H53" s="72"/>
-      <c r="I53" s="230"/>
+      <c r="I53" s="73"/>
       <c r="J53" s="74"/>
       <c r="K53" s="75"/>
       <c r="L53" s="75"/>
@@ -11097,7 +11153,7 @@
         <v>1.1545000000000001</v>
       </c>
       <c r="H54" s="72"/>
-      <c r="I54" s="230"/>
+      <c r="I54" s="73"/>
       <c r="J54" s="74"/>
       <c r="K54" s="75"/>
       <c r="L54" s="75"/>
@@ -11147,7 +11203,7 @@
         <v>0.95489999999999997</v>
       </c>
       <c r="H55" s="72"/>
-      <c r="I55" s="230"/>
+      <c r="I55" s="73"/>
       <c r="J55" s="74"/>
       <c r="K55" s="75"/>
       <c r="L55" s="75"/>
@@ -11197,7 +11253,7 @@
         <v>0.75519999999999998</v>
       </c>
       <c r="H56" s="72"/>
-      <c r="I56" s="230"/>
+      <c r="I56" s="73"/>
       <c r="J56" s="74"/>
       <c r="K56" s="75"/>
       <c r="L56" s="75"/>
@@ -11250,7 +11306,7 @@
         <v>1.1545000000000001</v>
       </c>
       <c r="H57" s="72"/>
-      <c r="I57" s="230"/>
+      <c r="I57" s="73"/>
       <c r="J57" s="74"/>
       <c r="K57" s="75"/>
       <c r="L57" s="75"/>
@@ -11300,7 +11356,7 @@
         <v>0.95489999999999997</v>
       </c>
       <c r="H58" s="72"/>
-      <c r="I58" s="230"/>
+      <c r="I58" s="73"/>
       <c r="J58" s="74"/>
       <c r="K58" s="75"/>
       <c r="L58" s="75"/>
@@ -11350,7 +11406,7 @@
         <v>0.75519999999999998</v>
       </c>
       <c r="H59" s="72"/>
-      <c r="I59" s="230"/>
+      <c r="I59" s="73"/>
       <c r="J59" s="74"/>
       <c r="K59" s="75"/>
       <c r="L59" s="75"/>
@@ -11402,7 +11458,7 @@
         <v>1.1545000000000001</v>
       </c>
       <c r="H60" s="72"/>
-      <c r="I60" s="230"/>
+      <c r="I60" s="73"/>
       <c r="J60" s="74"/>
       <c r="K60" s="75"/>
       <c r="L60" s="75"/>
@@ -11454,7 +11510,7 @@
         <v>0.95489999999999997</v>
       </c>
       <c r="H61" s="72"/>
-      <c r="I61" s="230"/>
+      <c r="I61" s="73"/>
       <c r="J61" s="74"/>
       <c r="K61" s="75"/>
       <c r="L61" s="75"/>
@@ -11504,7 +11560,7 @@
         <v>0.75519999999999998</v>
       </c>
       <c r="H62" s="72"/>
-      <c r="I62" s="230"/>
+      <c r="I62" s="73"/>
       <c r="J62" s="74"/>
       <c r="K62" s="75"/>
       <c r="L62" s="75"/>
@@ -11554,7 +11610,7 @@
         <v>1.1545000000000001</v>
       </c>
       <c r="H63" s="72"/>
-      <c r="I63" s="230"/>
+      <c r="I63" s="73"/>
       <c r="J63" s="74"/>
       <c r="K63" s="75"/>
       <c r="L63" s="75"/>
@@ -11606,7 +11662,7 @@
         <v>0.95489999999999997</v>
       </c>
       <c r="H64" s="72"/>
-      <c r="I64" s="230"/>
+      <c r="I64" s="73"/>
       <c r="J64" s="74"/>
       <c r="K64" s="75"/>
       <c r="L64" s="75"/>
@@ -11656,7 +11712,7 @@
         <v>0.75519999999999998</v>
       </c>
       <c r="H65" s="72"/>
-      <c r="I65" s="230"/>
+      <c r="I65" s="73"/>
       <c r="J65" s="74"/>
       <c r="K65" s="75"/>
       <c r="L65" s="75"/>
@@ -11709,7 +11765,7 @@
         <v>1.1545000000000001</v>
       </c>
       <c r="H66" s="72"/>
-      <c r="I66" s="230"/>
+      <c r="I66" s="73"/>
       <c r="J66" s="74"/>
       <c r="K66" s="75"/>
       <c r="L66" s="75"/>
@@ -11764,7 +11820,7 @@
         <v>0.95489999999999997</v>
       </c>
       <c r="H67" s="72"/>
-      <c r="I67" s="230"/>
+      <c r="I67" s="73"/>
       <c r="J67" s="74"/>
       <c r="K67" s="75"/>
       <c r="L67" s="75"/>
@@ -11819,7 +11875,7 @@
         <v>0.75519999999999998</v>
       </c>
       <c r="H68" s="72"/>
-      <c r="I68" s="230"/>
+      <c r="I68" s="73"/>
       <c r="J68" s="74"/>
       <c r="K68" s="75"/>
       <c r="L68" s="75"/>
@@ -11869,7 +11925,7 @@
         <v>1.1545000000000001</v>
       </c>
       <c r="H69" s="72"/>
-      <c r="I69" s="230"/>
+      <c r="I69" s="73"/>
       <c r="J69" s="74"/>
       <c r="K69" s="75"/>
       <c r="L69" s="75"/>
@@ -11919,7 +11975,7 @@
         <v>0.95489999999999997</v>
       </c>
       <c r="H70" s="72"/>
-      <c r="I70" s="230"/>
+      <c r="I70" s="73"/>
       <c r="J70" s="74"/>
       <c r="K70" s="75"/>
       <c r="L70" s="75"/>
@@ -11971,7 +12027,7 @@
         <v>0.75519999999999998</v>
       </c>
       <c r="H71" s="72"/>
-      <c r="I71" s="230"/>
+      <c r="I71" s="73"/>
       <c r="J71" s="74"/>
       <c r="K71" s="75"/>
       <c r="L71" s="75"/>
@@ -12021,7 +12077,7 @@
         <v>1.1545000000000001</v>
       </c>
       <c r="H72" s="72"/>
-      <c r="I72" s="230"/>
+      <c r="I72" s="73"/>
       <c r="J72" s="74"/>
       <c r="K72" s="75"/>
       <c r="L72" s="75"/>
@@ -12071,7 +12127,7 @@
         <v>0.95489999999999997</v>
       </c>
       <c r="H73" s="90"/>
-      <c r="I73" s="230"/>
+      <c r="I73" s="73"/>
       <c r="J73" s="92"/>
       <c r="K73" s="93"/>
       <c r="L73" s="75"/>
@@ -12121,7 +12177,7 @@
         <v>0.75519999999999998</v>
       </c>
       <c r="H74" s="90"/>
-      <c r="I74" s="230"/>
+      <c r="I74" s="73"/>
       <c r="J74" s="92"/>
       <c r="K74" s="93"/>
       <c r="L74" s="75"/>
@@ -12171,7 +12227,7 @@
         <v>1.1549</v>
       </c>
       <c r="H75" s="90"/>
-      <c r="I75" s="230"/>
+      <c r="I75" s="73"/>
       <c r="J75" s="92"/>
       <c r="K75" s="93"/>
       <c r="L75" s="75"/>
@@ -12264,7 +12320,7 @@
     </row>
     <row r="79" spans="2:21" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B79" s="97"/>
-      <c r="C79" s="135"/>
+      <c r="C79" s="134"/>
       <c r="D79" s="87"/>
       <c r="E79" s="64"/>
       <c r="F79" s="65"/>
@@ -12304,7 +12360,7 @@
     </row>
     <row r="81" spans="2:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B81" s="102"/>
-      <c r="C81" s="136"/>
+      <c r="C81" s="135"/>
       <c r="D81" s="103"/>
       <c r="E81" s="104"/>
       <c r="F81" s="104"/>
@@ -12357,94 +12413,104 @@
     </row>
     <row r="83" spans="2:18" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="84" spans="2:18" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E84" s="200" t="str">
+      <c r="E84" s="217" t="str">
         <f>RESUMEN!A14</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. CASO CONTRARIO SE INFORMARA VIA CARTA DOCUMENTO A LA UNIDAD FUNCIONAL QUE CREEMOS QUE CORRESPONDE, CUYO COSTO SERA IMPUTADO A LA UNIDAD FUNCIONAL SOSPECHADA.</v>
       </c>
-      <c r="F84" s="201"/>
-      <c r="G84" s="201"/>
-      <c r="H84" s="201"/>
-      <c r="I84" s="201"/>
-      <c r="J84" s="201"/>
-      <c r="K84" s="201"/>
-      <c r="L84" s="201"/>
-      <c r="M84" s="201"/>
-      <c r="N84" s="201"/>
-      <c r="O84" s="201"/>
-      <c r="P84" s="201"/>
+      <c r="F84" s="212"/>
+      <c r="G84" s="212"/>
+      <c r="H84" s="212"/>
+      <c r="I84" s="212"/>
+      <c r="J84" s="212"/>
+      <c r="K84" s="212"/>
+      <c r="L84" s="212"/>
+      <c r="M84" s="212"/>
+      <c r="N84" s="212"/>
+      <c r="O84" s="212"/>
+      <c r="P84" s="212"/>
     </row>
     <row r="85" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E85" s="201"/>
-      <c r="F85" s="201"/>
-      <c r="G85" s="201"/>
-      <c r="H85" s="201"/>
-      <c r="I85" s="201"/>
-      <c r="J85" s="201"/>
-      <c r="K85" s="201"/>
-      <c r="L85" s="201"/>
-      <c r="M85" s="201"/>
-      <c r="N85" s="201"/>
-      <c r="O85" s="201"/>
-      <c r="P85" s="201"/>
+      <c r="E85" s="212"/>
+      <c r="F85" s="212"/>
+      <c r="G85" s="212"/>
+      <c r="H85" s="212"/>
+      <c r="I85" s="212"/>
+      <c r="J85" s="212"/>
+      <c r="K85" s="212"/>
+      <c r="L85" s="212"/>
+      <c r="M85" s="212"/>
+      <c r="N85" s="212"/>
+      <c r="O85" s="212"/>
+      <c r="P85" s="212"/>
     </row>
     <row r="86" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E86" s="201"/>
-      <c r="F86" s="201"/>
-      <c r="G86" s="201"/>
-      <c r="H86" s="201"/>
-      <c r="I86" s="201"/>
-      <c r="J86" s="201"/>
-      <c r="K86" s="201"/>
-      <c r="L86" s="201"/>
-      <c r="M86" s="201"/>
-      <c r="N86" s="201"/>
-      <c r="O86" s="201"/>
-      <c r="P86" s="201"/>
+      <c r="E86" s="212"/>
+      <c r="F86" s="212"/>
+      <c r="G86" s="212"/>
+      <c r="H86" s="212"/>
+      <c r="I86" s="212"/>
+      <c r="J86" s="212"/>
+      <c r="K86" s="212"/>
+      <c r="L86" s="212"/>
+      <c r="M86" s="212"/>
+      <c r="N86" s="212"/>
+      <c r="O86" s="212"/>
+      <c r="P86" s="212"/>
     </row>
     <row r="87" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E87" s="201"/>
-      <c r="F87" s="201"/>
-      <c r="G87" s="201"/>
-      <c r="H87" s="201"/>
-      <c r="I87" s="201"/>
-      <c r="J87" s="201"/>
-      <c r="K87" s="201"/>
-      <c r="L87" s="201"/>
-      <c r="M87" s="201"/>
-      <c r="N87" s="201"/>
-      <c r="O87" s="201"/>
-      <c r="P87" s="201"/>
+      <c r="E87" s="212"/>
+      <c r="F87" s="212"/>
+      <c r="G87" s="212"/>
+      <c r="H87" s="212"/>
+      <c r="I87" s="212"/>
+      <c r="J87" s="212"/>
+      <c r="K87" s="212"/>
+      <c r="L87" s="212"/>
+      <c r="M87" s="212"/>
+      <c r="N87" s="212"/>
+      <c r="O87" s="212"/>
+      <c r="P87" s="212"/>
     </row>
     <row r="88" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E88" s="201"/>
-      <c r="F88" s="201"/>
-      <c r="G88" s="201"/>
-      <c r="H88" s="201"/>
-      <c r="I88" s="201"/>
-      <c r="J88" s="201"/>
-      <c r="K88" s="201"/>
-      <c r="L88" s="201"/>
-      <c r="M88" s="201"/>
-      <c r="N88" s="201"/>
-      <c r="O88" s="201"/>
-      <c r="P88" s="201"/>
+      <c r="E88" s="212"/>
+      <c r="F88" s="212"/>
+      <c r="G88" s="212"/>
+      <c r="H88" s="212"/>
+      <c r="I88" s="212"/>
+      <c r="J88" s="212"/>
+      <c r="K88" s="212"/>
+      <c r="L88" s="212"/>
+      <c r="M88" s="212"/>
+      <c r="N88" s="212"/>
+      <c r="O88" s="212"/>
+      <c r="P88" s="212"/>
     </row>
     <row r="89" spans="2:18" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E89" s="201"/>
-      <c r="F89" s="201"/>
-      <c r="G89" s="201"/>
-      <c r="H89" s="201"/>
-      <c r="I89" s="201"/>
-      <c r="J89" s="201"/>
-      <c r="K89" s="201"/>
-      <c r="L89" s="201"/>
-      <c r="M89" s="201"/>
-      <c r="N89" s="201"/>
-      <c r="O89" s="201"/>
-      <c r="P89" s="201"/>
+      <c r="E89" s="212"/>
+      <c r="F89" s="212"/>
+      <c r="G89" s="212"/>
+      <c r="H89" s="212"/>
+      <c r="I89" s="212"/>
+      <c r="J89" s="212"/>
+      <c r="K89" s="212"/>
+      <c r="L89" s="212"/>
+      <c r="M89" s="212"/>
+      <c r="N89" s="212"/>
+      <c r="O89" s="212"/>
+      <c r="P89" s="212"/>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="G1:P1"/>
+    <mergeCell ref="P2:R2"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I4:I5"/>
     <mergeCell ref="Q4:Q5"/>
     <mergeCell ref="R4:R5"/>
     <mergeCell ref="E84:P89"/>
@@ -12455,16 +12521,6 @@
     <mergeCell ref="M4:M5"/>
     <mergeCell ref="N4:N5"/>
     <mergeCell ref="O4:O5"/>
-    <mergeCell ref="G1:P1"/>
-    <mergeCell ref="P2:R2"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="I4:I5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>

--- a/GORRITI/Julio/GORRITI-Julio.xlsx
+++ b/GORRITI/Julio/GORRITI-Julio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\GORRITI\Julio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1A6B5D0-D8BB-426D-851E-29D457939FD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17E04CC3-3B5C-48D2-A6B3-E326B5FC6A7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1800,27 +1800,18 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1833,15 +1824,41 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="168" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1853,25 +1870,8 @@
     <xf numFmtId="0" fontId="16" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2330,49 +2330,49 @@
       <c r="E7" s="19"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="211" t="s">
+      <c r="B9" s="219" t="s">
         <v>206</v>
       </c>
-      <c r="C9" s="212"/>
+      <c r="C9" s="210"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="212"/>
-      <c r="C10" s="212"/>
+      <c r="B10" s="210"/>
+      <c r="C10" s="210"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B11" s="212"/>
-      <c r="C11" s="212"/>
+      <c r="B11" s="210"/>
+      <c r="C11" s="210"/>
     </row>
     <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="215" t="s">
+      <c r="A14" s="221" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="212"/>
-      <c r="C14" s="212"/>
-      <c r="D14" s="212"/>
-      <c r="E14" s="212"/>
+      <c r="B14" s="210"/>
+      <c r="C14" s="210"/>
+      <c r="D14" s="210"/>
+      <c r="E14" s="210"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="212"/>
-      <c r="B15" s="212"/>
-      <c r="C15" s="212"/>
-      <c r="D15" s="212"/>
-      <c r="E15" s="212"/>
+      <c r="A15" s="210"/>
+      <c r="B15" s="210"/>
+      <c r="C15" s="210"/>
+      <c r="D15" s="210"/>
+      <c r="E15" s="210"/>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="212"/>
-      <c r="B16" s="212"/>
-      <c r="C16" s="212"/>
-      <c r="D16" s="212"/>
-      <c r="E16" s="212"/>
+      <c r="A16" s="210"/>
+      <c r="B16" s="210"/>
+      <c r="C16" s="210"/>
+      <c r="D16" s="210"/>
+      <c r="E16" s="210"/>
     </row>
     <row r="17" spans="1:8" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="212"/>
-      <c r="B17" s="212"/>
-      <c r="C17" s="212"/>
-      <c r="D17" s="212"/>
-      <c r="E17" s="212"/>
+      <c r="A17" s="210"/>
+      <c r="B17" s="210"/>
+      <c r="C17" s="210"/>
+      <c r="D17" s="210"/>
+      <c r="E17" s="210"/>
     </row>
     <row r="18" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
@@ -2544,10 +2544,10 @@
       <c r="E34" s="162"/>
     </row>
     <row r="35" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="214" t="s">
+      <c r="A35" s="220" t="s">
         <v>202</v>
       </c>
-      <c r="B35" s="210"/>
+      <c r="B35" s="212"/>
       <c r="C35" s="182"/>
       <c r="D35" s="156">
         <v>60000</v>
@@ -2557,10 +2557,10 @@
       </c>
     </row>
     <row r="36" spans="1:8" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="213" t="s">
+      <c r="A36" s="211" t="s">
         <v>209</v>
       </c>
-      <c r="B36" s="216"/>
+      <c r="B36" s="214"/>
       <c r="C36" s="51"/>
       <c r="D36" s="156">
         <v>249000</v>
@@ -2592,10 +2592,10 @@
       <c r="E38" s="166"/>
     </row>
     <row r="39" spans="1:8" s="36" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="209" t="s">
+      <c r="A39" s="213" t="s">
         <v>21</v>
       </c>
-      <c r="B39" s="210"/>
+      <c r="B39" s="212"/>
       <c r="C39" s="53"/>
       <c r="D39" s="188">
         <v>144149</v>
@@ -2605,8 +2605,8 @@
       </c>
     </row>
     <row r="40" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="209"/>
-      <c r="B40" s="210"/>
+      <c r="A40" s="213"/>
+      <c r="B40" s="212"/>
       <c r="C40" s="53"/>
       <c r="D40" s="168"/>
       <c r="E40" s="167"/>
@@ -2810,10 +2810,10 @@
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="209" t="s">
+      <c r="A56" s="213" t="s">
         <v>35</v>
       </c>
-      <c r="B56" s="210"/>
+      <c r="B56" s="212"/>
       <c r="C56" s="5"/>
       <c r="D56" s="168">
         <v>2168902.4500000002</v>
@@ -2823,8 +2823,8 @@
       </c>
     </row>
     <row r="57" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="209"/>
-      <c r="B57" s="210"/>
+      <c r="A57" s="213"/>
+      <c r="B57" s="212"/>
       <c r="C57" s="154"/>
       <c r="D57" s="206"/>
       <c r="E57" s="207"/>
@@ -2851,10 +2851,10 @@
       <c r="E59" s="176"/>
     </row>
     <row r="60" spans="1:5" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="213" t="s">
+      <c r="A60" s="211" t="s">
         <v>228</v>
       </c>
-      <c r="B60" s="210"/>
+      <c r="B60" s="212"/>
       <c r="C60" s="54"/>
       <c r="D60" s="168">
         <v>48400</v>
@@ -2890,10 +2890,10 @@
       </c>
     </row>
     <row r="63" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="213" t="s">
+      <c r="A63" s="211" t="s">
         <v>225</v>
       </c>
-      <c r="B63" s="216"/>
+      <c r="B63" s="214"/>
       <c r="C63" s="5"/>
       <c r="D63" s="168">
         <v>770000</v>
@@ -2903,10 +2903,10 @@
       </c>
     </row>
     <row r="64" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="213" t="s">
+      <c r="A64" s="211" t="s">
         <v>232</v>
       </c>
-      <c r="B64" s="216"/>
+      <c r="B64" s="214"/>
       <c r="C64" s="5"/>
       <c r="D64" s="168">
         <v>40020.120000000003</v>
@@ -2916,10 +2916,10 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="213" t="s">
+      <c r="A65" s="211" t="s">
         <v>227</v>
       </c>
-      <c r="B65" s="216"/>
+      <c r="B65" s="214"/>
       <c r="C65" s="199"/>
       <c r="D65" s="116">
         <v>300000</v>
@@ -2929,10 +2929,10 @@
       </c>
     </row>
     <row r="66" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="213" t="s">
+      <c r="A66" s="211" t="s">
         <v>233</v>
       </c>
-      <c r="B66" s="216"/>
+      <c r="B66" s="214"/>
       <c r="C66" s="51"/>
       <c r="D66" s="116">
         <v>125475</v>
@@ -2942,10 +2942,10 @@
       </c>
     </row>
     <row r="67" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="213" t="s">
+      <c r="A67" s="211" t="s">
         <v>214</v>
       </c>
-      <c r="B67" s="210"/>
+      <c r="B67" s="212"/>
       <c r="C67" s="5"/>
       <c r="D67" s="116">
         <v>150000</v>
@@ -2955,10 +2955,10 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="213" t="s">
+      <c r="A68" s="211" t="s">
         <v>216</v>
       </c>
-      <c r="B68" s="216"/>
+      <c r="B68" s="214"/>
       <c r="C68" s="5"/>
       <c r="D68" s="116">
         <f>65050+57650</f>
@@ -2980,10 +2980,10 @@
       <c r="E69" s="180"/>
     </row>
     <row r="70" spans="1:10" ht="22.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="209" t="s">
+      <c r="A70" s="213" t="s">
         <v>220</v>
       </c>
-      <c r="B70" s="210"/>
+      <c r="B70" s="212"/>
       <c r="C70" s="5"/>
       <c r="D70" s="116">
         <v>8000</v>
@@ -2991,8 +2991,8 @@
       <c r="E70" s="180" t="s">
         <v>218</v>
       </c>
-      <c r="I70" s="209"/>
-      <c r="J70" s="210"/>
+      <c r="I70" s="213"/>
+      <c r="J70" s="212"/>
     </row>
     <row r="71" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="27" t="s">
@@ -3059,12 +3059,12 @@
       <c r="E76" s="120"/>
     </row>
     <row r="77" spans="1:10" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="219" t="s">
+      <c r="A77" s="216" t="s">
         <v>238</v>
       </c>
-      <c r="B77" s="220"/>
-      <c r="C77" s="220"/>
-      <c r="D77" s="221"/>
+      <c r="B77" s="217"/>
+      <c r="C77" s="217"/>
+      <c r="D77" s="218"/>
       <c r="E77" s="121">
         <v>1500000</v>
       </c>
@@ -3108,22 +3108,22 @@
       <c r="E82" s="126"/>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83" s="209"/>
-      <c r="B83" s="210"/>
+      <c r="A83" s="213"/>
+      <c r="B83" s="212"/>
       <c r="C83" s="5"/>
       <c r="D83" s="141"/>
       <c r="E83" s="114"/>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A84" s="209"/>
-      <c r="B84" s="210"/>
+      <c r="A84" s="213"/>
+      <c r="B84" s="212"/>
       <c r="C84" s="5"/>
       <c r="D84" s="116"/>
       <c r="E84" s="114"/>
     </row>
     <row r="85" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="213"/>
-      <c r="B85" s="210"/>
+      <c r="A85" s="211"/>
+      <c r="B85" s="212"/>
       <c r="C85" s="5"/>
       <c r="D85" s="116"/>
       <c r="E85" s="114"/>
@@ -3208,25 +3208,25 @@
     </row>
     <row r="98" spans="1:5" ht="34.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="99" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="217"/>
-      <c r="B99" s="212"/>
-      <c r="C99" s="212"/>
-      <c r="D99" s="212"/>
-      <c r="E99" s="212"/>
+      <c r="A99" s="209"/>
+      <c r="B99" s="210"/>
+      <c r="C99" s="210"/>
+      <c r="D99" s="210"/>
+      <c r="E99" s="210"/>
     </row>
     <row r="100" spans="1:5" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="212"/>
-      <c r="B100" s="212"/>
-      <c r="C100" s="212"/>
-      <c r="D100" s="212"/>
-      <c r="E100" s="212"/>
+      <c r="A100" s="210"/>
+      <c r="B100" s="210"/>
+      <c r="C100" s="210"/>
+      <c r="D100" s="210"/>
+      <c r="E100" s="210"/>
     </row>
     <row r="101" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="212"/>
-      <c r="B101" s="212"/>
-      <c r="C101" s="212"/>
-      <c r="D101" s="212"/>
-      <c r="E101" s="212"/>
+      <c r="A101" s="210"/>
+      <c r="B101" s="210"/>
+      <c r="C101" s="210"/>
+      <c r="D101" s="210"/>
+      <c r="E101" s="210"/>
     </row>
     <row r="103" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="21" t="s">
@@ -3402,16 +3402,16 @@
     </row>
     <row r="125" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A126" s="218" t="s">
+      <c r="A126" s="215" t="s">
         <v>63</v>
       </c>
-      <c r="B126" s="212"/>
-      <c r="C126" s="212"/>
+      <c r="B126" s="210"/>
+      <c r="C126" s="210"/>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A127" s="212"/>
-      <c r="B127" s="212"/>
-      <c r="C127" s="212"/>
+      <c r="A127" s="210"/>
+      <c r="B127" s="210"/>
+      <c r="C127" s="210"/>
     </row>
     <row r="128" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="128"/>
@@ -3439,45 +3439,35 @@
       <c r="M131" s="8"/>
     </row>
     <row r="132" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="217"/>
-      <c r="B132" s="212"/>
-      <c r="C132" s="212"/>
-      <c r="D132" s="212"/>
-      <c r="E132" s="212"/>
+      <c r="A132" s="209"/>
+      <c r="B132" s="210"/>
+      <c r="C132" s="210"/>
+      <c r="D132" s="210"/>
+      <c r="E132" s="210"/>
     </row>
     <row r="133" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A133" s="212"/>
-      <c r="B133" s="212"/>
-      <c r="C133" s="212"/>
-      <c r="D133" s="212"/>
-      <c r="E133" s="212"/>
+      <c r="A133" s="210"/>
+      <c r="B133" s="210"/>
+      <c r="C133" s="210"/>
+      <c r="D133" s="210"/>
+      <c r="E133" s="210"/>
     </row>
     <row r="134" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A134" s="212"/>
-      <c r="B134" s="212"/>
-      <c r="C134" s="212"/>
-      <c r="D134" s="212"/>
-      <c r="E134" s="212"/>
+      <c r="A134" s="210"/>
+      <c r="B134" s="210"/>
+      <c r="C134" s="210"/>
+      <c r="D134" s="210"/>
+      <c r="E134" s="210"/>
     </row>
     <row r="135" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A135" s="212"/>
-      <c r="B135" s="212"/>
-      <c r="C135" s="212"/>
-      <c r="D135" s="212"/>
-      <c r="E135" s="212"/>
+      <c r="A135" s="210"/>
+      <c r="B135" s="210"/>
+      <c r="C135" s="210"/>
+      <c r="D135" s="210"/>
+      <c r="E135" s="210"/>
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="A132:E135"/>
-    <mergeCell ref="A99:E101"/>
-    <mergeCell ref="A85:B85"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A64:B64"/>
-    <mergeCell ref="A60:B60"/>
-    <mergeCell ref="A84:B84"/>
-    <mergeCell ref="A83:B83"/>
-    <mergeCell ref="A126:C127"/>
-    <mergeCell ref="A77:D77"/>
     <mergeCell ref="I70:J70"/>
     <mergeCell ref="B9:C11"/>
     <mergeCell ref="A67:B67"/>
@@ -3492,6 +3482,16 @@
     <mergeCell ref="A40:B40"/>
     <mergeCell ref="A56:B56"/>
     <mergeCell ref="A66:B66"/>
+    <mergeCell ref="A132:E135"/>
+    <mergeCell ref="A99:E101"/>
+    <mergeCell ref="A85:B85"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="A84:B84"/>
+    <mergeCell ref="A83:B83"/>
+    <mergeCell ref="A126:C127"/>
+    <mergeCell ref="A77:D77"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3534,16 +3534,16 @@
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
       <c r="F1" s="6"/>
-      <c r="G1" s="228"/>
-      <c r="H1" s="212"/>
-      <c r="I1" s="212"/>
-      <c r="J1" s="212"/>
-      <c r="K1" s="212"/>
-      <c r="L1" s="212"/>
-      <c r="M1" s="212"/>
-      <c r="N1" s="212"/>
-      <c r="O1" s="212"/>
-      <c r="P1" s="212"/>
+      <c r="G1" s="235"/>
+      <c r="H1" s="210"/>
+      <c r="I1" s="210"/>
+      <c r="J1" s="210"/>
+      <c r="K1" s="210"/>
+      <c r="L1" s="210"/>
+      <c r="M1" s="210"/>
+      <c r="N1" s="210"/>
+      <c r="O1" s="210"/>
+      <c r="P1" s="210"/>
       <c r="Q1" s="6"/>
       <c r="R1" s="6"/>
     </row>
@@ -3568,12 +3568,12 @@
       <c r="M2" s="7"/>
       <c r="N2" s="6"/>
       <c r="O2" s="6"/>
-      <c r="P2" s="224">
+      <c r="P2" s="232">
         <f>U2</f>
         <v>14485791.410000002</v>
       </c>
-      <c r="Q2" s="212"/>
-      <c r="R2" s="212"/>
+      <c r="Q2" s="210"/>
+      <c r="R2" s="210"/>
       <c r="S2" s="20"/>
       <c r="U2">
         <v>14485791.410000002</v>
@@ -3600,56 +3600,56 @@
       <c r="R3" s="59"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A4" s="235" t="s">
+      <c r="A4" s="227" t="s">
         <v>65</v>
       </c>
-      <c r="B4" s="237" t="s">
+      <c r="B4" s="229" t="s">
         <v>66</v>
       </c>
       <c r="C4" s="132"/>
-      <c r="D4" s="225" t="s">
+      <c r="D4" s="222" t="s">
         <v>67</v>
       </c>
-      <c r="E4" s="225" t="s">
+      <c r="E4" s="222" t="s">
         <v>68</v>
       </c>
-      <c r="F4" s="234" t="s">
+      <c r="F4" s="224" t="s">
         <v>69</v>
       </c>
-      <c r="G4" s="225" t="s">
+      <c r="G4" s="222" t="s">
         <v>70</v>
       </c>
-      <c r="H4" s="232" t="s">
+      <c r="H4" s="226" t="s">
         <v>71</v>
       </c>
-      <c r="I4" s="225" t="s">
+      <c r="I4" s="222" t="s">
         <v>51</v>
       </c>
-      <c r="J4" s="234" t="s">
+      <c r="J4" s="224" t="s">
         <v>72</v>
       </c>
-      <c r="K4" s="236" t="s">
+      <c r="K4" s="228" t="s">
         <v>73</v>
       </c>
-      <c r="L4" s="232" t="s">
+      <c r="L4" s="226" t="s">
         <v>74</v>
       </c>
-      <c r="M4" s="231" t="s">
+      <c r="M4" s="237" t="s">
         <v>75</v>
       </c>
-      <c r="N4" s="232" t="s">
+      <c r="N4" s="226" t="s">
         <v>76</v>
       </c>
-      <c r="O4" s="226" t="s">
+      <c r="O4" s="233" t="s">
         <v>77</v>
       </c>
       <c r="P4" s="62" t="s">
         <v>78</v>
       </c>
-      <c r="Q4" s="229" t="s">
+      <c r="Q4" s="236" t="s">
         <v>79</v>
       </c>
-      <c r="R4" s="222" t="s">
+      <c r="R4" s="231" t="s">
         <v>80</v>
       </c>
       <c r="U4" s="42"/>
@@ -3660,16 +3660,16 @@
       <c r="C5" s="133"/>
       <c r="D5" s="223"/>
       <c r="E5" s="223"/>
-      <c r="F5" s="233"/>
+      <c r="F5" s="225"/>
       <c r="G5" s="223"/>
-      <c r="H5" s="233"/>
+      <c r="H5" s="225"/>
       <c r="I5" s="223"/>
-      <c r="J5" s="233"/>
-      <c r="K5" s="233"/>
-      <c r="L5" s="233"/>
+      <c r="J5" s="225"/>
+      <c r="K5" s="225"/>
+      <c r="L5" s="225"/>
       <c r="M5" s="223"/>
-      <c r="N5" s="233"/>
-      <c r="O5" s="227"/>
+      <c r="N5" s="225"/>
+      <c r="O5" s="234"/>
       <c r="P5" s="60" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 14/08</v>
@@ -8268,94 +8268,102 @@
     </row>
     <row r="83" spans="2:18" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="84" spans="2:18" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E84" s="217" t="str">
+      <c r="E84" s="209" t="str">
         <f>RESUMEN!A14</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. CASO CONTRARIO SE INFORMARA VIA CARTA DOCUMENTO A LA UNIDAD FUNCIONAL QUE CREEMOS QUE CORRESPONDE, CUYO COSTO SERA IMPUTADO A LA UNIDAD FUNCIONAL SOSPECHADA.</v>
       </c>
-      <c r="F84" s="212"/>
-      <c r="G84" s="212"/>
-      <c r="H84" s="212"/>
-      <c r="I84" s="212"/>
-      <c r="J84" s="212"/>
-      <c r="K84" s="212"/>
-      <c r="L84" s="212"/>
-      <c r="M84" s="212"/>
-      <c r="N84" s="212"/>
-      <c r="O84" s="212"/>
-      <c r="P84" s="212"/>
+      <c r="F84" s="210"/>
+      <c r="G84" s="210"/>
+      <c r="H84" s="210"/>
+      <c r="I84" s="210"/>
+      <c r="J84" s="210"/>
+      <c r="K84" s="210"/>
+      <c r="L84" s="210"/>
+      <c r="M84" s="210"/>
+      <c r="N84" s="210"/>
+      <c r="O84" s="210"/>
+      <c r="P84" s="210"/>
     </row>
     <row r="85" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E85" s="212"/>
-      <c r="F85" s="212"/>
-      <c r="G85" s="212"/>
-      <c r="H85" s="212"/>
-      <c r="I85" s="212"/>
-      <c r="J85" s="212"/>
-      <c r="K85" s="212"/>
-      <c r="L85" s="212"/>
-      <c r="M85" s="212"/>
-      <c r="N85" s="212"/>
-      <c r="O85" s="212"/>
-      <c r="P85" s="212"/>
+      <c r="E85" s="210"/>
+      <c r="F85" s="210"/>
+      <c r="G85" s="210"/>
+      <c r="H85" s="210"/>
+      <c r="I85" s="210"/>
+      <c r="J85" s="210"/>
+      <c r="K85" s="210"/>
+      <c r="L85" s="210"/>
+      <c r="M85" s="210"/>
+      <c r="N85" s="210"/>
+      <c r="O85" s="210"/>
+      <c r="P85" s="210"/>
     </row>
     <row r="86" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E86" s="212"/>
-      <c r="F86" s="212"/>
-      <c r="G86" s="212"/>
-      <c r="H86" s="212"/>
-      <c r="I86" s="212"/>
-      <c r="J86" s="212"/>
-      <c r="K86" s="212"/>
-      <c r="L86" s="212"/>
-      <c r="M86" s="212"/>
-      <c r="N86" s="212"/>
-      <c r="O86" s="212"/>
-      <c r="P86" s="212"/>
+      <c r="E86" s="210"/>
+      <c r="F86" s="210"/>
+      <c r="G86" s="210"/>
+      <c r="H86" s="210"/>
+      <c r="I86" s="210"/>
+      <c r="J86" s="210"/>
+      <c r="K86" s="210"/>
+      <c r="L86" s="210"/>
+      <c r="M86" s="210"/>
+      <c r="N86" s="210"/>
+      <c r="O86" s="210"/>
+      <c r="P86" s="210"/>
     </row>
     <row r="87" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E87" s="212"/>
-      <c r="F87" s="212"/>
-      <c r="G87" s="212"/>
-      <c r="H87" s="212"/>
-      <c r="I87" s="212"/>
-      <c r="J87" s="212"/>
-      <c r="K87" s="212"/>
-      <c r="L87" s="212"/>
-      <c r="M87" s="212"/>
-      <c r="N87" s="212"/>
-      <c r="O87" s="212"/>
-      <c r="P87" s="212"/>
+      <c r="E87" s="210"/>
+      <c r="F87" s="210"/>
+      <c r="G87" s="210"/>
+      <c r="H87" s="210"/>
+      <c r="I87" s="210"/>
+      <c r="J87" s="210"/>
+      <c r="K87" s="210"/>
+      <c r="L87" s="210"/>
+      <c r="M87" s="210"/>
+      <c r="N87" s="210"/>
+      <c r="O87" s="210"/>
+      <c r="P87" s="210"/>
     </row>
     <row r="88" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E88" s="212"/>
-      <c r="F88" s="212"/>
-      <c r="G88" s="212"/>
-      <c r="H88" s="212"/>
-      <c r="I88" s="212"/>
-      <c r="J88" s="212"/>
-      <c r="K88" s="212"/>
-      <c r="L88" s="212"/>
-      <c r="M88" s="212"/>
-      <c r="N88" s="212"/>
-      <c r="O88" s="212"/>
-      <c r="P88" s="212"/>
+      <c r="E88" s="210"/>
+      <c r="F88" s="210"/>
+      <c r="G88" s="210"/>
+      <c r="H88" s="210"/>
+      <c r="I88" s="210"/>
+      <c r="J88" s="210"/>
+      <c r="K88" s="210"/>
+      <c r="L88" s="210"/>
+      <c r="M88" s="210"/>
+      <c r="N88" s="210"/>
+      <c r="O88" s="210"/>
+      <c r="P88" s="210"/>
     </row>
     <row r="89" spans="2:18" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E89" s="212"/>
-      <c r="F89" s="212"/>
-      <c r="G89" s="212"/>
-      <c r="H89" s="212"/>
-      <c r="I89" s="212"/>
-      <c r="J89" s="212"/>
-      <c r="K89" s="212"/>
-      <c r="L89" s="212"/>
-      <c r="M89" s="212"/>
-      <c r="N89" s="212"/>
-      <c r="O89" s="212"/>
-      <c r="P89" s="212"/>
+      <c r="E89" s="210"/>
+      <c r="F89" s="210"/>
+      <c r="G89" s="210"/>
+      <c r="H89" s="210"/>
+      <c r="I89" s="210"/>
+      <c r="J89" s="210"/>
+      <c r="K89" s="210"/>
+      <c r="L89" s="210"/>
+      <c r="M89" s="210"/>
+      <c r="N89" s="210"/>
+      <c r="O89" s="210"/>
+      <c r="P89" s="210"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="R4:R5"/>
+    <mergeCell ref="P2:R2"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="O4:O5"/>
+    <mergeCell ref="G1:P1"/>
+    <mergeCell ref="Q4:Q5"/>
+    <mergeCell ref="M4:M5"/>
+    <mergeCell ref="N4:N5"/>
     <mergeCell ref="E84:P89"/>
     <mergeCell ref="D4:D5"/>
     <mergeCell ref="J4:J5"/>
@@ -8367,14 +8375,6 @@
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="F4:F5"/>
     <mergeCell ref="H4:H5"/>
-    <mergeCell ref="R4:R5"/>
-    <mergeCell ref="P2:R2"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="O4:O5"/>
-    <mergeCell ref="G1:P1"/>
-    <mergeCell ref="Q4:Q5"/>
-    <mergeCell ref="M4:M5"/>
-    <mergeCell ref="N4:N5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
@@ -8429,16 +8429,16 @@
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
       <c r="F1" s="6"/>
-      <c r="G1" s="228"/>
-      <c r="H1" s="212"/>
-      <c r="I1" s="212"/>
-      <c r="J1" s="212"/>
-      <c r="K1" s="212"/>
-      <c r="L1" s="212"/>
-      <c r="M1" s="212"/>
-      <c r="N1" s="212"/>
-      <c r="O1" s="212"/>
-      <c r="P1" s="212"/>
+      <c r="G1" s="235"/>
+      <c r="H1" s="210"/>
+      <c r="I1" s="210"/>
+      <c r="J1" s="210"/>
+      <c r="K1" s="210"/>
+      <c r="L1" s="210"/>
+      <c r="M1" s="210"/>
+      <c r="N1" s="210"/>
+      <c r="O1" s="210"/>
+      <c r="P1" s="210"/>
       <c r="Q1" s="6"/>
       <c r="R1" s="6"/>
     </row>
@@ -8462,12 +8462,12 @@
       <c r="M2" s="7"/>
       <c r="N2" s="6"/>
       <c r="O2" s="6"/>
-      <c r="P2" s="224">
+      <c r="P2" s="232">
         <f>16770000+7700000</f>
         <v>24470000</v>
       </c>
-      <c r="Q2" s="212"/>
-      <c r="R2" s="212"/>
+      <c r="Q2" s="210"/>
+      <c r="R2" s="210"/>
       <c r="S2" s="20"/>
     </row>
     <row r="3" spans="1:21" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -8491,54 +8491,54 @@
       <c r="R3" s="59"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A4" s="235" t="s">
+      <c r="A4" s="227" t="s">
         <v>65</v>
       </c>
-      <c r="B4" s="237" t="s">
+      <c r="B4" s="229" t="s">
         <v>66</v>
       </c>
       <c r="C4" s="132"/>
-      <c r="D4" s="225" t="s">
+      <c r="D4" s="222" t="s">
         <v>67</v>
       </c>
-      <c r="E4" s="225" t="s">
+      <c r="E4" s="222" t="s">
         <v>68</v>
       </c>
-      <c r="F4" s="234" t="s">
+      <c r="F4" s="224" t="s">
         <v>69</v>
       </c>
-      <c r="G4" s="225" t="s">
+      <c r="G4" s="222" t="s">
         <v>70</v>
       </c>
-      <c r="H4" s="232" t="s">
+      <c r="H4" s="226" t="s">
         <v>71</v>
       </c>
-      <c r="I4" s="225" t="s">
+      <c r="I4" s="222" t="s">
         <v>51</v>
       </c>
-      <c r="J4" s="234" t="s">
+      <c r="J4" s="224" t="s">
         <v>72</v>
       </c>
-      <c r="K4" s="236" t="s">
+      <c r="K4" s="228" t="s">
         <v>73</v>
       </c>
-      <c r="L4" s="232" t="s">
+      <c r="L4" s="226" t="s">
         <v>74</v>
       </c>
-      <c r="M4" s="231" t="s">
+      <c r="M4" s="237" t="s">
         <v>75</v>
       </c>
-      <c r="N4" s="232" t="s">
+      <c r="N4" s="226" t="s">
         <v>236</v>
       </c>
-      <c r="O4" s="226"/>
-      <c r="P4" s="222" t="s">
+      <c r="O4" s="233"/>
+      <c r="P4" s="231" t="s">
         <v>78</v>
       </c>
-      <c r="Q4" s="229" t="s">
+      <c r="Q4" s="236" t="s">
         <v>79</v>
       </c>
-      <c r="R4" s="222" t="s">
+      <c r="R4" s="231" t="s">
         <v>80</v>
       </c>
       <c r="U4" s="42"/>
@@ -8549,16 +8549,16 @@
       <c r="C5" s="133"/>
       <c r="D5" s="223"/>
       <c r="E5" s="223"/>
-      <c r="F5" s="233"/>
+      <c r="F5" s="225"/>
       <c r="G5" s="223"/>
-      <c r="H5" s="233"/>
+      <c r="H5" s="225"/>
       <c r="I5" s="223"/>
-      <c r="J5" s="233"/>
-      <c r="K5" s="233"/>
-      <c r="L5" s="233"/>
+      <c r="J5" s="225"/>
+      <c r="K5" s="225"/>
+      <c r="L5" s="225"/>
       <c r="M5" s="223"/>
-      <c r="N5" s="233"/>
-      <c r="O5" s="227"/>
+      <c r="N5" s="225"/>
+      <c r="O5" s="234"/>
       <c r="P5" s="238"/>
       <c r="Q5" s="230"/>
       <c r="R5" s="223"/>
@@ -12413,94 +12413,102 @@
     </row>
     <row r="83" spans="2:18" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="84" spans="2:18" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E84" s="217" t="str">
+      <c r="E84" s="209" t="str">
         <f>RESUMEN!A14</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. CASO CONTRARIO SE INFORMARA VIA CARTA DOCUMENTO A LA UNIDAD FUNCIONAL QUE CREEMOS QUE CORRESPONDE, CUYO COSTO SERA IMPUTADO A LA UNIDAD FUNCIONAL SOSPECHADA.</v>
       </c>
-      <c r="F84" s="212"/>
-      <c r="G84" s="212"/>
-      <c r="H84" s="212"/>
-      <c r="I84" s="212"/>
-      <c r="J84" s="212"/>
-      <c r="K84" s="212"/>
-      <c r="L84" s="212"/>
-      <c r="M84" s="212"/>
-      <c r="N84" s="212"/>
-      <c r="O84" s="212"/>
-      <c r="P84" s="212"/>
+      <c r="F84" s="210"/>
+      <c r="G84" s="210"/>
+      <c r="H84" s="210"/>
+      <c r="I84" s="210"/>
+      <c r="J84" s="210"/>
+      <c r="K84" s="210"/>
+      <c r="L84" s="210"/>
+      <c r="M84" s="210"/>
+      <c r="N84" s="210"/>
+      <c r="O84" s="210"/>
+      <c r="P84" s="210"/>
     </row>
     <row r="85" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E85" s="212"/>
-      <c r="F85" s="212"/>
-      <c r="G85" s="212"/>
-      <c r="H85" s="212"/>
-      <c r="I85" s="212"/>
-      <c r="J85" s="212"/>
-      <c r="K85" s="212"/>
-      <c r="L85" s="212"/>
-      <c r="M85" s="212"/>
-      <c r="N85" s="212"/>
-      <c r="O85" s="212"/>
-      <c r="P85" s="212"/>
+      <c r="E85" s="210"/>
+      <c r="F85" s="210"/>
+      <c r="G85" s="210"/>
+      <c r="H85" s="210"/>
+      <c r="I85" s="210"/>
+      <c r="J85" s="210"/>
+      <c r="K85" s="210"/>
+      <c r="L85" s="210"/>
+      <c r="M85" s="210"/>
+      <c r="N85" s="210"/>
+      <c r="O85" s="210"/>
+      <c r="P85" s="210"/>
     </row>
     <row r="86" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E86" s="212"/>
-      <c r="F86" s="212"/>
-      <c r="G86" s="212"/>
-      <c r="H86" s="212"/>
-      <c r="I86" s="212"/>
-      <c r="J86" s="212"/>
-      <c r="K86" s="212"/>
-      <c r="L86" s="212"/>
-      <c r="M86" s="212"/>
-      <c r="N86" s="212"/>
-      <c r="O86" s="212"/>
-      <c r="P86" s="212"/>
+      <c r="E86" s="210"/>
+      <c r="F86" s="210"/>
+      <c r="G86" s="210"/>
+      <c r="H86" s="210"/>
+      <c r="I86" s="210"/>
+      <c r="J86" s="210"/>
+      <c r="K86" s="210"/>
+      <c r="L86" s="210"/>
+      <c r="M86" s="210"/>
+      <c r="N86" s="210"/>
+      <c r="O86" s="210"/>
+      <c r="P86" s="210"/>
     </row>
     <row r="87" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E87" s="212"/>
-      <c r="F87" s="212"/>
-      <c r="G87" s="212"/>
-      <c r="H87" s="212"/>
-      <c r="I87" s="212"/>
-      <c r="J87" s="212"/>
-      <c r="K87" s="212"/>
-      <c r="L87" s="212"/>
-      <c r="M87" s="212"/>
-      <c r="N87" s="212"/>
-      <c r="O87" s="212"/>
-      <c r="P87" s="212"/>
+      <c r="E87" s="210"/>
+      <c r="F87" s="210"/>
+      <c r="G87" s="210"/>
+      <c r="H87" s="210"/>
+      <c r="I87" s="210"/>
+      <c r="J87" s="210"/>
+      <c r="K87" s="210"/>
+      <c r="L87" s="210"/>
+      <c r="M87" s="210"/>
+      <c r="N87" s="210"/>
+      <c r="O87" s="210"/>
+      <c r="P87" s="210"/>
     </row>
     <row r="88" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E88" s="212"/>
-      <c r="F88" s="212"/>
-      <c r="G88" s="212"/>
-      <c r="H88" s="212"/>
-      <c r="I88" s="212"/>
-      <c r="J88" s="212"/>
-      <c r="K88" s="212"/>
-      <c r="L88" s="212"/>
-      <c r="M88" s="212"/>
-      <c r="N88" s="212"/>
-      <c r="O88" s="212"/>
-      <c r="P88" s="212"/>
+      <c r="E88" s="210"/>
+      <c r="F88" s="210"/>
+      <c r="G88" s="210"/>
+      <c r="H88" s="210"/>
+      <c r="I88" s="210"/>
+      <c r="J88" s="210"/>
+      <c r="K88" s="210"/>
+      <c r="L88" s="210"/>
+      <c r="M88" s="210"/>
+      <c r="N88" s="210"/>
+      <c r="O88" s="210"/>
+      <c r="P88" s="210"/>
     </row>
     <row r="89" spans="2:18" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E89" s="212"/>
-      <c r="F89" s="212"/>
-      <c r="G89" s="212"/>
-      <c r="H89" s="212"/>
-      <c r="I89" s="212"/>
-      <c r="J89" s="212"/>
-      <c r="K89" s="212"/>
-      <c r="L89" s="212"/>
-      <c r="M89" s="212"/>
-      <c r="N89" s="212"/>
-      <c r="O89" s="212"/>
-      <c r="P89" s="212"/>
+      <c r="E89" s="210"/>
+      <c r="F89" s="210"/>
+      <c r="G89" s="210"/>
+      <c r="H89" s="210"/>
+      <c r="I89" s="210"/>
+      <c r="J89" s="210"/>
+      <c r="K89" s="210"/>
+      <c r="L89" s="210"/>
+      <c r="M89" s="210"/>
+      <c r="N89" s="210"/>
+      <c r="O89" s="210"/>
+      <c r="P89" s="210"/>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="E84:P89"/>
+    <mergeCell ref="P4:P5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="L4:L5"/>
+    <mergeCell ref="M4:M5"/>
+    <mergeCell ref="N4:N5"/>
+    <mergeCell ref="O4:O5"/>
     <mergeCell ref="G1:P1"/>
     <mergeCell ref="P2:R2"/>
     <mergeCell ref="A4:A5"/>
@@ -12513,14 +12521,6 @@
     <mergeCell ref="I4:I5"/>
     <mergeCell ref="Q4:Q5"/>
     <mergeCell ref="R4:R5"/>
-    <mergeCell ref="E84:P89"/>
-    <mergeCell ref="P4:P5"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="L4:L5"/>
-    <mergeCell ref="M4:M5"/>
-    <mergeCell ref="N4:N5"/>
-    <mergeCell ref="O4:O5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
